--- a/PIT3/validation-rules/Employer_Submission_RPN_Validation_Rules.xlsx
+++ b/PIT3/validation-rules/Employer_Submission_RPN_Validation_Rules.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294E2B46-C888-47A2-B9A7-0B7C96ADE6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0FF0B1-1AF1-4AD8-8269-A463F72441D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2340" windowWidth="23940" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Document Control" sheetId="5" r:id="rId1"/>
     <sheet name="ValidationRules" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ValidationRules!$G$1:$G$480</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ValidationRules!$G$1:$G$481</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Document Control'!$A$1:$E$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">ValidationRules!$A$1:$M$149</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">ValidationRules!$A$1:$M$150</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">ValidationRules!$1:$1</definedName>
     <definedName name="ValidationCodes">#REF!</definedName>
   </definedNames>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="301">
   <si>
     <t>Payslip</t>
   </si>
@@ -1003,6 +1003,9 @@
   <si>
     <t>165, 166, 167, 168, 169, 170</t>
   </si>
+  <si>
+    <t>A PRSI class and number of insurable week(s) should be included when PRSI Exemption Reason is of type “Employment of certain family members”, “Under 16 years of age”, “Employment on certain social welfare schemes” or “other” is used</t>
+  </si>
 </sst>
 </file>
 
@@ -1298,7 +1301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1568,9 +1571,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -22279,18 +22279,18 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
     </row>
     <row r="11" spans="2:13" ht="30.2" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
@@ -22592,7 +22592,7 @@
       <c r="K30" s="13"/>
       <c r="M30" s="12"/>
     </row>
-    <row r="31" spans="2:13" ht="30.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="17"/>
       <c r="C31" s="68" t="s">
         <v>224</v>
@@ -22614,7 +22614,7 @@
       <c r="K32" s="13"/>
       <c r="M32" s="12"/>
     </row>
-    <row r="33" spans="2:4" ht="30.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B33" s="79"/>
       <c r="C33" s="81" t="s">
         <v>139</v>
@@ -22925,7 +22925,7 @@
       <c r="C67" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="D67" s="101" t="s">
+      <c r="D67" s="100" t="s">
         <v>162</v>
       </c>
     </row>
@@ -22966,9 +22966,13 @@
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B72" s="100"/>
-      <c r="C72" s="100"/>
-      <c r="D72" s="13"/>
+      <c r="B72" s="79"/>
+      <c r="C72" s="79">
+        <v>171</v>
+      </c>
+      <c r="D72" s="80" t="s">
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -22985,7 +22989,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BN480"/>
+  <dimension ref="A1:BN481"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" outlineLevelRow="2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -23102,23 +23106,23 @@
       <c r="BN1" s="20"/>
     </row>
     <row r="2" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="105" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="105"/>
       <c r="P2" s="21"/>
       <c r="Q2" s="21"/>
       <c r="R2" s="21"/>
@@ -23172,23 +23176,23 @@
       <c r="BN2" s="21"/>
     </row>
     <row r="3" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="107"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="106"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
@@ -23441,10 +23445,10 @@
       <c r="A6" s="92">
         <v>2</v>
       </c>
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="C6" s="102" t="s">
         <v>147</v>
       </c>
       <c r="D6" s="92" t="s">
@@ -23474,10 +23478,10 @@
       <c r="L6" s="92">
         <v>1013</v>
       </c>
-      <c r="M6" s="103" t="s">
+      <c r="M6" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="N6" s="102" t="s">
+      <c r="N6" s="101" t="s">
         <v>12</v>
       </c>
       <c r="O6" s="93" t="s">
@@ -24354,23 +24358,23 @@
       </c>
     </row>
     <row r="26" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="106" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="107"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="107"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="107"/>
-      <c r="N26" s="107"/>
-      <c r="O26" s="107"/>
+      <c r="B26" s="106"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="106"/>
+      <c r="O26" s="106"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
       <c r="R26" s="21"/>
@@ -26296,65 +26300,65 @@
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:66" ht="78.75" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>46</v>
-      </c>
-      <c r="B56" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>67</v>
+      <c r="C56" s="3" t="s">
+        <v>300</v>
       </c>
       <c r="D56" s="5">
         <v>31</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="F56" s="24" t="s">
+      <c r="F56" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="24">
+      <c r="G56" s="38">
         <v>200</v>
       </c>
-      <c r="H56" s="24" t="s">
+      <c r="H56" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="I56" s="24" t="s">
+      <c r="I56" s="38" t="s">
         <v>220</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="L56" s="8">
-        <v>2037</v>
-      </c>
-      <c r="M56" s="30" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="L56" s="5">
+        <v>2061</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>300</v>
       </c>
       <c r="N56" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="O56" s="37" t="s">
-        <v>120</v>
+      <c r="O56" s="31" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="D57" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>140</v>
@@ -26378,30 +26382,30 @@
         <v>11</v>
       </c>
       <c r="L57" s="8">
-        <v>2036</v>
-      </c>
-      <c r="M57" s="32" t="s">
-        <v>161</v>
+        <v>2037</v>
+      </c>
+      <c r="M57" s="30" t="s">
+        <v>21</v>
       </c>
       <c r="N57" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="O57" s="31" t="s">
-        <v>56</v>
+      <c r="O57" s="37" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C58" s="23" t="s">
-        <v>107</v>
+      <c r="C58" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="D58" s="5">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>140</v>
@@ -26422,178 +26426,127 @@
         <v>7</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L58" s="8">
-        <v>2038</v>
-      </c>
-      <c r="M58" s="30" t="s">
-        <v>106</v>
+        <v>2036</v>
+      </c>
+      <c r="M58" s="32" t="s">
+        <v>161</v>
       </c>
       <c r="N58" s="31" t="s">
         <v>0</v>
       </c>
       <c r="O58" s="31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:66" s="73" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A59" s="58">
-        <v>49</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>48</v>
       </c>
       <c r="B59" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" s="58">
-        <v>39</v>
-      </c>
-      <c r="E59" s="58" t="s">
+      <c r="C59" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="5">
+        <v>35</v>
+      </c>
+      <c r="E59" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F59" s="58" t="s">
+      <c r="F59" s="24" t="s">
         <v>140</v>
       </c>
       <c r="G59" s="24">
         <v>200</v>
       </c>
-      <c r="H59" s="74" t="s">
+      <c r="H59" s="24" t="s">
         <v>217</v>
       </c>
       <c r="I59" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="J59" s="58" t="s">
+      <c r="J59" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K59" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="L59" s="61">
-        <v>2039</v>
-      </c>
-      <c r="M59" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="N59" s="59" t="s">
+      <c r="K59" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L59" s="8">
+        <v>2038</v>
+      </c>
+      <c r="M59" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="N59" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="O59" s="59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
-        <v>50</v>
+      <c r="O59" s="31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:66" s="73" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A60" s="58">
+        <v>49</v>
       </c>
       <c r="B60" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="D60" s="4">
-        <v>19</v>
-      </c>
-      <c r="E60" s="24" t="s">
+      <c r="C60" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="58">
+        <v>39</v>
+      </c>
+      <c r="E60" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="F60" s="24" t="s">
+      <c r="F60" s="58" t="s">
         <v>140</v>
       </c>
       <c r="G60" s="24">
         <v>200</v>
       </c>
-      <c r="H60" s="24" t="s">
+      <c r="H60" s="74" t="s">
         <v>217</v>
       </c>
       <c r="I60" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="J60" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L60" s="10">
-        <v>2044</v>
-      </c>
-      <c r="M60" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="N60" s="30" t="s">
+      <c r="J60" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="K60" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="L60" s="61">
+        <v>2039</v>
+      </c>
+      <c r="M60" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="N60" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="O60" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="22"/>
-      <c r="R60" s="22"/>
-      <c r="S60" s="22"/>
-      <c r="T60" s="22"/>
-      <c r="U60" s="22"/>
-      <c r="V60" s="22"/>
-      <c r="W60" s="22"/>
-      <c r="X60" s="22"/>
-      <c r="Y60" s="22"/>
-      <c r="Z60" s="22"/>
-      <c r="AA60" s="22"/>
-      <c r="AB60" s="22"/>
-      <c r="AC60" s="22"/>
-      <c r="AD60" s="22"/>
-      <c r="AE60" s="22"/>
-      <c r="AF60" s="22"/>
-      <c r="AG60" s="22"/>
-      <c r="AH60" s="22"/>
-      <c r="AI60" s="22"/>
-      <c r="AJ60" s="22"/>
-      <c r="AK60" s="22"/>
-      <c r="AL60" s="22"/>
-      <c r="AM60" s="22"/>
-      <c r="AN60" s="22"/>
-      <c r="AO60" s="22"/>
-      <c r="AP60" s="22"/>
-      <c r="AQ60" s="22"/>
-      <c r="AR60" s="22"/>
-      <c r="AS60" s="22"/>
-      <c r="AT60" s="22"/>
-      <c r="AU60" s="22"/>
-      <c r="AV60" s="22"/>
-      <c r="AW60" s="22"/>
-      <c r="AX60" s="22"/>
-      <c r="AY60" s="22"/>
-      <c r="AZ60" s="22"/>
-      <c r="BA60" s="22"/>
-      <c r="BB60" s="22"/>
-      <c r="BC60" s="22"/>
-      <c r="BD60" s="22"/>
-      <c r="BE60" s="22"/>
-      <c r="BF60" s="22"/>
-      <c r="BG60" s="22"/>
-      <c r="BH60" s="22"/>
-      <c r="BI60" s="22"/>
-      <c r="BJ60" s="22"/>
-      <c r="BK60" s="22"/>
-      <c r="BL60" s="22"/>
-      <c r="BM60" s="22"/>
-      <c r="BN60" s="22"/>
+      <c r="O60" s="59" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="61" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B61" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C61" s="87" t="s">
-        <v>237</v>
+      <c r="C61" s="51" t="s">
+        <v>144</v>
       </c>
       <c r="D61" s="4">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E61" s="24" t="s">
         <v>140</v>
@@ -26617,16 +26570,16 @@
         <v>32</v>
       </c>
       <c r="L61" s="10">
-        <v>2045</v>
-      </c>
-      <c r="M61" s="90" t="s">
-        <v>237</v>
+        <v>2044</v>
+      </c>
+      <c r="M61" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="N61" s="30" t="s">
         <v>0</v>
       </c>
       <c r="O61" s="30" t="s">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="P61" s="22"/>
       <c r="Q61" s="22"/>
@@ -26682,24 +26635,24 @@
     </row>
     <row r="62" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>122</v>
-      </c>
-      <c r="B62" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B62" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C62" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="D62" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" s="54" t="s">
+      <c r="C62" s="87" t="s">
+        <v>237</v>
+      </c>
+      <c r="D62" s="4">
+        <v>8</v>
+      </c>
+      <c r="E62" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F62" s="54" t="s">
+      <c r="F62" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G62" s="54">
+      <c r="G62" s="24">
         <v>200</v>
       </c>
       <c r="H62" s="24" t="s">
@@ -26708,23 +26661,23 @@
       <c r="I62" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="J62" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="K62" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="L62" s="53">
-        <v>2047</v>
-      </c>
-      <c r="M62" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="N62" s="52" t="s">
+      <c r="J62" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62" s="10">
+        <v>2045</v>
+      </c>
+      <c r="M62" s="90" t="s">
+        <v>237</v>
+      </c>
+      <c r="N62" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="O62" s="63" t="s">
-        <v>0</v>
+      <c r="O62" s="30" t="s">
+        <v>1</v>
       </c>
       <c r="P62" s="22"/>
       <c r="Q62" s="22"/>
@@ -26778,51 +26731,51 @@
       <c r="BM62" s="22"/>
       <c r="BN62" s="22"/>
     </row>
-    <row r="63" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>155</v>
-      </c>
-      <c r="B63" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="85" t="s">
-        <v>276</v>
-      </c>
-      <c r="D63" s="4">
-        <v>16</v>
-      </c>
-      <c r="E63" s="24" t="s">
+      <c r="C63" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="F63" s="24" t="s">
+      <c r="F63" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="G63" s="24">
+      <c r="G63" s="54">
         <v>200</v>
       </c>
       <c r="H63" s="24" t="s">
         <v>217</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L63" s="10">
-        <v>2052</v>
-      </c>
-      <c r="M63" s="85" t="s">
-        <v>276</v>
-      </c>
-      <c r="N63" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="J63" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="K63" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="L63" s="53">
+        <v>2047</v>
+      </c>
+      <c r="M63" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="N63" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="O63" s="30" t="s">
-        <v>277</v>
+      <c r="O63" s="63" t="s">
+        <v>0</v>
       </c>
       <c r="P63" s="22"/>
       <c r="Q63" s="22"/>
@@ -26876,18 +26829,18 @@
       <c r="BM63" s="22"/>
       <c r="BN63" s="22"/>
     </row>
-    <row r="64" spans="1:66" s="7" customFormat="1" ht="220.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B64" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C64" s="85" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D64" s="4">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="E64" s="24" t="s">
         <v>140</v>
@@ -26904,23 +26857,23 @@
       <c r="I64" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="J64" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="K64" s="5" t="s">
-        <v>11</v>
+      <c r="J64" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="L64" s="10">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="M64" s="85" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="N64" s="30" t="s">
         <v>0</v>
       </c>
       <c r="O64" s="30" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="P64" s="22"/>
       <c r="Q64" s="22"/>
@@ -26974,51 +26927,51 @@
       <c r="BM64" s="22"/>
       <c r="BN64" s="22"/>
     </row>
-    <row r="65" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
-        <v>159</v>
+    <row r="65" spans="1:66" s="7" customFormat="1" ht="220.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>157</v>
       </c>
       <c r="B65" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C65" s="99" t="s">
-        <v>285</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" s="10" t="s">
+      <c r="C65" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="D65" s="4">
+        <v>55</v>
+      </c>
+      <c r="E65" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F65" s="10" t="s">
+      <c r="F65" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G65" s="10">
+      <c r="G65" s="24">
         <v>200</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="24" t="s">
         <v>217</v>
       </c>
       <c r="I65" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="J65" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K65" s="58" t="s">
+      <c r="J65" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="K65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="L65" s="10">
-        <v>2056</v>
-      </c>
-      <c r="M65" s="99" t="s">
-        <v>285</v>
+        <v>2053</v>
+      </c>
+      <c r="M65" s="85" t="s">
+        <v>282</v>
       </c>
       <c r="N65" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="O65" s="99" t="s">
-        <v>12</v>
+      <c r="O65" s="30" t="s">
+        <v>281</v>
       </c>
       <c r="P65" s="22"/>
       <c r="Q65" s="22"/>
@@ -27074,13 +27027,13 @@
     </row>
     <row r="66" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B66" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C66" s="99" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>12</v>
@@ -27107,10 +27060,10 @@
         <v>11</v>
       </c>
       <c r="L66" s="10">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="M66" s="99" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N66" s="30" t="s">
         <v>0</v>
@@ -27172,13 +27125,13 @@
     </row>
     <row r="67" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B67" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C67" s="99" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>12</v>
@@ -27205,10 +27158,10 @@
         <v>11</v>
       </c>
       <c r="L67" s="10">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="M67" s="99" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N67" s="30" t="s">
         <v>0</v>
@@ -27270,13 +27223,13 @@
     </row>
     <row r="68" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B68" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C68" s="30" t="s">
-        <v>290</v>
+      <c r="C68" s="99" t="s">
+        <v>287</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>12</v>
@@ -27303,10 +27256,10 @@
         <v>11</v>
       </c>
       <c r="L68" s="10">
-        <v>2060</v>
-      </c>
-      <c r="M68" s="30" t="s">
-        <v>290</v>
+        <v>2058</v>
+      </c>
+      <c r="M68" s="99" t="s">
+        <v>287</v>
       </c>
       <c r="N68" s="30" t="s">
         <v>0</v>
@@ -27366,94 +27319,122 @@
       <c r="BM68" s="22"/>
       <c r="BN68" s="22"/>
     </row>
-    <row r="69" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="108" t="s">
+    <row r="69" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
+        <v>163</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G69" s="10">
+        <v>200</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="I69" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K69" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="L69" s="10">
+        <v>2060</v>
+      </c>
+      <c r="M69" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="N69" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="O69" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="P69" s="22"/>
+      <c r="Q69" s="22"/>
+      <c r="R69" s="22"/>
+      <c r="S69" s="22"/>
+      <c r="T69" s="22"/>
+      <c r="U69" s="22"/>
+      <c r="V69" s="22"/>
+      <c r="W69" s="22"/>
+      <c r="X69" s="22"/>
+      <c r="Y69" s="22"/>
+      <c r="Z69" s="22"/>
+      <c r="AA69" s="22"/>
+      <c r="AB69" s="22"/>
+      <c r="AC69" s="22"/>
+      <c r="AD69" s="22"/>
+      <c r="AE69" s="22"/>
+      <c r="AF69" s="22"/>
+      <c r="AG69" s="22"/>
+      <c r="AH69" s="22"/>
+      <c r="AI69" s="22"/>
+      <c r="AJ69" s="22"/>
+      <c r="AK69" s="22"/>
+      <c r="AL69" s="22"/>
+      <c r="AM69" s="22"/>
+      <c r="AN69" s="22"/>
+      <c r="AO69" s="22"/>
+      <c r="AP69" s="22"/>
+      <c r="AQ69" s="22"/>
+      <c r="AR69" s="22"/>
+      <c r="AS69" s="22"/>
+      <c r="AT69" s="22"/>
+      <c r="AU69" s="22"/>
+      <c r="AV69" s="22"/>
+      <c r="AW69" s="22"/>
+      <c r="AX69" s="22"/>
+      <c r="AY69" s="22"/>
+      <c r="AZ69" s="22"/>
+      <c r="BA69" s="22"/>
+      <c r="BB69" s="22"/>
+      <c r="BC69" s="22"/>
+      <c r="BD69" s="22"/>
+      <c r="BE69" s="22"/>
+      <c r="BF69" s="22"/>
+      <c r="BG69" s="22"/>
+      <c r="BH69" s="22"/>
+      <c r="BI69" s="22"/>
+      <c r="BJ69" s="22"/>
+      <c r="BK69" s="22"/>
+      <c r="BL69" s="22"/>
+      <c r="BM69" s="22"/>
+      <c r="BN69" s="22"/>
+    </row>
+    <row r="70" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="B69" s="109"/>
-      <c r="C69" s="109"/>
-      <c r="D69" s="109"/>
-      <c r="E69" s="109"/>
-      <c r="F69" s="109"/>
-      <c r="G69" s="109"/>
-      <c r="H69" s="109"/>
-      <c r="I69" s="109"/>
-      <c r="J69" s="109"/>
-      <c r="K69" s="109"/>
-      <c r="L69" s="109"/>
-      <c r="M69" s="109"/>
-      <c r="N69" s="109"/>
-      <c r="O69" s="110"/>
-      <c r="P69" s="21"/>
-      <c r="Q69" s="21"/>
-      <c r="R69" s="21"/>
-      <c r="S69" s="21"/>
-      <c r="T69" s="21"/>
-      <c r="U69" s="21"/>
-      <c r="V69" s="21"/>
-      <c r="W69" s="21"/>
-      <c r="X69" s="21"/>
-      <c r="Y69" s="21"/>
-      <c r="Z69" s="21"/>
-      <c r="AA69" s="21"/>
-      <c r="AB69" s="21"/>
-      <c r="AC69" s="21"/>
-      <c r="AD69" s="21"/>
-      <c r="AE69" s="21"/>
-      <c r="AF69" s="21"/>
-      <c r="AG69" s="21"/>
-      <c r="AH69" s="21"/>
-      <c r="AI69" s="21"/>
-      <c r="AJ69" s="21"/>
-      <c r="AK69" s="21"/>
-      <c r="AL69" s="21"/>
-      <c r="AM69" s="21"/>
-      <c r="AN69" s="21"/>
-      <c r="AO69" s="21"/>
-      <c r="AP69" s="21"/>
-      <c r="AQ69" s="21"/>
-      <c r="AR69" s="21"/>
-      <c r="AS69" s="21"/>
-      <c r="AT69" s="21"/>
-      <c r="AU69" s="21"/>
-      <c r="AV69" s="21"/>
-      <c r="AW69" s="21"/>
-      <c r="AX69" s="21"/>
-      <c r="AY69" s="21"/>
-      <c r="AZ69" s="21"/>
-      <c r="BA69" s="21"/>
-      <c r="BB69" s="21"/>
-      <c r="BC69" s="21"/>
-      <c r="BD69" s="21"/>
-      <c r="BE69" s="21"/>
-      <c r="BF69" s="21"/>
-      <c r="BG69" s="21"/>
-      <c r="BH69" s="21"/>
-      <c r="BI69" s="21"/>
-      <c r="BJ69" s="21"/>
-      <c r="BK69" s="21"/>
-      <c r="BL69" s="21"/>
-      <c r="BM69" s="21"/>
-      <c r="BN69" s="21"/>
-    </row>
-    <row r="70" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="107" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" s="107"/>
-      <c r="C70" s="107"/>
-      <c r="D70" s="107"/>
-      <c r="E70" s="107"/>
-      <c r="F70" s="107"/>
-      <c r="G70" s="107"/>
-      <c r="H70" s="107"/>
-      <c r="I70" s="107"/>
-      <c r="J70" s="107"/>
-      <c r="K70" s="107"/>
-      <c r="L70" s="107"/>
-      <c r="M70" s="107"/>
-      <c r="N70" s="107"/>
-      <c r="O70" s="107"/>
+      <c r="B70" s="108"/>
+      <c r="C70" s="108"/>
+      <c r="D70" s="108"/>
+      <c r="E70" s="108"/>
+      <c r="F70" s="108"/>
+      <c r="G70" s="108"/>
+      <c r="H70" s="108"/>
+      <c r="I70" s="108"/>
+      <c r="J70" s="108"/>
+      <c r="K70" s="108"/>
+      <c r="L70" s="108"/>
+      <c r="M70" s="108"/>
+      <c r="N70" s="108"/>
+      <c r="O70" s="109"/>
       <c r="P70" s="21"/>
       <c r="Q70" s="21"/>
       <c r="R70" s="21"/>
@@ -27506,52 +27487,24 @@
       <c r="BM70" s="21"/>
       <c r="BN70" s="21"/>
     </row>
-    <row r="71" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="92">
-        <v>148</v>
-      </c>
-      <c r="B71" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C71" s="93" t="s">
-        <v>253</v>
-      </c>
-      <c r="D71" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="F71" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="G71" s="92">
-        <v>403</v>
-      </c>
-      <c r="H71" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="I71" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J71" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K71" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L71" s="92">
-        <v>1111</v>
-      </c>
-      <c r="M71" s="93" t="s">
-        <v>252</v>
-      </c>
-      <c r="N71" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O71" s="30" t="s">
-        <v>59</v>
-      </c>
+    <row r="71" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="106" t="s">
+        <v>146</v>
+      </c>
+      <c r="B71" s="106"/>
+      <c r="C71" s="106"/>
+      <c r="D71" s="106"/>
+      <c r="E71" s="106"/>
+      <c r="F71" s="106"/>
+      <c r="G71" s="106"/>
+      <c r="H71" s="106"/>
+      <c r="I71" s="106"/>
+      <c r="J71" s="106"/>
+      <c r="K71" s="106"/>
+      <c r="L71" s="106"/>
+      <c r="M71" s="106"/>
+      <c r="N71" s="106"/>
+      <c r="O71" s="106"/>
       <c r="P71" s="21"/>
       <c r="Q71" s="21"/>
       <c r="R71" s="21"/>
@@ -27604,15 +27557,15 @@
       <c r="BM71" s="21"/>
       <c r="BN71" s="21"/>
     </row>
-    <row r="72" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A72" s="92">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B72" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C72" s="93" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D72" s="92" t="s">
         <v>12</v>
@@ -27639,16 +27592,16 @@
         <v>32</v>
       </c>
       <c r="L72" s="92">
-        <v>1016</v>
+        <v>1111</v>
       </c>
       <c r="M72" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N72" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O72" s="93" t="s">
-        <v>12</v>
+        <v>252</v>
+      </c>
+      <c r="N72" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O72" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="P72" s="21"/>
       <c r="Q72" s="21"/>
@@ -27702,50 +27655,50 @@
       <c r="BM72" s="21"/>
       <c r="BN72" s="21"/>
     </row>
-    <row r="73" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A73" s="4">
-        <v>52</v>
+    <row r="73" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="92">
+        <v>146</v>
       </c>
       <c r="B73" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D73" s="4" t="s">
+      <c r="C73" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D73" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="24">
-        <v>401</v>
-      </c>
-      <c r="H73" s="58" t="s">
+      <c r="G73" s="92">
+        <v>403</v>
+      </c>
+      <c r="H73" s="92" t="s">
         <v>216</v>
       </c>
       <c r="I73" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J73" s="4" t="s">
+      <c r="J73" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K73" s="4" t="s">
+      <c r="K73" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L73" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M73" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N73" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="O73" s="49" t="s">
+      <c r="L73" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M73" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N73" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O73" s="93" t="s">
         <v>12</v>
       </c>
       <c r="P73" s="21"/>
@@ -27800,160 +27753,160 @@
       <c r="BM73" s="21"/>
       <c r="BN73" s="21"/>
     </row>
-    <row r="74" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A74" s="92">
-        <v>53</v>
-      </c>
-      <c r="B74" s="104" t="s">
+    <row r="74" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>52</v>
+      </c>
+      <c r="B74" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C74" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="D74" s="92" t="s">
+      <c r="C74" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="92" t="s">
+      <c r="E74" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F74" s="92" t="s">
+      <c r="F74" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="74">
+      <c r="G74" s="24">
         <v>401</v>
       </c>
       <c r="H74" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I74" s="74" t="s">
+      <c r="I74" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J74" s="92" t="s">
+      <c r="J74" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K74" s="92" t="s">
+      <c r="K74" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L74" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M74" s="103" t="s">
+      <c r="L74" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M74" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N74" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O74" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="P74" s="21"/>
+      <c r="Q74" s="21"/>
+      <c r="R74" s="21"/>
+      <c r="S74" s="21"/>
+      <c r="T74" s="21"/>
+      <c r="U74" s="21"/>
+      <c r="V74" s="21"/>
+      <c r="W74" s="21"/>
+      <c r="X74" s="21"/>
+      <c r="Y74" s="21"/>
+      <c r="Z74" s="21"/>
+      <c r="AA74" s="21"/>
+      <c r="AB74" s="21"/>
+      <c r="AC74" s="21"/>
+      <c r="AD74" s="21"/>
+      <c r="AE74" s="21"/>
+      <c r="AF74" s="21"/>
+      <c r="AG74" s="21"/>
+      <c r="AH74" s="21"/>
+      <c r="AI74" s="21"/>
+      <c r="AJ74" s="21"/>
+      <c r="AK74" s="21"/>
+      <c r="AL74" s="21"/>
+      <c r="AM74" s="21"/>
+      <c r="AN74" s="21"/>
+      <c r="AO74" s="21"/>
+      <c r="AP74" s="21"/>
+      <c r="AQ74" s="21"/>
+      <c r="AR74" s="21"/>
+      <c r="AS74" s="21"/>
+      <c r="AT74" s="21"/>
+      <c r="AU74" s="21"/>
+      <c r="AV74" s="21"/>
+      <c r="AW74" s="21"/>
+      <c r="AX74" s="21"/>
+      <c r="AY74" s="21"/>
+      <c r="AZ74" s="21"/>
+      <c r="BA74" s="21"/>
+      <c r="BB74" s="21"/>
+      <c r="BC74" s="21"/>
+      <c r="BD74" s="21"/>
+      <c r="BE74" s="21"/>
+      <c r="BF74" s="21"/>
+      <c r="BG74" s="21"/>
+      <c r="BH74" s="21"/>
+      <c r="BI74" s="21"/>
+      <c r="BJ74" s="21"/>
+      <c r="BK74" s="21"/>
+      <c r="BL74" s="21"/>
+      <c r="BM74" s="21"/>
+      <c r="BN74" s="21"/>
+    </row>
+    <row r="75" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A75" s="92">
+        <v>53</v>
+      </c>
+      <c r="B75" s="103" t="s">
+        <v>99</v>
+      </c>
+      <c r="C75" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="N74" s="102" t="s">
+      <c r="D75" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="O74" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A75" s="4">
-        <v>55</v>
-      </c>
-      <c r="B75" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="24">
-        <v>400</v>
+      <c r="G75" s="74">
+        <v>401</v>
       </c>
       <c r="H75" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I75" s="24" t="s">
+      <c r="I75" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J75" s="24" t="s">
+      <c r="J75" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K75" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L75" s="24">
-        <v>1003</v>
-      </c>
-      <c r="M75" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="N75" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O75" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="T75" s="22"/>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-      <c r="X75" s="22"/>
-      <c r="Y75" s="22"/>
-      <c r="Z75" s="22"/>
-      <c r="AA75" s="22"/>
-      <c r="AB75" s="22"/>
-      <c r="AC75" s="22"/>
-      <c r="AD75" s="22"/>
-      <c r="AE75" s="22"/>
-      <c r="AF75" s="22"/>
-      <c r="AG75" s="22"/>
-      <c r="AH75" s="22"/>
-      <c r="AI75" s="22"/>
-      <c r="AJ75" s="22"/>
-      <c r="AK75" s="22"/>
-      <c r="AL75" s="22"/>
-      <c r="AM75" s="22"/>
-      <c r="AN75" s="22"/>
-      <c r="AO75" s="22"/>
-      <c r="AP75" s="22"/>
-      <c r="AQ75" s="22"/>
-      <c r="AR75" s="22"/>
-      <c r="AS75" s="22"/>
-      <c r="AT75" s="22"/>
-      <c r="AU75" s="22"/>
-      <c r="AV75" s="22"/>
-      <c r="AW75" s="22"/>
-      <c r="AX75" s="22"/>
-      <c r="AY75" s="22"/>
-      <c r="AZ75" s="22"/>
-      <c r="BA75" s="22"/>
-      <c r="BB75" s="22"/>
-      <c r="BC75" s="22"/>
-      <c r="BD75" s="22"/>
-      <c r="BE75" s="22"/>
-      <c r="BF75" s="22"/>
-      <c r="BG75" s="22"/>
-      <c r="BH75" s="22"/>
-      <c r="BI75" s="22"/>
-      <c r="BJ75" s="22"/>
-      <c r="BK75" s="22"/>
-      <c r="BL75" s="22"/>
-      <c r="BM75" s="22"/>
-      <c r="BN75" s="22"/>
-    </row>
-    <row r="76" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K75" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L75" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M75" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="N75" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="O75" s="93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B76" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>86</v>
+        <v>264</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>12</v>
@@ -27977,13 +27930,13 @@
         <v>7</v>
       </c>
       <c r="K76" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="L76" s="25">
-        <v>1004</v>
+        <v>30</v>
+      </c>
+      <c r="L76" s="24">
+        <v>1003</v>
       </c>
       <c r="M76" s="32" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N76" s="30" t="s">
         <v>60</v>
@@ -28043,26 +27996,26 @@
       <c r="BM76" s="22"/>
       <c r="BN76" s="22"/>
     </row>
-    <row r="77" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="B77" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C77" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D77" s="53" t="s">
+      <c r="C77" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E77" s="53" t="s">
+      <c r="E77" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="53" t="s">
+      <c r="F77" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="54">
+      <c r="G77" s="24">
         <v>400</v>
       </c>
       <c r="H77" s="58" t="s">
@@ -28071,46 +28024,97 @@
       <c r="I77" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J77" s="53" t="s">
+      <c r="J77" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K77" s="54" t="s">
+      <c r="K77" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L77" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M77" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N77" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O77" s="63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="L77" s="25">
+        <v>1004</v>
+      </c>
+      <c r="M77" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="N77" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O77" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
+      <c r="R77" s="22"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
+      <c r="U77" s="22"/>
+      <c r="V77" s="22"/>
+      <c r="W77" s="22"/>
+      <c r="X77" s="22"/>
+      <c r="Y77" s="22"/>
+      <c r="Z77" s="22"/>
+      <c r="AA77" s="22"/>
+      <c r="AB77" s="22"/>
+      <c r="AC77" s="22"/>
+      <c r="AD77" s="22"/>
+      <c r="AE77" s="22"/>
+      <c r="AF77" s="22"/>
+      <c r="AG77" s="22"/>
+      <c r="AH77" s="22"/>
+      <c r="AI77" s="22"/>
+      <c r="AJ77" s="22"/>
+      <c r="AK77" s="22"/>
+      <c r="AL77" s="22"/>
+      <c r="AM77" s="22"/>
+      <c r="AN77" s="22"/>
+      <c r="AO77" s="22"/>
+      <c r="AP77" s="22"/>
+      <c r="AQ77" s="22"/>
+      <c r="AR77" s="22"/>
+      <c r="AS77" s="22"/>
+      <c r="AT77" s="22"/>
+      <c r="AU77" s="22"/>
+      <c r="AV77" s="22"/>
+      <c r="AW77" s="22"/>
+      <c r="AX77" s="22"/>
+      <c r="AY77" s="22"/>
+      <c r="AZ77" s="22"/>
+      <c r="BA77" s="22"/>
+      <c r="BB77" s="22"/>
+      <c r="BC77" s="22"/>
+      <c r="BD77" s="22"/>
+      <c r="BE77" s="22"/>
+      <c r="BF77" s="22"/>
+      <c r="BG77" s="22"/>
+      <c r="BH77" s="22"/>
+      <c r="BI77" s="22"/>
+      <c r="BJ77" s="22"/>
+      <c r="BK77" s="22"/>
+      <c r="BL77" s="22"/>
+      <c r="BM77" s="22"/>
+      <c r="BN77" s="22"/>
+    </row>
+    <row r="78" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="B78" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C78" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D78" s="4" t="s">
+      <c r="C78" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D78" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F78" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="24">
-        <v>403</v>
+      <c r="G78" s="54">
+        <v>400</v>
       </c>
       <c r="H78" s="58" t="s">
         <v>216</v>
@@ -28118,85 +28122,34 @@
       <c r="I78" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J78" s="24" t="s">
+      <c r="J78" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K78" s="24" t="s">
+      <c r="K78" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L78" s="25">
-        <v>1006</v>
-      </c>
-      <c r="M78" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="N78" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O78" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="P78" s="22"/>
-      <c r="Q78" s="22"/>
-      <c r="R78" s="22"/>
-      <c r="S78" s="22"/>
-      <c r="T78" s="22"/>
-      <c r="U78" s="22"/>
-      <c r="V78" s="22"/>
-      <c r="W78" s="22"/>
-      <c r="X78" s="22"/>
-      <c r="Y78" s="22"/>
-      <c r="Z78" s="22"/>
-      <c r="AA78" s="22"/>
-      <c r="AB78" s="22"/>
-      <c r="AC78" s="22"/>
-      <c r="AD78" s="22"/>
-      <c r="AE78" s="22"/>
-      <c r="AF78" s="22"/>
-      <c r="AG78" s="22"/>
-      <c r="AH78" s="22"/>
-      <c r="AI78" s="22"/>
-      <c r="AJ78" s="22"/>
-      <c r="AK78" s="22"/>
-      <c r="AL78" s="22"/>
-      <c r="AM78" s="22"/>
-      <c r="AN78" s="22"/>
-      <c r="AO78" s="22"/>
-      <c r="AP78" s="22"/>
-      <c r="AQ78" s="22"/>
-      <c r="AR78" s="22"/>
-      <c r="AS78" s="22"/>
-      <c r="AT78" s="22"/>
-      <c r="AU78" s="22"/>
-      <c r="AV78" s="22"/>
-      <c r="AW78" s="22"/>
-      <c r="AX78" s="22"/>
-      <c r="AY78" s="22"/>
-      <c r="AZ78" s="22"/>
-      <c r="BA78" s="22"/>
-      <c r="BB78" s="22"/>
-      <c r="BC78" s="22"/>
-      <c r="BD78" s="22"/>
-      <c r="BE78" s="22"/>
-      <c r="BF78" s="22"/>
-      <c r="BG78" s="22"/>
-      <c r="BH78" s="22"/>
-      <c r="BI78" s="22"/>
-      <c r="BJ78" s="22"/>
-      <c r="BK78" s="22"/>
-      <c r="BL78" s="22"/>
-      <c r="BM78" s="22"/>
-      <c r="BN78" s="22"/>
+      <c r="L78" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M78" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N78" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O78" s="63" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="79" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B79" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>12</v>
@@ -28220,13 +28173,13 @@
         <v>7</v>
       </c>
       <c r="K79" s="24" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L79" s="25">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="M79" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N79" s="30" t="s">
         <v>60</v>
@@ -28288,13 +28241,13 @@
     </row>
     <row r="80" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B80" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>12</v>
@@ -28321,10 +28274,10 @@
         <v>30</v>
       </c>
       <c r="L80" s="25">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M80" s="32" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N80" s="30" t="s">
         <v>60</v>
@@ -28384,27 +28337,29 @@
       <c r="BM80" s="22"/>
       <c r="BN80" s="22"/>
     </row>
-    <row r="81" spans="1:66" ht="21" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A81" s="4"/>
+    <row r="81" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>59</v>
+      </c>
       <c r="B81" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="D81" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E81" s="24" t="s">
+      <c r="E81" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F81" s="24" t="s">
+      <c r="F81" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G81" s="44">
+      <c r="G81" s="24">
         <v>403</v>
       </c>
-      <c r="H81" s="24" t="s">
+      <c r="H81" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I81" s="24" t="s">
@@ -28414,44 +28369,93 @@
         <v>7</v>
       </c>
       <c r="K81" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L81" s="24">
-        <v>1011</v>
+        <v>30</v>
+      </c>
+      <c r="L81" s="25">
+        <v>1008</v>
       </c>
       <c r="M81" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="N81" s="32" t="s">
-        <v>55</v>
+        <v>16</v>
+      </c>
+      <c r="N81" s="30" t="s">
+        <v>60</v>
       </c>
       <c r="O81" s="30" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="82" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A82" s="4">
-        <v>60</v>
-      </c>
+      <c r="P81" s="22"/>
+      <c r="Q81" s="22"/>
+      <c r="R81" s="22"/>
+      <c r="S81" s="22"/>
+      <c r="T81" s="22"/>
+      <c r="U81" s="22"/>
+      <c r="V81" s="22"/>
+      <c r="W81" s="22"/>
+      <c r="X81" s="22"/>
+      <c r="Y81" s="22"/>
+      <c r="Z81" s="22"/>
+      <c r="AA81" s="22"/>
+      <c r="AB81" s="22"/>
+      <c r="AC81" s="22"/>
+      <c r="AD81" s="22"/>
+      <c r="AE81" s="22"/>
+      <c r="AF81" s="22"/>
+      <c r="AG81" s="22"/>
+      <c r="AH81" s="22"/>
+      <c r="AI81" s="22"/>
+      <c r="AJ81" s="22"/>
+      <c r="AK81" s="22"/>
+      <c r="AL81" s="22"/>
+      <c r="AM81" s="22"/>
+      <c r="AN81" s="22"/>
+      <c r="AO81" s="22"/>
+      <c r="AP81" s="22"/>
+      <c r="AQ81" s="22"/>
+      <c r="AR81" s="22"/>
+      <c r="AS81" s="22"/>
+      <c r="AT81" s="22"/>
+      <c r="AU81" s="22"/>
+      <c r="AV81" s="22"/>
+      <c r="AW81" s="22"/>
+      <c r="AX81" s="22"/>
+      <c r="AY81" s="22"/>
+      <c r="AZ81" s="22"/>
+      <c r="BA81" s="22"/>
+      <c r="BB81" s="22"/>
+      <c r="BC81" s="22"/>
+      <c r="BD81" s="22"/>
+      <c r="BE81" s="22"/>
+      <c r="BF81" s="22"/>
+      <c r="BG81" s="22"/>
+      <c r="BH81" s="22"/>
+      <c r="BI81" s="22"/>
+      <c r="BJ81" s="22"/>
+      <c r="BK81" s="22"/>
+      <c r="BL81" s="22"/>
+      <c r="BM81" s="22"/>
+      <c r="BN81" s="22"/>
+    </row>
+    <row r="82" spans="1:66" ht="21" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A82" s="4"/>
       <c r="B82" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>203</v>
+        <v>295</v>
       </c>
       <c r="D82" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E82" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G82" s="24">
+      <c r="G82" s="44">
         <v>403</v>
       </c>
-      <c r="H82" s="58" t="s">
+      <c r="H82" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I82" s="24" t="s">
@@ -28469,75 +28473,24 @@
       <c r="M82" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N82" s="30" t="s">
-        <v>60</v>
+      <c r="N82" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O82" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="P82" s="22"/>
-      <c r="Q82" s="22"/>
-      <c r="R82" s="22"/>
-      <c r="S82" s="22"/>
-      <c r="T82" s="22"/>
-      <c r="U82" s="22"/>
-      <c r="V82" s="22"/>
-      <c r="W82" s="22"/>
-      <c r="X82" s="22"/>
-      <c r="Y82" s="22"/>
-      <c r="Z82" s="22"/>
-      <c r="AA82" s="22"/>
-      <c r="AB82" s="22"/>
-      <c r="AC82" s="22"/>
-      <c r="AD82" s="22"/>
-      <c r="AE82" s="22"/>
-      <c r="AF82" s="22"/>
-      <c r="AG82" s="22"/>
-      <c r="AH82" s="22"/>
-      <c r="AI82" s="22"/>
-      <c r="AJ82" s="22"/>
-      <c r="AK82" s="22"/>
-      <c r="AL82" s="22"/>
-      <c r="AM82" s="22"/>
-      <c r="AN82" s="22"/>
-      <c r="AO82" s="22"/>
-      <c r="AP82" s="22"/>
-      <c r="AQ82" s="22"/>
-      <c r="AR82" s="22"/>
-      <c r="AS82" s="22"/>
-      <c r="AT82" s="22"/>
-      <c r="AU82" s="22"/>
-      <c r="AV82" s="22"/>
-      <c r="AW82" s="22"/>
-      <c r="AX82" s="22"/>
-      <c r="AY82" s="22"/>
-      <c r="AZ82" s="22"/>
-      <c r="BA82" s="22"/>
-      <c r="BB82" s="22"/>
-      <c r="BC82" s="22"/>
-      <c r="BD82" s="22"/>
-      <c r="BE82" s="22"/>
-      <c r="BF82" s="22"/>
-      <c r="BG82" s="22"/>
-      <c r="BH82" s="22"/>
-      <c r="BI82" s="22"/>
-      <c r="BJ82" s="22"/>
-      <c r="BK82" s="22"/>
-      <c r="BL82" s="22"/>
-      <c r="BM82" s="22"/>
-      <c r="BN82" s="22"/>
+        <v>59</v>
+      </c>
     </row>
     <row r="83" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B83" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D83" s="24" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="4" t="s">
@@ -28547,7 +28500,7 @@
         <v>140</v>
       </c>
       <c r="G83" s="24">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H83" s="58" t="s">
         <v>216</v>
@@ -28555,23 +28508,23 @@
       <c r="I83" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J83" s="4" t="s">
+      <c r="J83" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K83" s="4" t="s">
+      <c r="K83" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="L83" s="4">
-        <v>2501</v>
-      </c>
-      <c r="M83" s="30" t="s">
-        <v>40</v>
+      <c r="L83" s="24">
+        <v>1011</v>
+      </c>
+      <c r="M83" s="32" t="s">
+        <v>202</v>
       </c>
       <c r="N83" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O83" s="30" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="P83" s="22"/>
       <c r="Q83" s="22"/>
@@ -28625,141 +28578,169 @@
       <c r="BM83" s="22"/>
       <c r="BN83" s="22"/>
     </row>
-    <row r="84" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="8">
-        <v>166</v>
+    <row r="84" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>61</v>
       </c>
       <c r="B84" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C84" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="D84" s="58" t="s">
+      <c r="C84" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F84" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G84" s="8">
-        <v>401</v>
-      </c>
-      <c r="H84" s="54" t="s">
+      <c r="G84" s="24">
+        <v>404</v>
+      </c>
+      <c r="H84" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I84" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J84" s="92" t="s">
+      <c r="J84" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K84" s="92" t="s">
+      <c r="K84" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L84" s="8">
+      <c r="L84" s="4">
+        <v>2501</v>
+      </c>
+      <c r="M84" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="N84" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="O84" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="T84" s="22"/>
+      <c r="U84" s="22"/>
+      <c r="V84" s="22"/>
+      <c r="W84" s="22"/>
+      <c r="X84" s="22"/>
+      <c r="Y84" s="22"/>
+      <c r="Z84" s="22"/>
+      <c r="AA84" s="22"/>
+      <c r="AB84" s="22"/>
+      <c r="AC84" s="22"/>
+      <c r="AD84" s="22"/>
+      <c r="AE84" s="22"/>
+      <c r="AF84" s="22"/>
+      <c r="AG84" s="22"/>
+      <c r="AH84" s="22"/>
+      <c r="AI84" s="22"/>
+      <c r="AJ84" s="22"/>
+      <c r="AK84" s="22"/>
+      <c r="AL84" s="22"/>
+      <c r="AM84" s="22"/>
+      <c r="AN84" s="22"/>
+      <c r="AO84" s="22"/>
+      <c r="AP84" s="22"/>
+      <c r="AQ84" s="22"/>
+      <c r="AR84" s="22"/>
+      <c r="AS84" s="22"/>
+      <c r="AT84" s="22"/>
+      <c r="AU84" s="22"/>
+      <c r="AV84" s="22"/>
+      <c r="AW84" s="22"/>
+      <c r="AX84" s="22"/>
+      <c r="AY84" s="22"/>
+      <c r="AZ84" s="22"/>
+      <c r="BA84" s="22"/>
+      <c r="BB84" s="22"/>
+      <c r="BC84" s="22"/>
+      <c r="BD84" s="22"/>
+      <c r="BE84" s="22"/>
+      <c r="BF84" s="22"/>
+      <c r="BG84" s="22"/>
+      <c r="BH84" s="22"/>
+      <c r="BI84" s="22"/>
+      <c r="BJ84" s="22"/>
+      <c r="BK84" s="22"/>
+      <c r="BL84" s="22"/>
+      <c r="BM84" s="22"/>
+      <c r="BN84" s="22"/>
+    </row>
+    <row r="85" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>166</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G85" s="8">
+        <v>401</v>
+      </c>
+      <c r="H85" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="I85" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J85" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K85" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L85" s="8">
         <v>1014</v>
       </c>
-      <c r="M84" s="31" t="s">
+      <c r="M85" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="N84" s="64" t="s">
+      <c r="N85" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O84" s="64" t="s">
+      <c r="O85" s="64" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="106" t="s">
+    <row r="86" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="B85" s="106"/>
-      <c r="C85" s="106"/>
-      <c r="D85" s="106"/>
-      <c r="E85" s="106"/>
-      <c r="F85" s="106"/>
-      <c r="G85" s="106"/>
-      <c r="H85" s="106"/>
-      <c r="I85" s="106"/>
-      <c r="J85" s="106"/>
-      <c r="K85" s="106"/>
-      <c r="L85" s="106"/>
-      <c r="M85" s="106"/>
-      <c r="N85" s="106"/>
-      <c r="O85" s="106"/>
-      <c r="P85" s="21"/>
-      <c r="Q85" s="21"/>
-      <c r="R85" s="21"/>
-      <c r="S85" s="21"/>
-      <c r="T85" s="21"/>
-      <c r="U85" s="21"/>
-      <c r="V85" s="21"/>
-      <c r="W85" s="21"/>
-      <c r="X85" s="21"/>
-      <c r="Y85" s="21"/>
-      <c r="Z85" s="21"/>
-      <c r="AA85" s="21"/>
-      <c r="AB85" s="21"/>
-      <c r="AC85" s="21"/>
-      <c r="AD85" s="21"/>
-      <c r="AE85" s="21"/>
-      <c r="AF85" s="21"/>
-      <c r="AG85" s="21"/>
-      <c r="AH85" s="21"/>
-      <c r="AI85" s="21"/>
-      <c r="AJ85" s="21"/>
-      <c r="AK85" s="21"/>
-      <c r="AL85" s="21"/>
-      <c r="AM85" s="21"/>
-      <c r="AN85" s="21"/>
-      <c r="AO85" s="21"/>
-      <c r="AP85" s="21"/>
-      <c r="AQ85" s="21"/>
-      <c r="AR85" s="21"/>
-      <c r="AS85" s="21"/>
-      <c r="AT85" s="21"/>
-      <c r="AU85" s="21"/>
-      <c r="AV85" s="21"/>
-      <c r="AW85" s="21"/>
-      <c r="AX85" s="21"/>
-      <c r="AY85" s="21"/>
-      <c r="AZ85" s="21"/>
-      <c r="BA85" s="21"/>
-      <c r="BB85" s="21"/>
-      <c r="BC85" s="21"/>
-      <c r="BD85" s="21"/>
-      <c r="BE85" s="21"/>
-      <c r="BF85" s="21"/>
-      <c r="BG85" s="21"/>
-      <c r="BH85" s="21"/>
-      <c r="BI85" s="21"/>
-      <c r="BJ85" s="21"/>
-      <c r="BK85" s="21"/>
-      <c r="BL85" s="21"/>
-      <c r="BM85" s="21"/>
-      <c r="BN85" s="21"/>
-    </row>
-    <row r="86" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="107" t="s">
-        <v>146</v>
-      </c>
-      <c r="B86" s="107"/>
-      <c r="C86" s="107"/>
-      <c r="D86" s="107"/>
-      <c r="E86" s="107"/>
-      <c r="F86" s="107"/>
-      <c r="G86" s="107"/>
-      <c r="H86" s="107"/>
-      <c r="I86" s="107"/>
-      <c r="J86" s="107"/>
-      <c r="K86" s="107"/>
-      <c r="L86" s="107"/>
-      <c r="M86" s="107"/>
-      <c r="N86" s="107"/>
-      <c r="O86" s="107"/>
+      <c r="B86" s="105"/>
+      <c r="C86" s="105"/>
+      <c r="D86" s="105"/>
+      <c r="E86" s="105"/>
+      <c r="F86" s="105"/>
+      <c r="G86" s="105"/>
+      <c r="H86" s="105"/>
+      <c r="I86" s="105"/>
+      <c r="J86" s="105"/>
+      <c r="K86" s="105"/>
+      <c r="L86" s="105"/>
+      <c r="M86" s="105"/>
+      <c r="N86" s="105"/>
+      <c r="O86" s="105"/>
       <c r="P86" s="21"/>
       <c r="Q86" s="21"/>
       <c r="R86" s="21"/>
@@ -28812,52 +28793,24 @@
       <c r="BM86" s="21"/>
       <c r="BN86" s="21"/>
     </row>
-    <row r="87" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="92">
-        <v>148</v>
-      </c>
-      <c r="B87" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C87" s="93" t="s">
-        <v>253</v>
-      </c>
-      <c r="D87" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E87" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="F87" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="G87" s="92">
-        <v>403</v>
-      </c>
-      <c r="H87" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="I87" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J87" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K87" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L87" s="92">
-        <v>1111</v>
-      </c>
-      <c r="M87" s="93" t="s">
-        <v>252</v>
-      </c>
-      <c r="N87" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O87" s="30" t="s">
-        <v>59</v>
-      </c>
+    <row r="87" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="106" t="s">
+        <v>146</v>
+      </c>
+      <c r="B87" s="106"/>
+      <c r="C87" s="106"/>
+      <c r="D87" s="106"/>
+      <c r="E87" s="106"/>
+      <c r="F87" s="106"/>
+      <c r="G87" s="106"/>
+      <c r="H87" s="106"/>
+      <c r="I87" s="106"/>
+      <c r="J87" s="106"/>
+      <c r="K87" s="106"/>
+      <c r="L87" s="106"/>
+      <c r="M87" s="106"/>
+      <c r="N87" s="106"/>
+      <c r="O87" s="106"/>
       <c r="P87" s="21"/>
       <c r="Q87" s="21"/>
       <c r="R87" s="21"/>
@@ -28910,15 +28863,15 @@
       <c r="BM87" s="21"/>
       <c r="BN87" s="21"/>
     </row>
-    <row r="88" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="92">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B88" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C88" s="93" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D88" s="92" t="s">
         <v>12</v>
@@ -28945,16 +28898,16 @@
         <v>32</v>
       </c>
       <c r="L88" s="92">
-        <v>1016</v>
+        <v>1111</v>
       </c>
       <c r="M88" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N88" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O88" s="93" t="s">
-        <v>12</v>
+        <v>252</v>
+      </c>
+      <c r="N88" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O88" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="P88" s="21"/>
       <c r="Q88" s="21"/>
@@ -29008,50 +28961,50 @@
       <c r="BM88" s="21"/>
       <c r="BN88" s="21"/>
     </row>
-    <row r="89" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A89" s="4">
-        <v>62</v>
+    <row r="89" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="92">
+        <v>146</v>
       </c>
       <c r="B89" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C89" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="D89" s="4" t="s">
+      <c r="C89" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D89" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E89" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G89" s="24">
-        <v>401</v>
-      </c>
-      <c r="H89" s="58" t="s">
+      <c r="G89" s="92">
+        <v>403</v>
+      </c>
+      <c r="H89" s="92" t="s">
         <v>216</v>
       </c>
       <c r="I89" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J89" s="4" t="s">
+      <c r="J89" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K89" s="4" t="s">
+      <c r="K89" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L89" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M89" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N89" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="O89" s="49" t="s">
+      <c r="L89" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M89" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N89" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O89" s="93" t="s">
         <v>12</v>
       </c>
       <c r="P89" s="21"/>
@@ -29106,160 +29059,160 @@
       <c r="BM89" s="21"/>
       <c r="BN89" s="21"/>
     </row>
-    <row r="90" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A90" s="92">
-        <v>63</v>
-      </c>
-      <c r="B90" s="104" t="s">
+    <row r="90" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>62</v>
+      </c>
+      <c r="B90" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C90" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="D90" s="92" t="s">
+      <c r="C90" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E90" s="92" t="s">
+      <c r="E90" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F90" s="92" t="s">
+      <c r="F90" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G90" s="74">
+      <c r="G90" s="24">
         <v>401</v>
       </c>
       <c r="H90" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I90" s="74" t="s">
+      <c r="I90" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J90" s="92" t="s">
+      <c r="J90" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K90" s="92" t="s">
+      <c r="K90" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L90" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M90" s="103" t="s">
+      <c r="L90" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M90" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N90" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O90" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="P90" s="21"/>
+      <c r="Q90" s="21"/>
+      <c r="R90" s="21"/>
+      <c r="S90" s="21"/>
+      <c r="T90" s="21"/>
+      <c r="U90" s="21"/>
+      <c r="V90" s="21"/>
+      <c r="W90" s="21"/>
+      <c r="X90" s="21"/>
+      <c r="Y90" s="21"/>
+      <c r="Z90" s="21"/>
+      <c r="AA90" s="21"/>
+      <c r="AB90" s="21"/>
+      <c r="AC90" s="21"/>
+      <c r="AD90" s="21"/>
+      <c r="AE90" s="21"/>
+      <c r="AF90" s="21"/>
+      <c r="AG90" s="21"/>
+      <c r="AH90" s="21"/>
+      <c r="AI90" s="21"/>
+      <c r="AJ90" s="21"/>
+      <c r="AK90" s="21"/>
+      <c r="AL90" s="21"/>
+      <c r="AM90" s="21"/>
+      <c r="AN90" s="21"/>
+      <c r="AO90" s="21"/>
+      <c r="AP90" s="21"/>
+      <c r="AQ90" s="21"/>
+      <c r="AR90" s="21"/>
+      <c r="AS90" s="21"/>
+      <c r="AT90" s="21"/>
+      <c r="AU90" s="21"/>
+      <c r="AV90" s="21"/>
+      <c r="AW90" s="21"/>
+      <c r="AX90" s="21"/>
+      <c r="AY90" s="21"/>
+      <c r="AZ90" s="21"/>
+      <c r="BA90" s="21"/>
+      <c r="BB90" s="21"/>
+      <c r="BC90" s="21"/>
+      <c r="BD90" s="21"/>
+      <c r="BE90" s="21"/>
+      <c r="BF90" s="21"/>
+      <c r="BG90" s="21"/>
+      <c r="BH90" s="21"/>
+      <c r="BI90" s="21"/>
+      <c r="BJ90" s="21"/>
+      <c r="BK90" s="21"/>
+      <c r="BL90" s="21"/>
+      <c r="BM90" s="21"/>
+      <c r="BN90" s="21"/>
+    </row>
+    <row r="91" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A91" s="92">
+        <v>63</v>
+      </c>
+      <c r="B91" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="N90" s="102" t="s">
+      <c r="D91" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="O90" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A91" s="4">
-        <v>65</v>
-      </c>
-      <c r="B91" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C91" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E91" s="4" t="s">
+      <c r="E91" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G91" s="24">
-        <v>400</v>
+      <c r="G91" s="74">
+        <v>401</v>
       </c>
       <c r="H91" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I91" s="24" t="s">
+      <c r="I91" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J91" s="25" t="s">
+      <c r="J91" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K91" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L91" s="25">
-        <v>1003</v>
-      </c>
-      <c r="M91" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="N91" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O91" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P91" s="22"/>
-      <c r="Q91" s="22"/>
-      <c r="R91" s="22"/>
-      <c r="S91" s="22"/>
-      <c r="T91" s="22"/>
-      <c r="U91" s="22"/>
-      <c r="V91" s="22"/>
-      <c r="W91" s="22"/>
-      <c r="X91" s="22"/>
-      <c r="Y91" s="22"/>
-      <c r="Z91" s="22"/>
-      <c r="AA91" s="22"/>
-      <c r="AB91" s="22"/>
-      <c r="AC91" s="22"/>
-      <c r="AD91" s="22"/>
-      <c r="AE91" s="22"/>
-      <c r="AF91" s="22"/>
-      <c r="AG91" s="22"/>
-      <c r="AH91" s="22"/>
-      <c r="AI91" s="22"/>
-      <c r="AJ91" s="22"/>
-      <c r="AK91" s="22"/>
-      <c r="AL91" s="22"/>
-      <c r="AM91" s="22"/>
-      <c r="AN91" s="22"/>
-      <c r="AO91" s="22"/>
-      <c r="AP91" s="22"/>
-      <c r="AQ91" s="22"/>
-      <c r="AR91" s="22"/>
-      <c r="AS91" s="22"/>
-      <c r="AT91" s="22"/>
-      <c r="AU91" s="22"/>
-      <c r="AV91" s="22"/>
-      <c r="AW91" s="22"/>
-      <c r="AX91" s="22"/>
-      <c r="AY91" s="22"/>
-      <c r="AZ91" s="22"/>
-      <c r="BA91" s="22"/>
-      <c r="BB91" s="22"/>
-      <c r="BC91" s="22"/>
-      <c r="BD91" s="22"/>
-      <c r="BE91" s="22"/>
-      <c r="BF91" s="22"/>
-      <c r="BG91" s="22"/>
-      <c r="BH91" s="22"/>
-      <c r="BI91" s="22"/>
-      <c r="BJ91" s="22"/>
-      <c r="BK91" s="22"/>
-      <c r="BL91" s="22"/>
-      <c r="BM91" s="22"/>
-      <c r="BN91" s="22"/>
-    </row>
-    <row r="92" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K91" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L91" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M91" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="N91" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="O91" s="93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B92" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>86</v>
+        <v>264</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>12</v>
@@ -29279,22 +29232,22 @@
       <c r="I92" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J92" s="24" t="s">
+      <c r="J92" s="25" t="s">
         <v>7</v>
       </c>
       <c r="K92" s="24" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L92" s="25">
-        <v>1004</v>
-      </c>
-      <c r="M92" s="30" t="s">
-        <v>24</v>
+        <v>1003</v>
+      </c>
+      <c r="M92" s="47" t="s">
+        <v>14</v>
       </c>
       <c r="N92" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="O92" s="30" t="s">
+      <c r="O92" s="4" t="s">
         <v>43</v>
       </c>
       <c r="P92" s="22"/>
@@ -29349,26 +29302,26 @@
       <c r="BM92" s="22"/>
       <c r="BN92" s="22"/>
     </row>
-    <row r="93" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="B93" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C93" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D93" s="53" t="s">
+      <c r="C93" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E93" s="53" t="s">
+      <c r="E93" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F93" s="53" t="s">
+      <c r="F93" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G93" s="54">
+      <c r="G93" s="24">
         <v>400</v>
       </c>
       <c r="H93" s="58" t="s">
@@ -29377,46 +29330,97 @@
       <c r="I93" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J93" s="53" t="s">
+      <c r="J93" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K93" s="54" t="s">
+      <c r="K93" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L93" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M93" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N93" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O93" s="63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="L93" s="25">
+        <v>1004</v>
+      </c>
+      <c r="M93" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="N93" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O93" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P93" s="22"/>
+      <c r="Q93" s="22"/>
+      <c r="R93" s="22"/>
+      <c r="S93" s="22"/>
+      <c r="T93" s="22"/>
+      <c r="U93" s="22"/>
+      <c r="V93" s="22"/>
+      <c r="W93" s="22"/>
+      <c r="X93" s="22"/>
+      <c r="Y93" s="22"/>
+      <c r="Z93" s="22"/>
+      <c r="AA93" s="22"/>
+      <c r="AB93" s="22"/>
+      <c r="AC93" s="22"/>
+      <c r="AD93" s="22"/>
+      <c r="AE93" s="22"/>
+      <c r="AF93" s="22"/>
+      <c r="AG93" s="22"/>
+      <c r="AH93" s="22"/>
+      <c r="AI93" s="22"/>
+      <c r="AJ93" s="22"/>
+      <c r="AK93" s="22"/>
+      <c r="AL93" s="22"/>
+      <c r="AM93" s="22"/>
+      <c r="AN93" s="22"/>
+      <c r="AO93" s="22"/>
+      <c r="AP93" s="22"/>
+      <c r="AQ93" s="22"/>
+      <c r="AR93" s="22"/>
+      <c r="AS93" s="22"/>
+      <c r="AT93" s="22"/>
+      <c r="AU93" s="22"/>
+      <c r="AV93" s="22"/>
+      <c r="AW93" s="22"/>
+      <c r="AX93" s="22"/>
+      <c r="AY93" s="22"/>
+      <c r="AZ93" s="22"/>
+      <c r="BA93" s="22"/>
+      <c r="BB93" s="22"/>
+      <c r="BC93" s="22"/>
+      <c r="BD93" s="22"/>
+      <c r="BE93" s="22"/>
+      <c r="BF93" s="22"/>
+      <c r="BG93" s="22"/>
+      <c r="BH93" s="22"/>
+      <c r="BI93" s="22"/>
+      <c r="BJ93" s="22"/>
+      <c r="BK93" s="22"/>
+      <c r="BL93" s="22"/>
+      <c r="BM93" s="22"/>
+      <c r="BN93" s="22"/>
+    </row>
+    <row r="94" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="B94" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C94" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="C94" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D94" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="E94" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F94" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G94" s="24">
-        <v>403</v>
+      <c r="G94" s="54">
+        <v>400</v>
       </c>
       <c r="H94" s="58" t="s">
         <v>216</v>
@@ -29424,85 +29428,34 @@
       <c r="I94" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J94" s="24" t="s">
+      <c r="J94" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K94" s="24" t="s">
+      <c r="K94" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L94" s="25">
-        <v>1006</v>
-      </c>
-      <c r="M94" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="N94" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O94" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="P94" s="22"/>
-      <c r="Q94" s="22"/>
-      <c r="R94" s="22"/>
-      <c r="S94" s="22"/>
-      <c r="T94" s="22"/>
-      <c r="U94" s="22"/>
-      <c r="V94" s="22"/>
-      <c r="W94" s="22"/>
-      <c r="X94" s="22"/>
-      <c r="Y94" s="22"/>
-      <c r="Z94" s="22"/>
-      <c r="AA94" s="22"/>
-      <c r="AB94" s="22"/>
-      <c r="AC94" s="22"/>
-      <c r="AD94" s="22"/>
-      <c r="AE94" s="22"/>
-      <c r="AF94" s="22"/>
-      <c r="AG94" s="22"/>
-      <c r="AH94" s="22"/>
-      <c r="AI94" s="22"/>
-      <c r="AJ94" s="22"/>
-      <c r="AK94" s="22"/>
-      <c r="AL94" s="22"/>
-      <c r="AM94" s="22"/>
-      <c r="AN94" s="22"/>
-      <c r="AO94" s="22"/>
-      <c r="AP94" s="22"/>
-      <c r="AQ94" s="22"/>
-      <c r="AR94" s="22"/>
-      <c r="AS94" s="22"/>
-      <c r="AT94" s="22"/>
-      <c r="AU94" s="22"/>
-      <c r="AV94" s="22"/>
-      <c r="AW94" s="22"/>
-      <c r="AX94" s="22"/>
-      <c r="AY94" s="22"/>
-      <c r="AZ94" s="22"/>
-      <c r="BA94" s="22"/>
-      <c r="BB94" s="22"/>
-      <c r="BC94" s="22"/>
-      <c r="BD94" s="22"/>
-      <c r="BE94" s="22"/>
-      <c r="BF94" s="22"/>
-      <c r="BG94" s="22"/>
-      <c r="BH94" s="22"/>
-      <c r="BI94" s="22"/>
-      <c r="BJ94" s="22"/>
-      <c r="BK94" s="22"/>
-      <c r="BL94" s="22"/>
-      <c r="BM94" s="22"/>
-      <c r="BN94" s="22"/>
+      <c r="L94" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M94" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N94" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O94" s="63" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="95" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B95" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>12</v>
@@ -29526,13 +29479,13 @@
         <v>7</v>
       </c>
       <c r="K95" s="24" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L95" s="25">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="M95" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N95" s="30" t="s">
         <v>60</v>
@@ -29594,13 +29547,13 @@
     </row>
     <row r="96" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B96" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>12</v>
@@ -29627,10 +29580,10 @@
         <v>30</v>
       </c>
       <c r="L96" s="25">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M96" s="30" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N96" s="30" t="s">
         <v>60</v>
@@ -29690,27 +29643,29 @@
       <c r="BM96" s="22"/>
       <c r="BN96" s="22"/>
     </row>
-    <row r="97" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
+    <row r="97" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <v>69</v>
+      </c>
       <c r="B97" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="D97" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E97" s="24" t="s">
+      <c r="E97" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F97" s="24" t="s">
+      <c r="F97" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G97" s="44">
+      <c r="G97" s="24">
         <v>403</v>
       </c>
-      <c r="H97" s="24" t="s">
+      <c r="H97" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I97" s="24" t="s">
@@ -29720,16 +29675,16 @@
         <v>7</v>
       </c>
       <c r="K97" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L97" s="24">
-        <v>1011</v>
-      </c>
-      <c r="M97" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="N97" s="32" t="s">
-        <v>55</v>
+        <v>30</v>
+      </c>
+      <c r="L97" s="25">
+        <v>1008</v>
+      </c>
+      <c r="M97" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="N97" s="30" t="s">
+        <v>60</v>
       </c>
       <c r="O97" s="30" t="s">
         <v>59</v>
@@ -29786,29 +29741,27 @@
       <c r="BM97" s="22"/>
       <c r="BN97" s="22"/>
     </row>
-    <row r="98" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A98" s="4">
-        <v>70</v>
-      </c>
+    <row r="98" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A98" s="4"/>
       <c r="B98" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>203</v>
+        <v>295</v>
       </c>
       <c r="D98" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="E98" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="F98" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G98" s="24">
+      <c r="G98" s="44">
         <v>403</v>
       </c>
-      <c r="H98" s="58" t="s">
+      <c r="H98" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I98" s="24" t="s">
@@ -29826,11 +29779,11 @@
       <c r="M98" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N98" s="30" t="s">
-        <v>60</v>
+      <c r="N98" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O98" s="30" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="P98" s="22"/>
       <c r="Q98" s="22"/>
@@ -29886,15 +29839,15 @@
     </row>
     <row r="99" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B99" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D99" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D99" s="24" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="4" t="s">
@@ -29904,7 +29857,7 @@
         <v>140</v>
       </c>
       <c r="G99" s="24">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H99" s="58" t="s">
         <v>216</v>
@@ -29912,23 +29865,23 @@
       <c r="I99" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J99" s="4" t="s">
+      <c r="J99" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K99" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L99" s="10">
-        <v>2506</v>
-      </c>
-      <c r="M99" s="30" t="s">
-        <v>39</v>
+      <c r="K99" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L99" s="24">
+        <v>1011</v>
+      </c>
+      <c r="M99" s="32" t="s">
+        <v>202</v>
       </c>
       <c r="N99" s="30" t="s">
         <v>60</v>
       </c>
       <c r="O99" s="30" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="P99" s="22"/>
       <c r="Q99" s="22"/>
@@ -29982,141 +29935,169 @@
       <c r="BM99" s="22"/>
       <c r="BN99" s="22"/>
     </row>
-    <row r="100" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="8">
-        <v>167</v>
+    <row r="100" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A100" s="4">
+        <v>71</v>
       </c>
       <c r="B100" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="D100" s="58" t="s">
+      <c r="C100" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F100" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G100" s="8">
-        <v>401</v>
-      </c>
-      <c r="H100" s="54" t="s">
+      <c r="G100" s="24">
+        <v>404</v>
+      </c>
+      <c r="H100" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I100" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J100" s="92" t="s">
+      <c r="J100" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K100" s="92" t="s">
+      <c r="K100" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L100" s="10">
+        <v>2506</v>
+      </c>
+      <c r="M100" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="N100" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O100" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P100" s="22"/>
+      <c r="Q100" s="22"/>
+      <c r="R100" s="22"/>
+      <c r="S100" s="22"/>
+      <c r="T100" s="22"/>
+      <c r="U100" s="22"/>
+      <c r="V100" s="22"/>
+      <c r="W100" s="22"/>
+      <c r="X100" s="22"/>
+      <c r="Y100" s="22"/>
+      <c r="Z100" s="22"/>
+      <c r="AA100" s="22"/>
+      <c r="AB100" s="22"/>
+      <c r="AC100" s="22"/>
+      <c r="AD100" s="22"/>
+      <c r="AE100" s="22"/>
+      <c r="AF100" s="22"/>
+      <c r="AG100" s="22"/>
+      <c r="AH100" s="22"/>
+      <c r="AI100" s="22"/>
+      <c r="AJ100" s="22"/>
+      <c r="AK100" s="22"/>
+      <c r="AL100" s="22"/>
+      <c r="AM100" s="22"/>
+      <c r="AN100" s="22"/>
+      <c r="AO100" s="22"/>
+      <c r="AP100" s="22"/>
+      <c r="AQ100" s="22"/>
+      <c r="AR100" s="22"/>
+      <c r="AS100" s="22"/>
+      <c r="AT100" s="22"/>
+      <c r="AU100" s="22"/>
+      <c r="AV100" s="22"/>
+      <c r="AW100" s="22"/>
+      <c r="AX100" s="22"/>
+      <c r="AY100" s="22"/>
+      <c r="AZ100" s="22"/>
+      <c r="BA100" s="22"/>
+      <c r="BB100" s="22"/>
+      <c r="BC100" s="22"/>
+      <c r="BD100" s="22"/>
+      <c r="BE100" s="22"/>
+      <c r="BF100" s="22"/>
+      <c r="BG100" s="22"/>
+      <c r="BH100" s="22"/>
+      <c r="BI100" s="22"/>
+      <c r="BJ100" s="22"/>
+      <c r="BK100" s="22"/>
+      <c r="BL100" s="22"/>
+      <c r="BM100" s="22"/>
+      <c r="BN100" s="22"/>
+    </row>
+    <row r="101" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="8">
+        <v>167</v>
+      </c>
+      <c r="B101" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G101" s="8">
+        <v>401</v>
+      </c>
+      <c r="H101" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="I101" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J101" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K101" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L100" s="8">
+      <c r="L101" s="8">
         <v>1014</v>
       </c>
-      <c r="M100" s="31" t="s">
+      <c r="M101" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="N100" s="64" t="s">
+      <c r="N101" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O100" s="64" t="s">
+      <c r="O101" s="64" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="106" t="s">
+    <row r="102" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="105" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="106"/>
-      <c r="C101" s="106"/>
-      <c r="D101" s="106"/>
-      <c r="E101" s="106"/>
-      <c r="F101" s="106"/>
-      <c r="G101" s="106"/>
-      <c r="H101" s="106"/>
-      <c r="I101" s="106"/>
-      <c r="J101" s="106"/>
-      <c r="K101" s="106"/>
-      <c r="L101" s="106"/>
-      <c r="M101" s="106"/>
-      <c r="N101" s="106"/>
-      <c r="O101" s="106"/>
-      <c r="P101" s="21"/>
-      <c r="Q101" s="21"/>
-      <c r="R101" s="21"/>
-      <c r="S101" s="21"/>
-      <c r="T101" s="21"/>
-      <c r="U101" s="21"/>
-      <c r="V101" s="21"/>
-      <c r="W101" s="21"/>
-      <c r="X101" s="21"/>
-      <c r="Y101" s="21"/>
-      <c r="Z101" s="21"/>
-      <c r="AA101" s="21"/>
-      <c r="AB101" s="21"/>
-      <c r="AC101" s="21"/>
-      <c r="AD101" s="21"/>
-      <c r="AE101" s="21"/>
-      <c r="AF101" s="21"/>
-      <c r="AG101" s="21"/>
-      <c r="AH101" s="21"/>
-      <c r="AI101" s="21"/>
-      <c r="AJ101" s="21"/>
-      <c r="AK101" s="21"/>
-      <c r="AL101" s="21"/>
-      <c r="AM101" s="21"/>
-      <c r="AN101" s="21"/>
-      <c r="AO101" s="21"/>
-      <c r="AP101" s="21"/>
-      <c r="AQ101" s="21"/>
-      <c r="AR101" s="21"/>
-      <c r="AS101" s="21"/>
-      <c r="AT101" s="21"/>
-      <c r="AU101" s="21"/>
-      <c r="AV101" s="21"/>
-      <c r="AW101" s="21"/>
-      <c r="AX101" s="21"/>
-      <c r="AY101" s="21"/>
-      <c r="AZ101" s="21"/>
-      <c r="BA101" s="21"/>
-      <c r="BB101" s="21"/>
-      <c r="BC101" s="21"/>
-      <c r="BD101" s="21"/>
-      <c r="BE101" s="21"/>
-      <c r="BF101" s="21"/>
-      <c r="BG101" s="21"/>
-      <c r="BH101" s="21"/>
-      <c r="BI101" s="21"/>
-      <c r="BJ101" s="21"/>
-      <c r="BK101" s="21"/>
-      <c r="BL101" s="21"/>
-      <c r="BM101" s="21"/>
-      <c r="BN101" s="21"/>
-    </row>
-    <row r="102" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="107" t="s">
-        <v>146</v>
-      </c>
-      <c r="B102" s="107"/>
-      <c r="C102" s="107"/>
-      <c r="D102" s="107"/>
-      <c r="E102" s="107"/>
-      <c r="F102" s="107"/>
-      <c r="G102" s="107"/>
-      <c r="H102" s="107"/>
-      <c r="I102" s="107"/>
-      <c r="J102" s="107"/>
-      <c r="K102" s="107"/>
-      <c r="L102" s="107"/>
-      <c r="M102" s="107"/>
-      <c r="N102" s="107"/>
-      <c r="O102" s="107"/>
+      <c r="B102" s="105"/>
+      <c r="C102" s="105"/>
+      <c r="D102" s="105"/>
+      <c r="E102" s="105"/>
+      <c r="F102" s="105"/>
+      <c r="G102" s="105"/>
+      <c r="H102" s="105"/>
+      <c r="I102" s="105"/>
+      <c r="J102" s="105"/>
+      <c r="K102" s="105"/>
+      <c r="L102" s="105"/>
+      <c r="M102" s="105"/>
+      <c r="N102" s="105"/>
+      <c r="O102" s="105"/>
       <c r="P102" s="21"/>
       <c r="Q102" s="21"/>
       <c r="R102" s="21"/>
@@ -30169,52 +30150,24 @@
       <c r="BM102" s="21"/>
       <c r="BN102" s="21"/>
     </row>
-    <row r="103" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="92">
+    <row r="103" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="B103" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C103" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D103" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E103" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="F103" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="G103" s="92">
-        <v>403</v>
-      </c>
-      <c r="H103" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="I103" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J103" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K103" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L103" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M103" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N103" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O103" s="93" t="s">
-        <v>12</v>
-      </c>
+      <c r="B103" s="106"/>
+      <c r="C103" s="106"/>
+      <c r="D103" s="106"/>
+      <c r="E103" s="106"/>
+      <c r="F103" s="106"/>
+      <c r="G103" s="106"/>
+      <c r="H103" s="106"/>
+      <c r="I103" s="106"/>
+      <c r="J103" s="106"/>
+      <c r="K103" s="106"/>
+      <c r="L103" s="106"/>
+      <c r="M103" s="106"/>
+      <c r="N103" s="106"/>
+      <c r="O103" s="106"/>
       <c r="P103" s="21"/>
       <c r="Q103" s="21"/>
       <c r="R103" s="21"/>
@@ -30267,50 +30220,50 @@
       <c r="BM103" s="21"/>
       <c r="BN103" s="21"/>
     </row>
-    <row r="104" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
-        <v>72</v>
+    <row r="104" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="92">
+        <v>146</v>
       </c>
       <c r="B104" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C104" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="D104" s="4" t="s">
+      <c r="C104" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D104" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="E104" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F104" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G104" s="24">
-        <v>401</v>
-      </c>
-      <c r="H104" s="58" t="s">
+      <c r="G104" s="92">
+        <v>403</v>
+      </c>
+      <c r="H104" s="92" t="s">
         <v>216</v>
       </c>
       <c r="I104" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J104" s="4" t="s">
+      <c r="J104" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K104" s="4" t="s">
+      <c r="K104" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L104" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M104" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N104" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="O104" s="49" t="s">
+      <c r="L104" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M104" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N104" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O104" s="93" t="s">
         <v>12</v>
       </c>
       <c r="P104" s="21"/>
@@ -30365,160 +30318,160 @@
       <c r="BM104" s="21"/>
       <c r="BN104" s="21"/>
     </row>
-    <row r="105" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A105" s="92">
-        <v>73</v>
-      </c>
-      <c r="B105" s="104" t="s">
+    <row r="105" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A105" s="4">
+        <v>72</v>
+      </c>
+      <c r="B105" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C105" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="D105" s="92" t="s">
+      <c r="C105" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E105" s="92" t="s">
+      <c r="E105" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F105" s="92" t="s">
+      <c r="F105" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G105" s="74">
+      <c r="G105" s="24">
         <v>401</v>
       </c>
       <c r="H105" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I105" s="74" t="s">
+      <c r="I105" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J105" s="92" t="s">
+      <c r="J105" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K105" s="92" t="s">
+      <c r="K105" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L105" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M105" s="103" t="s">
+      <c r="L105" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M105" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N105" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O105" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="P105" s="21"/>
+      <c r="Q105" s="21"/>
+      <c r="R105" s="21"/>
+      <c r="S105" s="21"/>
+      <c r="T105" s="21"/>
+      <c r="U105" s="21"/>
+      <c r="V105" s="21"/>
+      <c r="W105" s="21"/>
+      <c r="X105" s="21"/>
+      <c r="Y105" s="21"/>
+      <c r="Z105" s="21"/>
+      <c r="AA105" s="21"/>
+      <c r="AB105" s="21"/>
+      <c r="AC105" s="21"/>
+      <c r="AD105" s="21"/>
+      <c r="AE105" s="21"/>
+      <c r="AF105" s="21"/>
+      <c r="AG105" s="21"/>
+      <c r="AH105" s="21"/>
+      <c r="AI105" s="21"/>
+      <c r="AJ105" s="21"/>
+      <c r="AK105" s="21"/>
+      <c r="AL105" s="21"/>
+      <c r="AM105" s="21"/>
+      <c r="AN105" s="21"/>
+      <c r="AO105" s="21"/>
+      <c r="AP105" s="21"/>
+      <c r="AQ105" s="21"/>
+      <c r="AR105" s="21"/>
+      <c r="AS105" s="21"/>
+      <c r="AT105" s="21"/>
+      <c r="AU105" s="21"/>
+      <c r="AV105" s="21"/>
+      <c r="AW105" s="21"/>
+      <c r="AX105" s="21"/>
+      <c r="AY105" s="21"/>
+      <c r="AZ105" s="21"/>
+      <c r="BA105" s="21"/>
+      <c r="BB105" s="21"/>
+      <c r="BC105" s="21"/>
+      <c r="BD105" s="21"/>
+      <c r="BE105" s="21"/>
+      <c r="BF105" s="21"/>
+      <c r="BG105" s="21"/>
+      <c r="BH105" s="21"/>
+      <c r="BI105" s="21"/>
+      <c r="BJ105" s="21"/>
+      <c r="BK105" s="21"/>
+      <c r="BL105" s="21"/>
+      <c r="BM105" s="21"/>
+      <c r="BN105" s="21"/>
+    </row>
+    <row r="106" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A106" s="92">
+        <v>73</v>
+      </c>
+      <c r="B106" s="103" t="s">
+        <v>130</v>
+      </c>
+      <c r="C106" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="N105" s="102" t="s">
+      <c r="D106" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="O105" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
-        <v>75</v>
-      </c>
-      <c r="B106" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C106" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E106" s="4" t="s">
+      <c r="E106" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F106" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G106" s="24">
-        <v>400</v>
+      <c r="G106" s="74">
+        <v>401</v>
       </c>
       <c r="H106" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I106" s="24" t="s">
+      <c r="I106" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J106" s="4" t="s">
+      <c r="J106" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K106" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L106" s="10">
-        <v>1003</v>
-      </c>
-      <c r="M106" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="N106" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="O106" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P106" s="22"/>
-      <c r="Q106" s="22"/>
-      <c r="R106" s="22"/>
-      <c r="S106" s="22"/>
-      <c r="T106" s="22"/>
-      <c r="U106" s="22"/>
-      <c r="V106" s="22"/>
-      <c r="W106" s="22"/>
-      <c r="X106" s="22"/>
-      <c r="Y106" s="22"/>
-      <c r="Z106" s="22"/>
-      <c r="AA106" s="22"/>
-      <c r="AB106" s="22"/>
-      <c r="AC106" s="22"/>
-      <c r="AD106" s="22"/>
-      <c r="AE106" s="22"/>
-      <c r="AF106" s="22"/>
-      <c r="AG106" s="22"/>
-      <c r="AH106" s="22"/>
-      <c r="AI106" s="22"/>
-      <c r="AJ106" s="22"/>
-      <c r="AK106" s="22"/>
-      <c r="AL106" s="22"/>
-      <c r="AM106" s="22"/>
-      <c r="AN106" s="22"/>
-      <c r="AO106" s="22"/>
-      <c r="AP106" s="22"/>
-      <c r="AQ106" s="22"/>
-      <c r="AR106" s="22"/>
-      <c r="AS106" s="22"/>
-      <c r="AT106" s="22"/>
-      <c r="AU106" s="22"/>
-      <c r="AV106" s="22"/>
-      <c r="AW106" s="22"/>
-      <c r="AX106" s="22"/>
-      <c r="AY106" s="22"/>
-      <c r="AZ106" s="22"/>
-      <c r="BA106" s="22"/>
-      <c r="BB106" s="22"/>
-      <c r="BC106" s="22"/>
-      <c r="BD106" s="22"/>
-      <c r="BE106" s="22"/>
-      <c r="BF106" s="22"/>
-      <c r="BG106" s="22"/>
-      <c r="BH106" s="22"/>
-      <c r="BI106" s="22"/>
-      <c r="BJ106" s="22"/>
-      <c r="BK106" s="22"/>
-      <c r="BL106" s="22"/>
-      <c r="BM106" s="22"/>
-      <c r="BN106" s="22"/>
-    </row>
-    <row r="107" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K106" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L106" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M106" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="N106" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="O106" s="93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B107" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>148</v>
+      <c r="C107" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>12</v>
@@ -30542,13 +30495,13 @@
         <v>7</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L107" s="10">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="M107" s="30" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N107" s="30" t="s">
         <v>131</v>
@@ -30608,15 +30561,15 @@
       <c r="BM107" s="22"/>
       <c r="BN107" s="22"/>
     </row>
-    <row r="108" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B108" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>12</v>
@@ -30640,13 +30593,13 @@
         <v>7</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L108" s="10">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="M108" s="30" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N108" s="30" t="s">
         <v>131</v>
@@ -30706,26 +30659,26 @@
       <c r="BM108" s="22"/>
       <c r="BN108" s="22"/>
     </row>
-    <row r="109" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="B109" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C109" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D109" s="53" t="s">
+      <c r="C109" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E109" s="53" t="s">
+      <c r="E109" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F109" s="53" t="s">
+      <c r="F109" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G109" s="54">
+      <c r="G109" s="24">
         <v>400</v>
       </c>
       <c r="H109" s="58" t="s">
@@ -30734,46 +30687,97 @@
       <c r="I109" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J109" s="53" t="s">
+      <c r="J109" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K109" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="L109" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M109" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N109" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O109" s="63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K109" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L109" s="10">
+        <v>1005</v>
+      </c>
+      <c r="M109" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="N109" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="O109" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P109" s="22"/>
+      <c r="Q109" s="22"/>
+      <c r="R109" s="22"/>
+      <c r="S109" s="22"/>
+      <c r="T109" s="22"/>
+      <c r="U109" s="22"/>
+      <c r="V109" s="22"/>
+      <c r="W109" s="22"/>
+      <c r="X109" s="22"/>
+      <c r="Y109" s="22"/>
+      <c r="Z109" s="22"/>
+      <c r="AA109" s="22"/>
+      <c r="AB109" s="22"/>
+      <c r="AC109" s="22"/>
+      <c r="AD109" s="22"/>
+      <c r="AE109" s="22"/>
+      <c r="AF109" s="22"/>
+      <c r="AG109" s="22"/>
+      <c r="AH109" s="22"/>
+      <c r="AI109" s="22"/>
+      <c r="AJ109" s="22"/>
+      <c r="AK109" s="22"/>
+      <c r="AL109" s="22"/>
+      <c r="AM109" s="22"/>
+      <c r="AN109" s="22"/>
+      <c r="AO109" s="22"/>
+      <c r="AP109" s="22"/>
+      <c r="AQ109" s="22"/>
+      <c r="AR109" s="22"/>
+      <c r="AS109" s="22"/>
+      <c r="AT109" s="22"/>
+      <c r="AU109" s="22"/>
+      <c r="AV109" s="22"/>
+      <c r="AW109" s="22"/>
+      <c r="AX109" s="22"/>
+      <c r="AY109" s="22"/>
+      <c r="AZ109" s="22"/>
+      <c r="BA109" s="22"/>
+      <c r="BB109" s="22"/>
+      <c r="BC109" s="22"/>
+      <c r="BD109" s="22"/>
+      <c r="BE109" s="22"/>
+      <c r="BF109" s="22"/>
+      <c r="BG109" s="22"/>
+      <c r="BH109" s="22"/>
+      <c r="BI109" s="22"/>
+      <c r="BJ109" s="22"/>
+      <c r="BK109" s="22"/>
+      <c r="BL109" s="22"/>
+      <c r="BM109" s="22"/>
+      <c r="BN109" s="22"/>
+    </row>
+    <row r="110" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="B110" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D110" s="4" t="s">
+      <c r="C110" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D110" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F110" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G110" s="24">
-        <v>403</v>
+      <c r="G110" s="54">
+        <v>400</v>
       </c>
       <c r="H110" s="58" t="s">
         <v>216</v>
@@ -30781,85 +30785,34 @@
       <c r="I110" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J110" s="4" t="s">
+      <c r="J110" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K110" s="4" t="s">
+      <c r="K110" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L110" s="10">
-        <v>1006</v>
-      </c>
-      <c r="M110" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="N110" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="O110" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="P110" s="22"/>
-      <c r="Q110" s="22"/>
-      <c r="R110" s="22"/>
-      <c r="S110" s="22"/>
-      <c r="T110" s="22"/>
-      <c r="U110" s="22"/>
-      <c r="V110" s="22"/>
-      <c r="W110" s="22"/>
-      <c r="X110" s="22"/>
-      <c r="Y110" s="22"/>
-      <c r="Z110" s="22"/>
-      <c r="AA110" s="22"/>
-      <c r="AB110" s="22"/>
-      <c r="AC110" s="22"/>
-      <c r="AD110" s="22"/>
-      <c r="AE110" s="22"/>
-      <c r="AF110" s="22"/>
-      <c r="AG110" s="22"/>
-      <c r="AH110" s="22"/>
-      <c r="AI110" s="22"/>
-      <c r="AJ110" s="22"/>
-      <c r="AK110" s="22"/>
-      <c r="AL110" s="22"/>
-      <c r="AM110" s="22"/>
-      <c r="AN110" s="22"/>
-      <c r="AO110" s="22"/>
-      <c r="AP110" s="22"/>
-      <c r="AQ110" s="22"/>
-      <c r="AR110" s="22"/>
-      <c r="AS110" s="22"/>
-      <c r="AT110" s="22"/>
-      <c r="AU110" s="22"/>
-      <c r="AV110" s="22"/>
-      <c r="AW110" s="22"/>
-      <c r="AX110" s="22"/>
-      <c r="AY110" s="22"/>
-      <c r="AZ110" s="22"/>
-      <c r="BA110" s="22"/>
-      <c r="BB110" s="22"/>
-      <c r="BC110" s="22"/>
-      <c r="BD110" s="22"/>
-      <c r="BE110" s="22"/>
-      <c r="BF110" s="22"/>
-      <c r="BG110" s="22"/>
-      <c r="BH110" s="22"/>
-      <c r="BI110" s="22"/>
-      <c r="BJ110" s="22"/>
-      <c r="BK110" s="22"/>
-      <c r="BL110" s="22"/>
-      <c r="BM110" s="22"/>
-      <c r="BN110" s="22"/>
+      <c r="L110" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M110" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N110" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O110" s="63" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="111" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B111" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>12</v>
@@ -30883,13 +30836,13 @@
         <v>7</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L111" s="10">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="M111" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N111" s="30" t="s">
         <v>131</v>
@@ -30949,15 +30902,15 @@
       <c r="BM111" s="22"/>
       <c r="BN111" s="22"/>
     </row>
-    <row r="112" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B112" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>12</v>
@@ -30984,10 +30937,10 @@
         <v>30</v>
       </c>
       <c r="L112" s="10">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M112" s="30" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N112" s="30" t="s">
         <v>131</v>
@@ -31047,46 +31000,48 @@
       <c r="BM112" s="22"/>
       <c r="BN112" s="22"/>
     </row>
-    <row r="113" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
+    <row r="113" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A113" s="4">
+        <v>80</v>
+      </c>
       <c r="B113" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C113" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="D113" s="24" t="s">
+      <c r="C113" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="24" t="s">
+      <c r="E113" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F113" s="24" t="s">
+      <c r="F113" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G113" s="44">
+      <c r="G113" s="24">
         <v>403</v>
       </c>
-      <c r="H113" s="24" t="s">
+      <c r="H113" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I113" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J113" s="24" t="s">
+      <c r="J113" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K113" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L113" s="24">
-        <v>1011</v>
-      </c>
-      <c r="M113" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="N113" s="32" t="s">
-        <v>55</v>
+      <c r="K113" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L113" s="10">
+        <v>1008</v>
+      </c>
+      <c r="M113" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="N113" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="O113" s="30" t="s">
         <v>59</v>
@@ -31143,51 +31098,49 @@
       <c r="BM113" s="22"/>
       <c r="BN113" s="22"/>
     </row>
-    <row r="114" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A114" s="4">
-        <v>81</v>
-      </c>
+    <row r="114" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A114" s="4"/>
       <c r="B114" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C114" s="6" t="s">
-        <v>203</v>
+      <c r="C114" s="23" t="s">
+        <v>295</v>
       </c>
       <c r="D114" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E114" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F114" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G114" s="24">
+      <c r="G114" s="44">
         <v>403</v>
       </c>
-      <c r="H114" s="58" t="s">
+      <c r="H114" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I114" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J114" s="4" t="s">
+      <c r="J114" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K114" s="4" t="s">
+      <c r="K114" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="L114" s="4">
+      <c r="L114" s="24">
         <v>1011</v>
       </c>
       <c r="M114" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N114" s="30" t="s">
-        <v>131</v>
+      <c r="N114" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O114" s="30" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="P114" s="22"/>
       <c r="Q114" s="22"/>
@@ -31241,27 +31194,27 @@
       <c r="BM114" s="22"/>
       <c r="BN114" s="22"/>
     </row>
-    <row r="115" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B115" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D115" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D115" s="24" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>140</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G115" s="24">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H115" s="58" t="s">
         <v>216</v>
@@ -31275,17 +31228,17 @@
       <c r="K115" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L115" s="10">
-        <v>3001</v>
-      </c>
-      <c r="M115" s="30" t="s">
-        <v>211</v>
+      <c r="L115" s="4">
+        <v>1011</v>
+      </c>
+      <c r="M115" s="32" t="s">
+        <v>202</v>
       </c>
       <c r="N115" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O115" s="30" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="P115" s="22"/>
       <c r="Q115" s="22"/>
@@ -31339,15 +31292,15 @@
       <c r="BM115" s="22"/>
       <c r="BN115" s="22"/>
     </row>
-    <row r="116" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B116" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>113</v>
+        <v>210</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>12</v>
@@ -31356,7 +31309,7 @@
         <v>140</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G116" s="24">
         <v>400</v>
@@ -31371,19 +31324,19 @@
         <v>7</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="L116" s="10">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="M116" s="30" t="s">
-        <v>28</v>
+        <v>211</v>
       </c>
       <c r="N116" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O116" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P116" s="22"/>
       <c r="Q116" s="22"/>
@@ -31438,14 +31391,14 @@
       <c r="BN116" s="22"/>
     </row>
     <row r="117" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A117" s="26">
-        <v>137</v>
+      <c r="A117" s="4">
+        <v>83</v>
       </c>
       <c r="B117" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C117" s="71" t="s">
-        <v>207</v>
+      <c r="C117" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>12</v>
@@ -31453,8 +31406,8 @@
       <c r="E117" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F117" s="26" t="s">
-        <v>141</v>
+      <c r="F117" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="G117" s="24">
         <v>400</v>
@@ -31471,17 +31424,17 @@
       <c r="K117" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L117" s="26">
-        <v>3009</v>
-      </c>
-      <c r="M117" s="71" t="s">
-        <v>207</v>
+      <c r="L117" s="10">
+        <v>3002</v>
+      </c>
+      <c r="M117" s="30" t="s">
+        <v>28</v>
       </c>
       <c r="N117" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O117" s="33" t="s">
-        <v>212</v>
+      <c r="O117" s="30" t="s">
+        <v>66</v>
       </c>
       <c r="P117" s="22"/>
       <c r="Q117" s="22"/>
@@ -31535,15 +31488,15 @@
       <c r="BM117" s="22"/>
       <c r="BN117" s="22"/>
     </row>
-    <row r="118" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A118" s="26">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B118" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C118" s="71" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>12</v>
@@ -31567,81 +31520,81 @@
         <v>7</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L118" s="26">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="M118" s="71" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N118" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O118" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="P118" s="21"/>
-      <c r="Q118" s="21"/>
-      <c r="R118" s="21"/>
-      <c r="S118" s="21"/>
-      <c r="T118" s="21"/>
-      <c r="U118" s="21"/>
-      <c r="V118" s="21"/>
-      <c r="W118" s="21"/>
-      <c r="X118" s="21"/>
-      <c r="Y118" s="21"/>
-      <c r="Z118" s="21"/>
-      <c r="AA118" s="21"/>
-      <c r="AB118" s="21"/>
-      <c r="AC118" s="21"/>
-      <c r="AD118" s="21"/>
-      <c r="AE118" s="21"/>
-      <c r="AF118" s="21"/>
-      <c r="AG118" s="21"/>
-      <c r="AH118" s="21"/>
-      <c r="AI118" s="21"/>
-      <c r="AJ118" s="21"/>
-      <c r="AK118" s="21"/>
-      <c r="AL118" s="21"/>
-      <c r="AM118" s="21"/>
-      <c r="AN118" s="21"/>
-      <c r="AO118" s="21"/>
-      <c r="AP118" s="21"/>
-      <c r="AQ118" s="21"/>
-      <c r="AR118" s="21"/>
-      <c r="AS118" s="21"/>
-      <c r="AT118" s="21"/>
-      <c r="AU118" s="21"/>
-      <c r="AV118" s="21"/>
-      <c r="AW118" s="21"/>
-      <c r="AX118" s="21"/>
-      <c r="AY118" s="21"/>
-      <c r="AZ118" s="21"/>
-      <c r="BA118" s="21"/>
-      <c r="BB118" s="21"/>
-      <c r="BC118" s="21"/>
-      <c r="BD118" s="21"/>
-      <c r="BE118" s="21"/>
-      <c r="BF118" s="21"/>
-      <c r="BG118" s="21"/>
-      <c r="BH118" s="21"/>
-      <c r="BI118" s="21"/>
-      <c r="BJ118" s="21"/>
-      <c r="BK118" s="21"/>
-      <c r="BL118" s="21"/>
-      <c r="BM118" s="21"/>
-      <c r="BN118" s="21"/>
-    </row>
-    <row r="119" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="P118" s="22"/>
+      <c r="Q118" s="22"/>
+      <c r="R118" s="22"/>
+      <c r="S118" s="22"/>
+      <c r="T118" s="22"/>
+      <c r="U118" s="22"/>
+      <c r="V118" s="22"/>
+      <c r="W118" s="22"/>
+      <c r="X118" s="22"/>
+      <c r="Y118" s="22"/>
+      <c r="Z118" s="22"/>
+      <c r="AA118" s="22"/>
+      <c r="AB118" s="22"/>
+      <c r="AC118" s="22"/>
+      <c r="AD118" s="22"/>
+      <c r="AE118" s="22"/>
+      <c r="AF118" s="22"/>
+      <c r="AG118" s="22"/>
+      <c r="AH118" s="22"/>
+      <c r="AI118" s="22"/>
+      <c r="AJ118" s="22"/>
+      <c r="AK118" s="22"/>
+      <c r="AL118" s="22"/>
+      <c r="AM118" s="22"/>
+      <c r="AN118" s="22"/>
+      <c r="AO118" s="22"/>
+      <c r="AP118" s="22"/>
+      <c r="AQ118" s="22"/>
+      <c r="AR118" s="22"/>
+      <c r="AS118" s="22"/>
+      <c r="AT118" s="22"/>
+      <c r="AU118" s="22"/>
+      <c r="AV118" s="22"/>
+      <c r="AW118" s="22"/>
+      <c r="AX118" s="22"/>
+      <c r="AY118" s="22"/>
+      <c r="AZ118" s="22"/>
+      <c r="BA118" s="22"/>
+      <c r="BB118" s="22"/>
+      <c r="BC118" s="22"/>
+      <c r="BD118" s="22"/>
+      <c r="BE118" s="22"/>
+      <c r="BF118" s="22"/>
+      <c r="BG118" s="22"/>
+      <c r="BH118" s="22"/>
+      <c r="BI118" s="22"/>
+      <c r="BJ118" s="22"/>
+      <c r="BK118" s="22"/>
+      <c r="BL118" s="22"/>
+      <c r="BM118" s="22"/>
+      <c r="BN118" s="22"/>
+    </row>
+    <row r="119" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="26">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B119" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C119" s="71" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>12</v>
@@ -31668,10 +31621,10 @@
         <v>30</v>
       </c>
       <c r="L119" s="26">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="M119" s="71" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N119" s="30" t="s">
         <v>131</v>
@@ -31731,15 +31684,15 @@
       <c r="BM119" s="21"/>
       <c r="BN119" s="21"/>
     </row>
-    <row r="120" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A120" s="26">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B120" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C120" s="71" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>12</v>
@@ -31751,7 +31704,7 @@
         <v>141</v>
       </c>
       <c r="G120" s="24">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H120" s="58" t="s">
         <v>216</v>
@@ -31766,16 +31719,16 @@
         <v>30</v>
       </c>
       <c r="L120" s="26">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="M120" s="71" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="N120" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O120" s="30" t="s">
-        <v>12</v>
+      <c r="O120" s="33" t="s">
+        <v>213</v>
       </c>
       <c r="P120" s="21"/>
       <c r="Q120" s="21"/>
@@ -31831,13 +31784,13 @@
     </row>
     <row r="121" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A121" s="26">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B121" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C121" s="84" t="s">
-        <v>229</v>
+      <c r="C121" s="71" t="s">
+        <v>221</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>12</v>
@@ -31845,11 +31798,11 @@
       <c r="E121" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F121" s="4" t="s">
-        <v>140</v>
+      <c r="F121" s="26" t="s">
+        <v>141</v>
       </c>
       <c r="G121" s="24">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H121" s="58" t="s">
         <v>216</v>
@@ -31864,16 +31817,16 @@
         <v>30</v>
       </c>
       <c r="L121" s="26">
-        <v>3013</v>
-      </c>
-      <c r="M121" s="84" t="s">
-        <v>230</v>
+        <v>3012</v>
+      </c>
+      <c r="M121" s="71" t="s">
+        <v>222</v>
       </c>
       <c r="N121" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O121" s="30" t="s">
-        <v>231</v>
+        <v>12</v>
       </c>
       <c r="P121" s="21"/>
       <c r="Q121" s="21"/>
@@ -31927,26 +31880,26 @@
       <c r="BM121" s="21"/>
       <c r="BN121" s="21"/>
     </row>
-    <row r="122" spans="1:66" s="50" customFormat="1" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A122" s="58">
-        <v>84</v>
-      </c>
-      <c r="B122" s="59" t="s">
+    <row r="122" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A122" s="26">
+        <v>141</v>
+      </c>
+      <c r="B122" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C122" s="60" t="s">
-        <v>165</v>
-      </c>
-      <c r="D122" s="58" t="s">
+      <c r="C122" s="84" t="s">
+        <v>229</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E122" s="72" t="s">
+      <c r="E122" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F122" s="72" t="s">
+      <c r="F122" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G122" s="58">
+      <c r="G122" s="24">
         <v>400</v>
       </c>
       <c r="H122" s="58" t="s">
@@ -31955,23 +31908,23 @@
       <c r="I122" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J122" s="58" t="s">
+      <c r="J122" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K122" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="L122" s="58">
-        <v>1002</v>
-      </c>
-      <c r="M122" s="59" t="s">
-        <v>167</v>
-      </c>
-      <c r="N122" s="59" t="s">
+      <c r="K122" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L122" s="26">
+        <v>3013</v>
+      </c>
+      <c r="M122" s="84" t="s">
+        <v>230</v>
+      </c>
+      <c r="N122" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O122" s="59" t="s">
-        <v>66</v>
+      <c r="O122" s="30" t="s">
+        <v>231</v>
       </c>
       <c r="P122" s="21"/>
       <c r="Q122" s="21"/>
@@ -32027,13 +31980,13 @@
     </row>
     <row r="123" spans="1:66" s="50" customFormat="1" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="B123" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C123" s="97" t="s">
-        <v>280</v>
+      <c r="C123" s="60" t="s">
+        <v>165</v>
       </c>
       <c r="D123" s="58" t="s">
         <v>12</v>
@@ -32060,16 +32013,16 @@
         <v>11</v>
       </c>
       <c r="L123" s="58">
-        <v>3014</v>
-      </c>
-      <c r="M123" s="97" t="s">
-        <v>280</v>
-      </c>
-      <c r="N123" s="30" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M123" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="N123" s="59" t="s">
         <v>131</v>
       </c>
       <c r="O123" s="59" t="s">
-        <v>279</v>
+        <v>66</v>
       </c>
       <c r="P123" s="21"/>
       <c r="Q123" s="21"/>
@@ -32123,337 +32076,365 @@
       <c r="BM123" s="21"/>
       <c r="BN123" s="21"/>
     </row>
-    <row r="124" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="8">
-        <v>168</v>
-      </c>
-      <c r="B124" s="30" t="s">
+    <row r="124" spans="1:66" s="50" customFormat="1" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A124" s="58">
+        <v>156</v>
+      </c>
+      <c r="B124" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C124" s="31" t="s">
-        <v>298</v>
+      <c r="C124" s="97" t="s">
+        <v>280</v>
       </c>
       <c r="D124" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E124" s="8" t="s">
+      <c r="E124" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="F124" s="8" t="s">
+      <c r="F124" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="G124" s="8">
-        <v>401</v>
-      </c>
-      <c r="H124" s="54" t="s">
+      <c r="G124" s="58">
+        <v>400</v>
+      </c>
+      <c r="H124" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I124" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J124" s="92" t="s">
+      <c r="J124" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K124" s="92" t="s">
+      <c r="K124" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="L124" s="58">
+        <v>3014</v>
+      </c>
+      <c r="M124" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="N124" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="O124" s="59" t="s">
+        <v>279</v>
+      </c>
+      <c r="P124" s="21"/>
+      <c r="Q124" s="21"/>
+      <c r="R124" s="21"/>
+      <c r="S124" s="21"/>
+      <c r="T124" s="21"/>
+      <c r="U124" s="21"/>
+      <c r="V124" s="21"/>
+      <c r="W124" s="21"/>
+      <c r="X124" s="21"/>
+      <c r="Y124" s="21"/>
+      <c r="Z124" s="21"/>
+      <c r="AA124" s="21"/>
+      <c r="AB124" s="21"/>
+      <c r="AC124" s="21"/>
+      <c r="AD124" s="21"/>
+      <c r="AE124" s="21"/>
+      <c r="AF124" s="21"/>
+      <c r="AG124" s="21"/>
+      <c r="AH124" s="21"/>
+      <c r="AI124" s="21"/>
+      <c r="AJ124" s="21"/>
+      <c r="AK124" s="21"/>
+      <c r="AL124" s="21"/>
+      <c r="AM124" s="21"/>
+      <c r="AN124" s="21"/>
+      <c r="AO124" s="21"/>
+      <c r="AP124" s="21"/>
+      <c r="AQ124" s="21"/>
+      <c r="AR124" s="21"/>
+      <c r="AS124" s="21"/>
+      <c r="AT124" s="21"/>
+      <c r="AU124" s="21"/>
+      <c r="AV124" s="21"/>
+      <c r="AW124" s="21"/>
+      <c r="AX124" s="21"/>
+      <c r="AY124" s="21"/>
+      <c r="AZ124" s="21"/>
+      <c r="BA124" s="21"/>
+      <c r="BB124" s="21"/>
+      <c r="BC124" s="21"/>
+      <c r="BD124" s="21"/>
+      <c r="BE124" s="21"/>
+      <c r="BF124" s="21"/>
+      <c r="BG124" s="21"/>
+      <c r="BH124" s="21"/>
+      <c r="BI124" s="21"/>
+      <c r="BJ124" s="21"/>
+      <c r="BK124" s="21"/>
+      <c r="BL124" s="21"/>
+      <c r="BM124" s="21"/>
+      <c r="BN124" s="21"/>
+    </row>
+    <row r="125" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="8">
+        <v>168</v>
+      </c>
+      <c r="B125" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C125" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D125" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G125" s="8">
+        <v>401</v>
+      </c>
+      <c r="H125" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="I125" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J125" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K125" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L124" s="8">
+      <c r="L125" s="8">
         <v>1014</v>
       </c>
-      <c r="M124" s="31" t="s">
+      <c r="M125" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="N124" s="64" t="s">
+      <c r="N125" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O124" s="64" t="s">
+      <c r="O125" s="64" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A125" s="107" t="s">
+    <row r="126" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A126" s="106" t="s">
         <v>145</v>
       </c>
-      <c r="B125" s="107"/>
-      <c r="C125" s="107"/>
-      <c r="D125" s="107"/>
-      <c r="E125" s="107"/>
-      <c r="F125" s="107"/>
-      <c r="G125" s="107"/>
-      <c r="H125" s="107"/>
-      <c r="I125" s="107"/>
-      <c r="J125" s="107"/>
-      <c r="K125" s="107"/>
-      <c r="L125" s="107"/>
-      <c r="M125" s="107"/>
-      <c r="N125" s="107"/>
-      <c r="O125" s="107"/>
-      <c r="P125" s="21"/>
-      <c r="Q125" s="21"/>
-      <c r="R125" s="21"/>
-      <c r="S125" s="21"/>
-      <c r="T125" s="21"/>
-      <c r="U125" s="21"/>
-      <c r="V125" s="21"/>
-      <c r="W125" s="21"/>
-      <c r="X125" s="21"/>
-      <c r="Y125" s="21"/>
-      <c r="Z125" s="21"/>
-      <c r="AA125" s="21"/>
-      <c r="AB125" s="21"/>
-      <c r="AC125" s="21"/>
-      <c r="AD125" s="21"/>
-      <c r="AE125" s="21"/>
-      <c r="AF125" s="21"/>
-      <c r="AG125" s="21"/>
-      <c r="AH125" s="21"/>
-      <c r="AI125" s="21"/>
-      <c r="AJ125" s="21"/>
-      <c r="AK125" s="21"/>
-      <c r="AL125" s="21"/>
-      <c r="AM125" s="21"/>
-      <c r="AN125" s="21"/>
-      <c r="AO125" s="21"/>
-      <c r="AP125" s="21"/>
-      <c r="AQ125" s="21"/>
-      <c r="AR125" s="21"/>
-      <c r="AS125" s="21"/>
-      <c r="AT125" s="21"/>
-      <c r="AU125" s="21"/>
-      <c r="AV125" s="21"/>
-      <c r="AW125" s="21"/>
-      <c r="AX125" s="21"/>
-      <c r="AY125" s="21"/>
-      <c r="AZ125" s="21"/>
-      <c r="BA125" s="21"/>
-      <c r="BB125" s="21"/>
-      <c r="BC125" s="21"/>
-      <c r="BD125" s="21"/>
-      <c r="BE125" s="21"/>
-      <c r="BF125" s="21"/>
-      <c r="BG125" s="21"/>
-      <c r="BH125" s="21"/>
-      <c r="BI125" s="21"/>
-      <c r="BJ125" s="21"/>
-      <c r="BK125" s="21"/>
-      <c r="BL125" s="21"/>
-      <c r="BM125" s="21"/>
-      <c r="BN125" s="21"/>
-    </row>
-    <row r="126" spans="1:66" s="36" customFormat="1" ht="49.7" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A126" s="38">
+      <c r="B126" s="106"/>
+      <c r="C126" s="106"/>
+      <c r="D126" s="106"/>
+      <c r="E126" s="106"/>
+      <c r="F126" s="106"/>
+      <c r="G126" s="106"/>
+      <c r="H126" s="106"/>
+      <c r="I126" s="106"/>
+      <c r="J126" s="106"/>
+      <c r="K126" s="106"/>
+      <c r="L126" s="106"/>
+      <c r="M126" s="106"/>
+      <c r="N126" s="106"/>
+      <c r="O126" s="106"/>
+      <c r="P126" s="21"/>
+      <c r="Q126" s="21"/>
+      <c r="R126" s="21"/>
+      <c r="S126" s="21"/>
+      <c r="T126" s="21"/>
+      <c r="U126" s="21"/>
+      <c r="V126" s="21"/>
+      <c r="W126" s="21"/>
+      <c r="X126" s="21"/>
+      <c r="Y126" s="21"/>
+      <c r="Z126" s="21"/>
+      <c r="AA126" s="21"/>
+      <c r="AB126" s="21"/>
+      <c r="AC126" s="21"/>
+      <c r="AD126" s="21"/>
+      <c r="AE126" s="21"/>
+      <c r="AF126" s="21"/>
+      <c r="AG126" s="21"/>
+      <c r="AH126" s="21"/>
+      <c r="AI126" s="21"/>
+      <c r="AJ126" s="21"/>
+      <c r="AK126" s="21"/>
+      <c r="AL126" s="21"/>
+      <c r="AM126" s="21"/>
+      <c r="AN126" s="21"/>
+      <c r="AO126" s="21"/>
+      <c r="AP126" s="21"/>
+      <c r="AQ126" s="21"/>
+      <c r="AR126" s="21"/>
+      <c r="AS126" s="21"/>
+      <c r="AT126" s="21"/>
+      <c r="AU126" s="21"/>
+      <c r="AV126" s="21"/>
+      <c r="AW126" s="21"/>
+      <c r="AX126" s="21"/>
+      <c r="AY126" s="21"/>
+      <c r="AZ126" s="21"/>
+      <c r="BA126" s="21"/>
+      <c r="BB126" s="21"/>
+      <c r="BC126" s="21"/>
+      <c r="BD126" s="21"/>
+      <c r="BE126" s="21"/>
+      <c r="BF126" s="21"/>
+      <c r="BG126" s="21"/>
+      <c r="BH126" s="21"/>
+      <c r="BI126" s="21"/>
+      <c r="BJ126" s="21"/>
+      <c r="BK126" s="21"/>
+      <c r="BL126" s="21"/>
+      <c r="BM126" s="21"/>
+      <c r="BN126" s="21"/>
+    </row>
+    <row r="127" spans="1:66" s="36" customFormat="1" ht="49.7" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A127" s="38">
         <v>145</v>
-      </c>
-      <c r="B126" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C126" s="41" t="s">
-        <v>241</v>
-      </c>
-      <c r="D126" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E126" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="F126" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="G126" s="24">
-        <v>400</v>
-      </c>
-      <c r="H126" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="I126" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J126" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="K126" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="L126" s="86">
-        <v>3008</v>
-      </c>
-      <c r="M126" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="N126" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="O126" s="87" t="s">
-        <v>242</v>
-      </c>
-      <c r="P126" s="35"/>
-      <c r="Q126" s="35"/>
-      <c r="R126" s="35"/>
-      <c r="S126" s="35"/>
-      <c r="T126" s="35"/>
-      <c r="U126" s="35"/>
-      <c r="V126" s="35"/>
-      <c r="W126" s="35"/>
-      <c r="X126" s="35"/>
-      <c r="Y126" s="35"/>
-      <c r="Z126" s="35"/>
-      <c r="AA126" s="35"/>
-      <c r="AB126" s="35"/>
-      <c r="AC126" s="35"/>
-      <c r="AD126" s="35"/>
-      <c r="AE126" s="35"/>
-      <c r="AF126" s="35"/>
-      <c r="AG126" s="35"/>
-      <c r="AH126" s="35"/>
-      <c r="AI126" s="35"/>
-      <c r="AJ126" s="35"/>
-      <c r="AK126" s="35"/>
-      <c r="AL126" s="35"/>
-      <c r="AM126" s="35"/>
-      <c r="AN126" s="35"/>
-      <c r="AO126" s="35"/>
-      <c r="AP126" s="35"/>
-      <c r="AQ126" s="35"/>
-      <c r="AR126" s="35"/>
-      <c r="AS126" s="35"/>
-      <c r="AT126" s="35"/>
-      <c r="AU126" s="35"/>
-      <c r="AV126" s="35"/>
-      <c r="AW126" s="35"/>
-      <c r="AX126" s="35"/>
-      <c r="AY126" s="35"/>
-      <c r="AZ126" s="35"/>
-      <c r="BA126" s="35"/>
-      <c r="BB126" s="35"/>
-      <c r="BC126" s="35"/>
-      <c r="BD126" s="35"/>
-      <c r="BE126" s="35"/>
-      <c r="BF126" s="35"/>
-      <c r="BG126" s="35"/>
-      <c r="BH126" s="35"/>
-      <c r="BI126" s="35"/>
-      <c r="BJ126" s="35"/>
-      <c r="BK126" s="35"/>
-      <c r="BL126" s="35"/>
-      <c r="BM126" s="35"/>
-      <c r="BN126" s="35"/>
-    </row>
-    <row r="127" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A127" s="4">
-        <v>85</v>
       </c>
       <c r="B127" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D127" s="4">
-        <v>8</v>
+      <c r="C127" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D127" s="38" t="s">
+        <v>12</v>
       </c>
       <c r="E127" s="24" t="s">
         <v>140</v>
       </c>
       <c r="F127" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="G127" s="24">
+        <v>400</v>
+      </c>
+      <c r="H127" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="I127" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J127" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="K127" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="L127" s="86">
+        <v>3008</v>
+      </c>
+      <c r="M127" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="N127" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="O127" s="87" t="s">
+        <v>242</v>
+      </c>
+      <c r="P127" s="35"/>
+      <c r="Q127" s="35"/>
+      <c r="R127" s="35"/>
+      <c r="S127" s="35"/>
+      <c r="T127" s="35"/>
+      <c r="U127" s="35"/>
+      <c r="V127" s="35"/>
+      <c r="W127" s="35"/>
+      <c r="X127" s="35"/>
+      <c r="Y127" s="35"/>
+      <c r="Z127" s="35"/>
+      <c r="AA127" s="35"/>
+      <c r="AB127" s="35"/>
+      <c r="AC127" s="35"/>
+      <c r="AD127" s="35"/>
+      <c r="AE127" s="35"/>
+      <c r="AF127" s="35"/>
+      <c r="AG127" s="35"/>
+      <c r="AH127" s="35"/>
+      <c r="AI127" s="35"/>
+      <c r="AJ127" s="35"/>
+      <c r="AK127" s="35"/>
+      <c r="AL127" s="35"/>
+      <c r="AM127" s="35"/>
+      <c r="AN127" s="35"/>
+      <c r="AO127" s="35"/>
+      <c r="AP127" s="35"/>
+      <c r="AQ127" s="35"/>
+      <c r="AR127" s="35"/>
+      <c r="AS127" s="35"/>
+      <c r="AT127" s="35"/>
+      <c r="AU127" s="35"/>
+      <c r="AV127" s="35"/>
+      <c r="AW127" s="35"/>
+      <c r="AX127" s="35"/>
+      <c r="AY127" s="35"/>
+      <c r="AZ127" s="35"/>
+      <c r="BA127" s="35"/>
+      <c r="BB127" s="35"/>
+      <c r="BC127" s="35"/>
+      <c r="BD127" s="35"/>
+      <c r="BE127" s="35"/>
+      <c r="BF127" s="35"/>
+      <c r="BG127" s="35"/>
+      <c r="BH127" s="35"/>
+      <c r="BI127" s="35"/>
+      <c r="BJ127" s="35"/>
+      <c r="BK127" s="35"/>
+      <c r="BL127" s="35"/>
+      <c r="BM127" s="35"/>
+      <c r="BN127" s="35"/>
+    </row>
+    <row r="128" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A128" s="4">
+        <v>85</v>
+      </c>
+      <c r="B128" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D128" s="4">
+        <v>8</v>
+      </c>
+      <c r="E128" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G127" s="44">
+      <c r="F128" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G128" s="44">
         <v>200</v>
       </c>
-      <c r="H127" s="24" t="s">
+      <c r="H128" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="I127" s="24" t="s">
+      <c r="I128" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="J127" s="4" t="s">
+      <c r="J128" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K127" s="4" t="s">
+      <c r="K128" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L127" s="4">
+      <c r="L128" s="4">
         <v>1010</v>
       </c>
-      <c r="M127" s="30" t="s">
+      <c r="M128" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="N127" s="30" t="s">
+      <c r="N128" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O127" s="30" t="s">
+      <c r="O128" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="P127" s="22"/>
-      <c r="Q127" s="22"/>
-      <c r="R127" s="22"/>
-      <c r="S127" s="22"/>
-      <c r="T127" s="22"/>
-      <c r="U127" s="22"/>
-      <c r="V127" s="22"/>
-      <c r="W127" s="22"/>
-      <c r="X127" s="22"/>
-      <c r="Y127" s="22"/>
-      <c r="Z127" s="22"/>
-      <c r="AA127" s="22"/>
-      <c r="AB127" s="22"/>
-      <c r="AC127" s="22"/>
-      <c r="AD127" s="22"/>
-      <c r="AE127" s="22"/>
-      <c r="AF127" s="22"/>
-      <c r="AG127" s="22"/>
-      <c r="AH127" s="22"/>
-      <c r="AI127" s="22"/>
-      <c r="AJ127" s="22"/>
-      <c r="AK127" s="22"/>
-      <c r="AL127" s="22"/>
-      <c r="AM127" s="22"/>
-      <c r="AN127" s="22"/>
-      <c r="AO127" s="22"/>
-      <c r="AP127" s="22"/>
-      <c r="AQ127" s="22"/>
-      <c r="AR127" s="22"/>
-      <c r="AS127" s="22"/>
-      <c r="AT127" s="22"/>
-      <c r="AU127" s="22"/>
-      <c r="AV127" s="22"/>
-      <c r="AW127" s="22"/>
-      <c r="AX127" s="22"/>
-      <c r="AY127" s="22"/>
-      <c r="AZ127" s="22"/>
-      <c r="BA127" s="22"/>
-      <c r="BB127" s="22"/>
-      <c r="BC127" s="22"/>
-      <c r="BD127" s="22"/>
-      <c r="BE127" s="22"/>
-      <c r="BF127" s="22"/>
-      <c r="BG127" s="22"/>
-      <c r="BH127" s="22"/>
-      <c r="BI127" s="22"/>
-      <c r="BJ127" s="22"/>
-      <c r="BK127" s="22"/>
-      <c r="BL127" s="22"/>
-      <c r="BM127" s="22"/>
-      <c r="BN127" s="22"/>
-    </row>
-    <row r="128" spans="1:66" s="7" customFormat="1" ht="18.75" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A128" s="106" t="s">
-        <v>132</v>
-      </c>
-      <c r="B128" s="106"/>
-      <c r="C128" s="106"/>
-      <c r="D128" s="106"/>
-      <c r="E128" s="106"/>
-      <c r="F128" s="106"/>
-      <c r="G128" s="106"/>
-      <c r="H128" s="106"/>
-      <c r="I128" s="106"/>
-      <c r="J128" s="106"/>
-      <c r="K128" s="106"/>
-      <c r="L128" s="106"/>
-      <c r="M128" s="106"/>
-      <c r="N128" s="106"/>
-      <c r="O128" s="106"/>
       <c r="P128" s="22"/>
       <c r="Q128" s="22"/>
       <c r="R128" s="22"/>
@@ -32506,24 +32487,24 @@
       <c r="BM128" s="22"/>
       <c r="BN128" s="22"/>
     </row>
-    <row r="129" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A129" s="107" t="s">
-        <v>146</v>
-      </c>
-      <c r="B129" s="107"/>
-      <c r="C129" s="107"/>
-      <c r="D129" s="107"/>
-      <c r="E129" s="107"/>
-      <c r="F129" s="107"/>
-      <c r="G129" s="107"/>
-      <c r="H129" s="107"/>
-      <c r="I129" s="107"/>
-      <c r="J129" s="107"/>
-      <c r="K129" s="107"/>
-      <c r="L129" s="107"/>
-      <c r="M129" s="107"/>
-      <c r="N129" s="107"/>
-      <c r="O129" s="107"/>
+    <row r="129" spans="1:66" s="7" customFormat="1" ht="18.75" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A129" s="105" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="105"/>
+      <c r="C129" s="105"/>
+      <c r="D129" s="105"/>
+      <c r="E129" s="105"/>
+      <c r="F129" s="105"/>
+      <c r="G129" s="105"/>
+      <c r="H129" s="105"/>
+      <c r="I129" s="105"/>
+      <c r="J129" s="105"/>
+      <c r="K129" s="105"/>
+      <c r="L129" s="105"/>
+      <c r="M129" s="105"/>
+      <c r="N129" s="105"/>
+      <c r="O129" s="105"/>
       <c r="P129" s="22"/>
       <c r="Q129" s="22"/>
       <c r="R129" s="22"/>
@@ -32576,305 +32557,277 @@
       <c r="BM129" s="22"/>
       <c r="BN129" s="22"/>
     </row>
-    <row r="130" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="92">
+    <row r="130" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A130" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="B130" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C130" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D130" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E130" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="F130" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="G130" s="92">
-        <v>403</v>
-      </c>
-      <c r="H130" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="I130" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J130" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K130" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L130" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M130" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N130" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O130" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="P130" s="21"/>
-      <c r="Q130" s="21"/>
-      <c r="R130" s="21"/>
-      <c r="S130" s="21"/>
-      <c r="T130" s="21"/>
-      <c r="U130" s="21"/>
-      <c r="V130" s="21"/>
-      <c r="W130" s="21"/>
-      <c r="X130" s="21"/>
-      <c r="Y130" s="21"/>
-      <c r="Z130" s="21"/>
-      <c r="AA130" s="21"/>
-      <c r="AB130" s="21"/>
-      <c r="AC130" s="21"/>
-      <c r="AD130" s="21"/>
-      <c r="AE130" s="21"/>
-      <c r="AF130" s="21"/>
-      <c r="AG130" s="21"/>
-      <c r="AH130" s="21"/>
-      <c r="AI130" s="21"/>
-      <c r="AJ130" s="21"/>
-      <c r="AK130" s="21"/>
-      <c r="AL130" s="21"/>
-      <c r="AM130" s="21"/>
-      <c r="AN130" s="21"/>
-      <c r="AO130" s="21"/>
-      <c r="AP130" s="21"/>
-      <c r="AQ130" s="21"/>
-      <c r="AR130" s="21"/>
-      <c r="AS130" s="21"/>
-      <c r="AT130" s="21"/>
-      <c r="AU130" s="21"/>
-      <c r="AV130" s="21"/>
-      <c r="AW130" s="21"/>
-      <c r="AX130" s="21"/>
-      <c r="AY130" s="21"/>
-      <c r="AZ130" s="21"/>
-      <c r="BA130" s="21"/>
-      <c r="BB130" s="21"/>
-      <c r="BC130" s="21"/>
-      <c r="BD130" s="21"/>
-      <c r="BE130" s="21"/>
-      <c r="BF130" s="21"/>
-      <c r="BG130" s="21"/>
-      <c r="BH130" s="21"/>
-      <c r="BI130" s="21"/>
-      <c r="BJ130" s="21"/>
-      <c r="BK130" s="21"/>
-      <c r="BL130" s="21"/>
-      <c r="BM130" s="21"/>
-      <c r="BN130" s="21"/>
-    </row>
-    <row r="131" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A131" s="4">
-        <v>86</v>
+      <c r="B130" s="106"/>
+      <c r="C130" s="106"/>
+      <c r="D130" s="106"/>
+      <c r="E130" s="106"/>
+      <c r="F130" s="106"/>
+      <c r="G130" s="106"/>
+      <c r="H130" s="106"/>
+      <c r="I130" s="106"/>
+      <c r="J130" s="106"/>
+      <c r="K130" s="106"/>
+      <c r="L130" s="106"/>
+      <c r="M130" s="106"/>
+      <c r="N130" s="106"/>
+      <c r="O130" s="106"/>
+      <c r="P130" s="22"/>
+      <c r="Q130" s="22"/>
+      <c r="R130" s="22"/>
+      <c r="S130" s="22"/>
+      <c r="T130" s="22"/>
+      <c r="U130" s="22"/>
+      <c r="V130" s="22"/>
+      <c r="W130" s="22"/>
+      <c r="X130" s="22"/>
+      <c r="Y130" s="22"/>
+      <c r="Z130" s="22"/>
+      <c r="AA130" s="22"/>
+      <c r="AB130" s="22"/>
+      <c r="AC130" s="22"/>
+      <c r="AD130" s="22"/>
+      <c r="AE130" s="22"/>
+      <c r="AF130" s="22"/>
+      <c r="AG130" s="22"/>
+      <c r="AH130" s="22"/>
+      <c r="AI130" s="22"/>
+      <c r="AJ130" s="22"/>
+      <c r="AK130" s="22"/>
+      <c r="AL130" s="22"/>
+      <c r="AM130" s="22"/>
+      <c r="AN130" s="22"/>
+      <c r="AO130" s="22"/>
+      <c r="AP130" s="22"/>
+      <c r="AQ130" s="22"/>
+      <c r="AR130" s="22"/>
+      <c r="AS130" s="22"/>
+      <c r="AT130" s="22"/>
+      <c r="AU130" s="22"/>
+      <c r="AV130" s="22"/>
+      <c r="AW130" s="22"/>
+      <c r="AX130" s="22"/>
+      <c r="AY130" s="22"/>
+      <c r="AZ130" s="22"/>
+      <c r="BA130" s="22"/>
+      <c r="BB130" s="22"/>
+      <c r="BC130" s="22"/>
+      <c r="BD130" s="22"/>
+      <c r="BE130" s="22"/>
+      <c r="BF130" s="22"/>
+      <c r="BG130" s="22"/>
+      <c r="BH130" s="22"/>
+      <c r="BI130" s="22"/>
+      <c r="BJ130" s="22"/>
+      <c r="BK130" s="22"/>
+      <c r="BL130" s="22"/>
+      <c r="BM130" s="22"/>
+      <c r="BN130" s="22"/>
+    </row>
+    <row r="131" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="92">
+        <v>146</v>
       </c>
       <c r="B131" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C131" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="D131" s="4" t="s">
+      <c r="C131" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D131" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E131" s="4" t="s">
+      <c r="E131" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F131" s="4" t="s">
+      <c r="F131" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G131" s="24">
-        <v>401</v>
-      </c>
-      <c r="H131" s="58" t="s">
+      <c r="G131" s="92">
+        <v>403</v>
+      </c>
+      <c r="H131" s="92" t="s">
         <v>216</v>
       </c>
       <c r="I131" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J131" s="4" t="s">
+      <c r="J131" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K131" s="4" t="s">
+      <c r="K131" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L131" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M131" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N131" s="32" t="s">
+      <c r="L131" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M131" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N131" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O131" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="O131" s="49" t="s">
+      <c r="P131" s="21"/>
+      <c r="Q131" s="21"/>
+      <c r="R131" s="21"/>
+      <c r="S131" s="21"/>
+      <c r="T131" s="21"/>
+      <c r="U131" s="21"/>
+      <c r="V131" s="21"/>
+      <c r="W131" s="21"/>
+      <c r="X131" s="21"/>
+      <c r="Y131" s="21"/>
+      <c r="Z131" s="21"/>
+      <c r="AA131" s="21"/>
+      <c r="AB131" s="21"/>
+      <c r="AC131" s="21"/>
+      <c r="AD131" s="21"/>
+      <c r="AE131" s="21"/>
+      <c r="AF131" s="21"/>
+      <c r="AG131" s="21"/>
+      <c r="AH131" s="21"/>
+      <c r="AI131" s="21"/>
+      <c r="AJ131" s="21"/>
+      <c r="AK131" s="21"/>
+      <c r="AL131" s="21"/>
+      <c r="AM131" s="21"/>
+      <c r="AN131" s="21"/>
+      <c r="AO131" s="21"/>
+      <c r="AP131" s="21"/>
+      <c r="AQ131" s="21"/>
+      <c r="AR131" s="21"/>
+      <c r="AS131" s="21"/>
+      <c r="AT131" s="21"/>
+      <c r="AU131" s="21"/>
+      <c r="AV131" s="21"/>
+      <c r="AW131" s="21"/>
+      <c r="AX131" s="21"/>
+      <c r="AY131" s="21"/>
+      <c r="AZ131" s="21"/>
+      <c r="BA131" s="21"/>
+      <c r="BB131" s="21"/>
+      <c r="BC131" s="21"/>
+      <c r="BD131" s="21"/>
+      <c r="BE131" s="21"/>
+      <c r="BF131" s="21"/>
+      <c r="BG131" s="21"/>
+      <c r="BH131" s="21"/>
+      <c r="BI131" s="21"/>
+      <c r="BJ131" s="21"/>
+      <c r="BK131" s="21"/>
+      <c r="BL131" s="21"/>
+      <c r="BM131" s="21"/>
+      <c r="BN131" s="21"/>
+    </row>
+    <row r="132" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A132" s="4">
+        <v>86</v>
+      </c>
+      <c r="B132" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C132" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="132" spans="1:66" s="22" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A132" s="92">
-        <v>87</v>
-      </c>
-      <c r="B132" s="104" t="s">
-        <v>133</v>
-      </c>
-      <c r="C132" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="D132" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E132" s="92" t="s">
+      <c r="E132" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F132" s="92" t="s">
+      <c r="F132" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G132" s="74">
+      <c r="G132" s="24">
         <v>401</v>
       </c>
       <c r="H132" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I132" s="74" t="s">
+      <c r="I132" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J132" s="92" t="s">
+      <c r="J132" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K132" s="92" t="s">
+      <c r="K132" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L132" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M132" s="103" t="s">
+      <c r="L132" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M132" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N132" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O132" s="49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:66" s="22" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A133" s="92">
+        <v>87</v>
+      </c>
+      <c r="B133" s="103" t="s">
+        <v>133</v>
+      </c>
+      <c r="C133" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="N132" s="102" t="s">
+      <c r="D133" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="O132" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A133" s="4">
-        <v>89</v>
-      </c>
-      <c r="B133" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C133" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E133" s="4" t="s">
+      <c r="E133" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F133" s="4" t="s">
+      <c r="F133" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G133" s="24">
-        <v>400</v>
+      <c r="G133" s="74">
+        <v>401</v>
       </c>
       <c r="H133" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I133" s="24" t="s">
+      <c r="I133" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J133" s="4" t="s">
+      <c r="J133" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K133" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L133" s="10">
-        <v>1003</v>
-      </c>
-      <c r="M133" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="N133" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="O133" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P133" s="22"/>
-      <c r="Q133" s="22"/>
-      <c r="R133" s="22"/>
-      <c r="S133" s="22"/>
-      <c r="T133" s="22"/>
-      <c r="U133" s="22"/>
-      <c r="V133" s="22"/>
-      <c r="W133" s="22"/>
-      <c r="X133" s="22"/>
-      <c r="Y133" s="22"/>
-      <c r="Z133" s="22"/>
-      <c r="AA133" s="22"/>
-      <c r="AB133" s="22"/>
-      <c r="AC133" s="22"/>
-      <c r="AD133" s="22"/>
-      <c r="AE133" s="22"/>
-      <c r="AF133" s="22"/>
-      <c r="AG133" s="22"/>
-      <c r="AH133" s="22"/>
-      <c r="AI133" s="22"/>
-      <c r="AJ133" s="22"/>
-      <c r="AK133" s="22"/>
-      <c r="AL133" s="22"/>
-      <c r="AM133" s="22"/>
-      <c r="AN133" s="22"/>
-      <c r="AO133" s="22"/>
-      <c r="AP133" s="22"/>
-      <c r="AQ133" s="22"/>
-      <c r="AR133" s="22"/>
-      <c r="AS133" s="22"/>
-      <c r="AT133" s="22"/>
-      <c r="AU133" s="22"/>
-      <c r="AV133" s="22"/>
-      <c r="AW133" s="22"/>
-      <c r="AX133" s="22"/>
-      <c r="AY133" s="22"/>
-      <c r="AZ133" s="22"/>
-      <c r="BA133" s="22"/>
-      <c r="BB133" s="22"/>
-      <c r="BC133" s="22"/>
-      <c r="BD133" s="22"/>
-      <c r="BE133" s="22"/>
-      <c r="BF133" s="22"/>
-      <c r="BG133" s="22"/>
-      <c r="BH133" s="22"/>
-      <c r="BI133" s="22"/>
-      <c r="BJ133" s="22"/>
-      <c r="BK133" s="22"/>
-      <c r="BL133" s="22"/>
-      <c r="BM133" s="22"/>
-      <c r="BN133" s="22"/>
-    </row>
-    <row r="134" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K133" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L133" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M133" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="N133" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="O133" s="93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B134" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="6" t="s">
-        <v>148</v>
+      <c r="C134" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>12</v>
@@ -32898,13 +32851,13 @@
         <v>7</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L134" s="10">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="M134" s="30" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N134" s="30" t="s">
         <v>134</v>
@@ -32964,15 +32917,15 @@
       <c r="BM134" s="22"/>
       <c r="BN134" s="22"/>
     </row>
-    <row r="135" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B135" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>12</v>
@@ -32996,13 +32949,13 @@
         <v>7</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L135" s="10">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="M135" s="30" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N135" s="30" t="s">
         <v>134</v>
@@ -33062,26 +33015,26 @@
       <c r="BM135" s="22"/>
       <c r="BN135" s="22"/>
     </row>
-    <row r="136" spans="1:66" s="7" customFormat="1" ht="33.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="B136" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C136" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D136" s="53" t="s">
+      <c r="C136" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E136" s="53" t="s">
+      <c r="E136" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F136" s="53" t="s">
+      <c r="F136" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G136" s="54">
+      <c r="G136" s="24">
         <v>400</v>
       </c>
       <c r="H136" s="58" t="s">
@@ -33090,23 +33043,23 @@
       <c r="I136" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J136" s="53" t="s">
+      <c r="J136" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K136" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="L136" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M136" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N136" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O136" s="63" t="s">
-        <v>12</v>
+      <c r="K136" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L136" s="10">
+        <v>1005</v>
+      </c>
+      <c r="M136" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="N136" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="O136" s="30" t="s">
+        <v>43</v>
       </c>
       <c r="P136" s="22"/>
       <c r="Q136" s="22"/>
@@ -33160,27 +33113,27 @@
       <c r="BM136" s="22"/>
       <c r="BN136" s="22"/>
     </row>
-    <row r="137" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:66" s="7" customFormat="1" ht="33.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="B137" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D137" s="4" t="s">
+      <c r="C137" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D137" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E137" s="4" t="s">
+      <c r="E137" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F137" s="4" t="s">
+      <c r="F137" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G137" s="24">
-        <v>404</v>
+      <c r="G137" s="54">
+        <v>400</v>
       </c>
       <c r="H137" s="58" t="s">
         <v>216</v>
@@ -33188,85 +33141,85 @@
       <c r="I137" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J137" s="4" t="s">
+      <c r="J137" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K137" s="4" t="s">
+      <c r="K137" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L137" s="10">
-        <v>1006</v>
-      </c>
-      <c r="M137" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="N137" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="O137" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="P137" s="21"/>
-      <c r="Q137" s="21"/>
-      <c r="R137" s="21"/>
-      <c r="S137" s="21"/>
-      <c r="T137" s="21"/>
-      <c r="U137" s="21"/>
-      <c r="V137" s="21"/>
-      <c r="W137" s="21"/>
-      <c r="X137" s="21"/>
-      <c r="Y137" s="21"/>
-      <c r="Z137" s="21"/>
-      <c r="AA137" s="21"/>
-      <c r="AB137" s="21"/>
-      <c r="AC137" s="21"/>
-      <c r="AD137" s="21"/>
-      <c r="AE137" s="21"/>
-      <c r="AF137" s="21"/>
-      <c r="AG137" s="21"/>
-      <c r="AH137" s="21"/>
-      <c r="AI137" s="21"/>
-      <c r="AJ137" s="21"/>
-      <c r="AK137" s="21"/>
-      <c r="AL137" s="21"/>
-      <c r="AM137" s="21"/>
-      <c r="AN137" s="21"/>
-      <c r="AO137" s="21"/>
-      <c r="AP137" s="21"/>
-      <c r="AQ137" s="21"/>
-      <c r="AR137" s="21"/>
-      <c r="AS137" s="21"/>
-      <c r="AT137" s="21"/>
-      <c r="AU137" s="21"/>
-      <c r="AV137" s="21"/>
-      <c r="AW137" s="21"/>
-      <c r="AX137" s="21"/>
-      <c r="AY137" s="21"/>
-      <c r="AZ137" s="21"/>
-      <c r="BA137" s="21"/>
-      <c r="BB137" s="21"/>
-      <c r="BC137" s="21"/>
-      <c r="BD137" s="21"/>
-      <c r="BE137" s="21"/>
-      <c r="BF137" s="21"/>
-      <c r="BG137" s="21"/>
-      <c r="BH137" s="21"/>
-      <c r="BI137" s="21"/>
-      <c r="BJ137" s="21"/>
-      <c r="BK137" s="21"/>
-      <c r="BL137" s="21"/>
-      <c r="BM137" s="21"/>
-      <c r="BN137" s="21"/>
-    </row>
-    <row r="138" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="L137" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M137" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N137" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O137" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P137" s="22"/>
+      <c r="Q137" s="22"/>
+      <c r="R137" s="22"/>
+      <c r="S137" s="22"/>
+      <c r="T137" s="22"/>
+      <c r="U137" s="22"/>
+      <c r="V137" s="22"/>
+      <c r="W137" s="22"/>
+      <c r="X137" s="22"/>
+      <c r="Y137" s="22"/>
+      <c r="Z137" s="22"/>
+      <c r="AA137" s="22"/>
+      <c r="AB137" s="22"/>
+      <c r="AC137" s="22"/>
+      <c r="AD137" s="22"/>
+      <c r="AE137" s="22"/>
+      <c r="AF137" s="22"/>
+      <c r="AG137" s="22"/>
+      <c r="AH137" s="22"/>
+      <c r="AI137" s="22"/>
+      <c r="AJ137" s="22"/>
+      <c r="AK137" s="22"/>
+      <c r="AL137" s="22"/>
+      <c r="AM137" s="22"/>
+      <c r="AN137" s="22"/>
+      <c r="AO137" s="22"/>
+      <c r="AP137" s="22"/>
+      <c r="AQ137" s="22"/>
+      <c r="AR137" s="22"/>
+      <c r="AS137" s="22"/>
+      <c r="AT137" s="22"/>
+      <c r="AU137" s="22"/>
+      <c r="AV137" s="22"/>
+      <c r="AW137" s="22"/>
+      <c r="AX137" s="22"/>
+      <c r="AY137" s="22"/>
+      <c r="AZ137" s="22"/>
+      <c r="BA137" s="22"/>
+      <c r="BB137" s="22"/>
+      <c r="BC137" s="22"/>
+      <c r="BD137" s="22"/>
+      <c r="BE137" s="22"/>
+      <c r="BF137" s="22"/>
+      <c r="BG137" s="22"/>
+      <c r="BH137" s="22"/>
+      <c r="BI137" s="22"/>
+      <c r="BJ137" s="22"/>
+      <c r="BK137" s="22"/>
+      <c r="BL137" s="22"/>
+      <c r="BM137" s="22"/>
+      <c r="BN137" s="22"/>
+    </row>
+    <row r="138" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B138" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>12</v>
@@ -33290,13 +33243,13 @@
         <v>7</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L138" s="10">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="M138" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N138" s="30" t="s">
         <v>134</v>
@@ -33304,16 +33257,67 @@
       <c r="O138" s="30" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="139" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="P138" s="21"/>
+      <c r="Q138" s="21"/>
+      <c r="R138" s="21"/>
+      <c r="S138" s="21"/>
+      <c r="T138" s="21"/>
+      <c r="U138" s="21"/>
+      <c r="V138" s="21"/>
+      <c r="W138" s="21"/>
+      <c r="X138" s="21"/>
+      <c r="Y138" s="21"/>
+      <c r="Z138" s="21"/>
+      <c r="AA138" s="21"/>
+      <c r="AB138" s="21"/>
+      <c r="AC138" s="21"/>
+      <c r="AD138" s="21"/>
+      <c r="AE138" s="21"/>
+      <c r="AF138" s="21"/>
+      <c r="AG138" s="21"/>
+      <c r="AH138" s="21"/>
+      <c r="AI138" s="21"/>
+      <c r="AJ138" s="21"/>
+      <c r="AK138" s="21"/>
+      <c r="AL138" s="21"/>
+      <c r="AM138" s="21"/>
+      <c r="AN138" s="21"/>
+      <c r="AO138" s="21"/>
+      <c r="AP138" s="21"/>
+      <c r="AQ138" s="21"/>
+      <c r="AR138" s="21"/>
+      <c r="AS138" s="21"/>
+      <c r="AT138" s="21"/>
+      <c r="AU138" s="21"/>
+      <c r="AV138" s="21"/>
+      <c r="AW138" s="21"/>
+      <c r="AX138" s="21"/>
+      <c r="AY138" s="21"/>
+      <c r="AZ138" s="21"/>
+      <c r="BA138" s="21"/>
+      <c r="BB138" s="21"/>
+      <c r="BC138" s="21"/>
+      <c r="BD138" s="21"/>
+      <c r="BE138" s="21"/>
+      <c r="BF138" s="21"/>
+      <c r="BG138" s="21"/>
+      <c r="BH138" s="21"/>
+      <c r="BI138" s="21"/>
+      <c r="BJ138" s="21"/>
+      <c r="BK138" s="21"/>
+      <c r="BL138" s="21"/>
+      <c r="BM138" s="21"/>
+      <c r="BN138" s="21"/>
+    </row>
+    <row r="139" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B139" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>12</v>
@@ -33325,7 +33329,7 @@
         <v>140</v>
       </c>
       <c r="G139" s="24">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H139" s="58" t="s">
         <v>216</v>
@@ -33340,10 +33344,10 @@
         <v>30</v>
       </c>
       <c r="L139" s="10">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M139" s="30" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N139" s="30" t="s">
         <v>134</v>
@@ -33352,15 +33356,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A140" s="26">
-        <v>141</v>
+    <row r="140" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A140" s="4">
+        <v>94</v>
       </c>
       <c r="B140" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C140" s="84" t="s">
-        <v>229</v>
+      <c r="C140" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>12</v>
@@ -33368,11 +33372,11 @@
       <c r="E140" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F140" s="26" t="s">
+      <c r="F140" s="4" t="s">
         <v>140</v>
       </c>
       <c r="G140" s="24">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H140" s="58" t="s">
         <v>216</v>
@@ -33386,113 +33390,64 @@
       <c r="K140" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L140" s="26">
-        <v>3013</v>
-      </c>
-      <c r="M140" s="84" t="s">
-        <v>230</v>
+      <c r="L140" s="10">
+        <v>1008</v>
+      </c>
+      <c r="M140" s="30" t="s">
+        <v>16</v>
       </c>
       <c r="N140" s="30" t="s">
         <v>134</v>
       </c>
       <c r="O140" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="P140" s="21"/>
-      <c r="Q140" s="21"/>
-      <c r="R140" s="21"/>
-      <c r="S140" s="21"/>
-      <c r="T140" s="21"/>
-      <c r="U140" s="21"/>
-      <c r="V140" s="21"/>
-      <c r="W140" s="21"/>
-      <c r="X140" s="21"/>
-      <c r="Y140" s="21"/>
-      <c r="Z140" s="21"/>
-      <c r="AA140" s="21"/>
-      <c r="AB140" s="21"/>
-      <c r="AC140" s="21"/>
-      <c r="AD140" s="21"/>
-      <c r="AE140" s="21"/>
-      <c r="AF140" s="21"/>
-      <c r="AG140" s="21"/>
-      <c r="AH140" s="21"/>
-      <c r="AI140" s="21"/>
-      <c r="AJ140" s="21"/>
-      <c r="AK140" s="21"/>
-      <c r="AL140" s="21"/>
-      <c r="AM140" s="21"/>
-      <c r="AN140" s="21"/>
-      <c r="AO140" s="21"/>
-      <c r="AP140" s="21"/>
-      <c r="AQ140" s="21"/>
-      <c r="AR140" s="21"/>
-      <c r="AS140" s="21"/>
-      <c r="AT140" s="21"/>
-      <c r="AU140" s="21"/>
-      <c r="AV140" s="21"/>
-      <c r="AW140" s="21"/>
-      <c r="AX140" s="21"/>
-      <c r="AY140" s="21"/>
-      <c r="AZ140" s="21"/>
-      <c r="BA140" s="21"/>
-      <c r="BB140" s="21"/>
-      <c r="BC140" s="21"/>
-      <c r="BD140" s="21"/>
-      <c r="BE140" s="21"/>
-      <c r="BF140" s="21"/>
-      <c r="BG140" s="21"/>
-      <c r="BH140" s="21"/>
-      <c r="BI140" s="21"/>
-      <c r="BJ140" s="21"/>
-      <c r="BK140" s="21"/>
-      <c r="BL140" s="21"/>
-      <c r="BM140" s="21"/>
-      <c r="BN140" s="21"/>
+        <v>59</v>
+      </c>
     </row>
     <row r="141" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A141" s="26"/>
+      <c r="A141" s="26">
+        <v>141</v>
+      </c>
       <c r="B141" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C141" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="D141" s="24" t="s">
+      <c r="C141" s="84" t="s">
+        <v>229</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E141" s="24" t="s">
+      <c r="E141" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F141" s="24" t="s">
+      <c r="F141" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="G141" s="44">
-        <v>403</v>
-      </c>
-      <c r="H141" s="24" t="s">
+      <c r="G141" s="24">
+        <v>400</v>
+      </c>
+      <c r="H141" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I141" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J141" s="24" t="s">
+      <c r="J141" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K141" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L141" s="24">
-        <v>1011</v>
-      </c>
-      <c r="M141" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="N141" s="32" t="s">
-        <v>55</v>
+      <c r="K141" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L141" s="26">
+        <v>3013</v>
+      </c>
+      <c r="M141" s="84" t="s">
+        <v>230</v>
+      </c>
+      <c r="N141" s="30" t="s">
+        <v>134</v>
       </c>
       <c r="O141" s="30" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="P141" s="21"/>
       <c r="Q141" s="21"/>
@@ -33546,64 +33501,113 @@
       <c r="BM141" s="21"/>
       <c r="BN141" s="21"/>
     </row>
-    <row r="142" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A142" s="4">
-        <v>95</v>
-      </c>
+    <row r="142" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A142" s="26"/>
       <c r="B142" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>203</v>
+      <c r="C142" s="23" t="s">
+        <v>295</v>
       </c>
       <c r="D142" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E142" s="4" t="s">
+      <c r="E142" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F142" s="4" t="s">
+      <c r="F142" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G142" s="24">
+      <c r="G142" s="44">
         <v>403</v>
       </c>
-      <c r="H142" s="58" t="s">
+      <c r="H142" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I142" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J142" s="4" t="s">
+      <c r="J142" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K142" s="4" t="s">
+      <c r="K142" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="L142" s="4">
+      <c r="L142" s="24">
         <v>1011</v>
       </c>
       <c r="M142" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N142" s="30" t="s">
-        <v>134</v>
+      <c r="N142" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O142" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="P142" s="21"/>
+      <c r="Q142" s="21"/>
+      <c r="R142" s="21"/>
+      <c r="S142" s="21"/>
+      <c r="T142" s="21"/>
+      <c r="U142" s="21"/>
+      <c r="V142" s="21"/>
+      <c r="W142" s="21"/>
+      <c r="X142" s="21"/>
+      <c r="Y142" s="21"/>
+      <c r="Z142" s="21"/>
+      <c r="AA142" s="21"/>
+      <c r="AB142" s="21"/>
+      <c r="AC142" s="21"/>
+      <c r="AD142" s="21"/>
+      <c r="AE142" s="21"/>
+      <c r="AF142" s="21"/>
+      <c r="AG142" s="21"/>
+      <c r="AH142" s="21"/>
+      <c r="AI142" s="21"/>
+      <c r="AJ142" s="21"/>
+      <c r="AK142" s="21"/>
+      <c r="AL142" s="21"/>
+      <c r="AM142" s="21"/>
+      <c r="AN142" s="21"/>
+      <c r="AO142" s="21"/>
+      <c r="AP142" s="21"/>
+      <c r="AQ142" s="21"/>
+      <c r="AR142" s="21"/>
+      <c r="AS142" s="21"/>
+      <c r="AT142" s="21"/>
+      <c r="AU142" s="21"/>
+      <c r="AV142" s="21"/>
+      <c r="AW142" s="21"/>
+      <c r="AX142" s="21"/>
+      <c r="AY142" s="21"/>
+      <c r="AZ142" s="21"/>
+      <c r="BA142" s="21"/>
+      <c r="BB142" s="21"/>
+      <c r="BC142" s="21"/>
+      <c r="BD142" s="21"/>
+      <c r="BE142" s="21"/>
+      <c r="BF142" s="21"/>
+      <c r="BG142" s="21"/>
+      <c r="BH142" s="21"/>
+      <c r="BI142" s="21"/>
+      <c r="BJ142" s="21"/>
+      <c r="BK142" s="21"/>
+      <c r="BL142" s="21"/>
+      <c r="BM142" s="21"/>
+      <c r="BN142" s="21"/>
+    </row>
+    <row r="143" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B143" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D143" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D143" s="24" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="4" t="s">
@@ -33613,7 +33617,7 @@
         <v>140</v>
       </c>
       <c r="G143" s="24">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H143" s="58" t="s">
         <v>216</v>
@@ -33627,234 +33631,234 @@
       <c r="K143" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L143" s="10">
-        <v>4001</v>
-      </c>
-      <c r="M143" s="30" t="s">
-        <v>19</v>
+      <c r="L143" s="4">
+        <v>1011</v>
+      </c>
+      <c r="M143" s="32" t="s">
+        <v>202</v>
       </c>
       <c r="N143" s="30" t="s">
         <v>134</v>
       </c>
       <c r="O143" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="P143" s="22"/>
-      <c r="Q143" s="22"/>
-      <c r="R143" s="22"/>
-      <c r="S143" s="22"/>
-      <c r="T143" s="22"/>
-      <c r="U143" s="22"/>
-      <c r="V143" s="22"/>
-      <c r="W143" s="22"/>
-      <c r="X143" s="22"/>
-      <c r="Y143" s="22"/>
-      <c r="Z143" s="22"/>
-      <c r="AA143" s="22"/>
-      <c r="AB143" s="22"/>
-      <c r="AC143" s="22"/>
-      <c r="AD143" s="22"/>
-      <c r="AE143" s="22"/>
-      <c r="AF143" s="22"/>
-      <c r="AG143" s="22"/>
-      <c r="AH143" s="22"/>
-      <c r="AI143" s="22"/>
-      <c r="AJ143" s="22"/>
-      <c r="AK143" s="22"/>
-      <c r="AL143" s="22"/>
-      <c r="AM143" s="22"/>
-      <c r="AN143" s="22"/>
-      <c r="AO143" s="22"/>
-      <c r="AP143" s="22"/>
-      <c r="AQ143" s="22"/>
-      <c r="AR143" s="22"/>
-      <c r="AS143" s="22"/>
-      <c r="AT143" s="22"/>
-      <c r="AU143" s="22"/>
-      <c r="AV143" s="22"/>
-      <c r="AW143" s="22"/>
-      <c r="AX143" s="22"/>
-      <c r="AY143" s="22"/>
-      <c r="AZ143" s="22"/>
-      <c r="BA143" s="22"/>
-      <c r="BB143" s="22"/>
-      <c r="BC143" s="22"/>
-      <c r="BD143" s="22"/>
-      <c r="BE143" s="22"/>
-      <c r="BF143" s="22"/>
-      <c r="BG143" s="22"/>
-      <c r="BH143" s="22"/>
-      <c r="BI143" s="22"/>
-      <c r="BJ143" s="22"/>
-      <c r="BK143" s="22"/>
-      <c r="BL143" s="22"/>
-      <c r="BM143" s="22"/>
-      <c r="BN143" s="22"/>
-    </row>
-    <row r="144" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A144" s="26">
-        <v>142</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A144" s="4">
+        <v>96</v>
       </c>
       <c r="B144" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C144" s="84" t="s">
+      <c r="C144" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G144" s="24">
+        <v>400</v>
+      </c>
+      <c r="H144" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="I144" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J144" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K144" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L144" s="10">
+        <v>4001</v>
+      </c>
+      <c r="M144" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="N144" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="O144" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="P144" s="22"/>
+      <c r="Q144" s="22"/>
+      <c r="R144" s="22"/>
+      <c r="S144" s="22"/>
+      <c r="T144" s="22"/>
+      <c r="U144" s="22"/>
+      <c r="V144" s="22"/>
+      <c r="W144" s="22"/>
+      <c r="X144" s="22"/>
+      <c r="Y144" s="22"/>
+      <c r="Z144" s="22"/>
+      <c r="AA144" s="22"/>
+      <c r="AB144" s="22"/>
+      <c r="AC144" s="22"/>
+      <c r="AD144" s="22"/>
+      <c r="AE144" s="22"/>
+      <c r="AF144" s="22"/>
+      <c r="AG144" s="22"/>
+      <c r="AH144" s="22"/>
+      <c r="AI144" s="22"/>
+      <c r="AJ144" s="22"/>
+      <c r="AK144" s="22"/>
+      <c r="AL144" s="22"/>
+      <c r="AM144" s="22"/>
+      <c r="AN144" s="22"/>
+      <c r="AO144" s="22"/>
+      <c r="AP144" s="22"/>
+      <c r="AQ144" s="22"/>
+      <c r="AR144" s="22"/>
+      <c r="AS144" s="22"/>
+      <c r="AT144" s="22"/>
+      <c r="AU144" s="22"/>
+      <c r="AV144" s="22"/>
+      <c r="AW144" s="22"/>
+      <c r="AX144" s="22"/>
+      <c r="AY144" s="22"/>
+      <c r="AZ144" s="22"/>
+      <c r="BA144" s="22"/>
+      <c r="BB144" s="22"/>
+      <c r="BC144" s="22"/>
+      <c r="BD144" s="22"/>
+      <c r="BE144" s="22"/>
+      <c r="BF144" s="22"/>
+      <c r="BG144" s="22"/>
+      <c r="BH144" s="22"/>
+      <c r="BI144" s="22"/>
+      <c r="BJ144" s="22"/>
+      <c r="BK144" s="22"/>
+      <c r="BL144" s="22"/>
+      <c r="BM144" s="22"/>
+      <c r="BN144" s="22"/>
+    </row>
+    <row r="145" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A145" s="26">
+        <v>142</v>
+      </c>
+      <c r="B145" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C145" s="84" t="s">
         <v>236</v>
       </c>
-      <c r="D144" s="26"/>
-      <c r="E144" s="26"/>
-      <c r="F144" s="26"/>
-      <c r="G144" s="65">
+      <c r="D145" s="26"/>
+      <c r="E145" s="26"/>
+      <c r="F145" s="26"/>
+      <c r="G145" s="65">
         <v>413</v>
       </c>
-      <c r="H144" s="65" t="s">
+      <c r="H145" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="I144" s="65"/>
-      <c r="J144" s="58" t="s">
+      <c r="I145" s="65"/>
+      <c r="J145" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K144" s="26"/>
-      <c r="L144" s="26"/>
-      <c r="M144" s="84" t="s">
+      <c r="K145" s="26"/>
+      <c r="L145" s="26"/>
+      <c r="M145" s="84" t="s">
         <v>236</v>
       </c>
-      <c r="N144" s="33"/>
-      <c r="O144" s="33"/>
-    </row>
-    <row r="145" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="8">
+      <c r="N145" s="33"/>
+      <c r="O145" s="33"/>
+    </row>
+    <row r="146" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="8">
         <v>169</v>
       </c>
-      <c r="B145" s="31" t="s">
+      <c r="B146" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C145" s="31" t="s">
+      <c r="C146" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="D145" s="58" t="s">
+      <c r="D146" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E145" s="8" t="s">
+      <c r="E146" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F145" s="8" t="s">
+      <c r="F146" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G145" s="8">
+      <c r="G146" s="8">
         <v>401</v>
       </c>
-      <c r="H145" s="54" t="s">
+      <c r="H146" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="I145" s="24" t="s">
+      <c r="I146" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J145" s="92" t="s">
+      <c r="J146" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K145" s="92" t="s">
+      <c r="K146" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L145" s="8">
+      <c r="L146" s="8">
         <v>1014</v>
       </c>
-      <c r="M145" s="31" t="s">
+      <c r="M146" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="N145" s="64" t="s">
+      <c r="N146" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O145" s="64" t="s">
+      <c r="O146" s="64" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A146" s="107" t="s">
+    <row r="147" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A147" s="106" t="s">
         <v>145</v>
       </c>
-      <c r="B146" s="107"/>
-      <c r="C146" s="107"/>
-      <c r="D146" s="107"/>
-      <c r="E146" s="107"/>
-      <c r="F146" s="107"/>
-      <c r="G146" s="107"/>
-      <c r="H146" s="107"/>
-      <c r="I146" s="107"/>
-      <c r="J146" s="107"/>
-      <c r="K146" s="107"/>
-      <c r="L146" s="107"/>
-      <c r="M146" s="107"/>
-      <c r="N146" s="107"/>
-      <c r="O146" s="107"/>
-    </row>
-    <row r="147" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="4">
+      <c r="B147" s="106"/>
+      <c r="C147" s="106"/>
+      <c r="D147" s="106"/>
+      <c r="E147" s="106"/>
+      <c r="F147" s="106"/>
+      <c r="G147" s="106"/>
+      <c r="H147" s="106"/>
+      <c r="I147" s="106"/>
+      <c r="J147" s="106"/>
+      <c r="K147" s="106"/>
+      <c r="L147" s="106"/>
+      <c r="M147" s="106"/>
+      <c r="N147" s="106"/>
+      <c r="O147" s="106"/>
+    </row>
+    <row r="148" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A148" s="4">
         <v>154</v>
-      </c>
-      <c r="B147" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="C147" s="49" t="s">
-        <v>274</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G147" s="4">
-        <v>200</v>
-      </c>
-      <c r="H147" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="I147" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="J147" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K147" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L147" s="4">
-        <v>4006</v>
-      </c>
-      <c r="M147" s="49" t="s">
-        <v>274</v>
-      </c>
-      <c r="N147" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="O147" s="49" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="148" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="8">
-        <v>151</v>
       </c>
       <c r="B148" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C148" s="96" t="s">
-        <v>268</v>
+      <c r="C148" s="49" t="s">
+        <v>274</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="E148" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="F148" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G148" s="38">
+      <c r="G148" s="4">
         <v>200</v>
       </c>
       <c r="H148" s="24" t="s">
@@ -33869,28 +33873,28 @@
       <c r="K148" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L148" s="8">
-        <v>4005</v>
-      </c>
-      <c r="M148" s="96" t="s">
-        <v>268</v>
+      <c r="L148" s="4">
+        <v>4006</v>
+      </c>
+      <c r="M148" s="49" t="s">
+        <v>274</v>
       </c>
       <c r="N148" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O148" s="96" t="s">
-        <v>267</v>
+      <c r="O148" s="49" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="4">
-        <v>97</v>
+      <c r="A149" s="8">
+        <v>151</v>
       </c>
       <c r="B149" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C149" s="23" t="s">
-        <v>85</v>
+      <c r="C149" s="96" t="s">
+        <v>268</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>12</v>
@@ -33913,33 +33917,33 @@
       <c r="J149" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K149" s="5" t="s">
-        <v>30</v>
+      <c r="K149" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="L149" s="8">
-        <v>4002</v>
-      </c>
-      <c r="M149" s="32" t="s">
-        <v>38</v>
+        <v>4005</v>
+      </c>
+      <c r="M149" s="96" t="s">
+        <v>268</v>
       </c>
       <c r="N149" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O149" s="31" t="s">
-        <v>62</v>
+      <c r="O149" s="96" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="150" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B150" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C150" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D150" s="26" t="s">
+      <c r="C150" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D150" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -33960,31 +33964,31 @@
       <c r="J150" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K150" s="26" t="s">
+      <c r="K150" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L150" s="26">
-        <v>4003</v>
+      <c r="L150" s="8">
+        <v>4002</v>
       </c>
       <c r="M150" s="32" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="N150" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O150" s="33" t="s">
-        <v>1</v>
+      <c r="O150" s="31" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="151" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B151" s="31" t="s">
         <v>133</v>
       </c>
       <c r="C151" s="27" t="s">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="D151" s="26" t="s">
         <v>12</v>
@@ -34011,35 +34015,35 @@
         <v>30</v>
       </c>
       <c r="L151" s="26">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="M151" s="32" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="N151" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O151" s="31" t="s">
-        <v>184</v>
+      <c r="O151" s="33" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B152" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D152" s="4">
-        <v>8</v>
-      </c>
-      <c r="E152" s="24" t="s">
+      <c r="C152" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="D152" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F152" s="24" t="s">
+      <c r="F152" s="5" t="s">
         <v>140</v>
       </c>
       <c r="G152" s="38">
@@ -34051,311 +34055,311 @@
       <c r="I152" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="J152" s="4" t="s">
+      <c r="J152" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K152" s="4" t="s">
+      <c r="K152" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="L152" s="26">
+        <v>4004</v>
+      </c>
+      <c r="M152" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="N152" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="O152" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="153" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="4">
+        <v>99</v>
+      </c>
+      <c r="B153" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D153" s="4">
+        <v>8</v>
+      </c>
+      <c r="E153" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F153" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G153" s="38">
+        <v>200</v>
+      </c>
+      <c r="H153" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="I153" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="J153" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K153" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L152" s="4">
+      <c r="L153" s="4">
         <v>1010</v>
       </c>
-      <c r="M152" s="30" t="s">
+      <c r="M153" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="N152" s="30" t="s">
+      <c r="N153" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="O152" s="30" t="s">
+      <c r="O153" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:66" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="106" t="s">
+    <row r="154" spans="1:66" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A154" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="B153" s="106"/>
-      <c r="C153" s="106"/>
-      <c r="D153" s="106"/>
-      <c r="E153" s="106"/>
-      <c r="F153" s="106"/>
-      <c r="G153" s="106"/>
-      <c r="H153" s="106"/>
-      <c r="I153" s="106"/>
-      <c r="J153" s="106"/>
-      <c r="K153" s="106"/>
-      <c r="L153" s="106"/>
-      <c r="M153" s="106"/>
-      <c r="N153" s="106"/>
-      <c r="O153" s="106"/>
-    </row>
-    <row r="154" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A154" s="107" t="s">
+      <c r="B154" s="105"/>
+      <c r="C154" s="105"/>
+      <c r="D154" s="105"/>
+      <c r="E154" s="105"/>
+      <c r="F154" s="105"/>
+      <c r="G154" s="105"/>
+      <c r="H154" s="105"/>
+      <c r="I154" s="105"/>
+      <c r="J154" s="105"/>
+      <c r="K154" s="105"/>
+      <c r="L154" s="105"/>
+      <c r="M154" s="105"/>
+      <c r="N154" s="105"/>
+      <c r="O154" s="105"/>
+    </row>
+    <row r="155" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A155" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="B154" s="107"/>
-      <c r="C154" s="107"/>
-      <c r="D154" s="107"/>
-      <c r="E154" s="107"/>
-      <c r="F154" s="107"/>
-      <c r="G154" s="107"/>
-      <c r="H154" s="107"/>
-      <c r="I154" s="107"/>
-      <c r="J154" s="107"/>
-      <c r="K154" s="107"/>
-      <c r="L154" s="107"/>
-      <c r="M154" s="107"/>
-      <c r="N154" s="107"/>
-      <c r="O154" s="107"/>
-    </row>
-    <row r="155" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="92">
+      <c r="B155" s="106"/>
+      <c r="C155" s="106"/>
+      <c r="D155" s="106"/>
+      <c r="E155" s="106"/>
+      <c r="F155" s="106"/>
+      <c r="G155" s="106"/>
+      <c r="H155" s="106"/>
+      <c r="I155" s="106"/>
+      <c r="J155" s="106"/>
+      <c r="K155" s="106"/>
+      <c r="L155" s="106"/>
+      <c r="M155" s="106"/>
+      <c r="N155" s="106"/>
+      <c r="O155" s="106"/>
+    </row>
+    <row r="156" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="92">
         <v>146</v>
-      </c>
-      <c r="B155" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="C155" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D155" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E155" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="F155" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="G155" s="92">
-        <v>403</v>
-      </c>
-      <c r="H155" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="I155" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J155" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K155" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L155" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M155" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N155" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O155" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="P155" s="21"/>
-      <c r="Q155" s="21"/>
-      <c r="R155" s="21"/>
-      <c r="S155" s="21"/>
-      <c r="T155" s="21"/>
-      <c r="U155" s="21"/>
-      <c r="V155" s="21"/>
-      <c r="W155" s="21"/>
-      <c r="X155" s="21"/>
-      <c r="Y155" s="21"/>
-      <c r="Z155" s="21"/>
-      <c r="AA155" s="21"/>
-      <c r="AB155" s="21"/>
-      <c r="AC155" s="21"/>
-      <c r="AD155" s="21"/>
-      <c r="AE155" s="21"/>
-      <c r="AF155" s="21"/>
-      <c r="AG155" s="21"/>
-      <c r="AH155" s="21"/>
-      <c r="AI155" s="21"/>
-      <c r="AJ155" s="21"/>
-      <c r="AK155" s="21"/>
-      <c r="AL155" s="21"/>
-      <c r="AM155" s="21"/>
-      <c r="AN155" s="21"/>
-      <c r="AO155" s="21"/>
-      <c r="AP155" s="21"/>
-      <c r="AQ155" s="21"/>
-      <c r="AR155" s="21"/>
-      <c r="AS155" s="21"/>
-      <c r="AT155" s="21"/>
-      <c r="AU155" s="21"/>
-      <c r="AV155" s="21"/>
-      <c r="AW155" s="21"/>
-      <c r="AX155" s="21"/>
-      <c r="AY155" s="21"/>
-      <c r="AZ155" s="21"/>
-      <c r="BA155" s="21"/>
-      <c r="BB155" s="21"/>
-      <c r="BC155" s="21"/>
-      <c r="BD155" s="21"/>
-      <c r="BE155" s="21"/>
-      <c r="BF155" s="21"/>
-      <c r="BG155" s="21"/>
-      <c r="BH155" s="21"/>
-      <c r="BI155" s="21"/>
-      <c r="BJ155" s="21"/>
-      <c r="BK155" s="21"/>
-      <c r="BL155" s="21"/>
-      <c r="BM155" s="21"/>
-      <c r="BN155" s="21"/>
-    </row>
-    <row r="156" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A156" s="4">
-        <v>102</v>
       </c>
       <c r="B156" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C156" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D156" s="4" t="s">
+      <c r="C156" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D156" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E156" s="4" t="s">
+      <c r="E156" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F156" s="4" t="s">
+      <c r="F156" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G156" s="24">
-        <v>401</v>
-      </c>
-      <c r="H156" s="65" t="s">
+      <c r="G156" s="92">
+        <v>403</v>
+      </c>
+      <c r="H156" s="92" t="s">
         <v>216</v>
       </c>
       <c r="I156" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J156" s="4" t="s">
+      <c r="J156" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K156" s="4" t="s">
+      <c r="K156" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L156" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M156" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N156" s="32" t="s">
+      <c r="L156" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M156" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N156" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O156" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="O156" s="49" t="s">
+      <c r="P156" s="21"/>
+      <c r="Q156" s="21"/>
+      <c r="R156" s="21"/>
+      <c r="S156" s="21"/>
+      <c r="T156" s="21"/>
+      <c r="U156" s="21"/>
+      <c r="V156" s="21"/>
+      <c r="W156" s="21"/>
+      <c r="X156" s="21"/>
+      <c r="Y156" s="21"/>
+      <c r="Z156" s="21"/>
+      <c r="AA156" s="21"/>
+      <c r="AB156" s="21"/>
+      <c r="AC156" s="21"/>
+      <c r="AD156" s="21"/>
+      <c r="AE156" s="21"/>
+      <c r="AF156" s="21"/>
+      <c r="AG156" s="21"/>
+      <c r="AH156" s="21"/>
+      <c r="AI156" s="21"/>
+      <c r="AJ156" s="21"/>
+      <c r="AK156" s="21"/>
+      <c r="AL156" s="21"/>
+      <c r="AM156" s="21"/>
+      <c r="AN156" s="21"/>
+      <c r="AO156" s="21"/>
+      <c r="AP156" s="21"/>
+      <c r="AQ156" s="21"/>
+      <c r="AR156" s="21"/>
+      <c r="AS156" s="21"/>
+      <c r="AT156" s="21"/>
+      <c r="AU156" s="21"/>
+      <c r="AV156" s="21"/>
+      <c r="AW156" s="21"/>
+      <c r="AX156" s="21"/>
+      <c r="AY156" s="21"/>
+      <c r="AZ156" s="21"/>
+      <c r="BA156" s="21"/>
+      <c r="BB156" s="21"/>
+      <c r="BC156" s="21"/>
+      <c r="BD156" s="21"/>
+      <c r="BE156" s="21"/>
+      <c r="BF156" s="21"/>
+      <c r="BG156" s="21"/>
+      <c r="BH156" s="21"/>
+      <c r="BI156" s="21"/>
+      <c r="BJ156" s="21"/>
+      <c r="BK156" s="21"/>
+      <c r="BL156" s="21"/>
+      <c r="BM156" s="21"/>
+      <c r="BN156" s="21"/>
+    </row>
+    <row r="157" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A157" s="4">
+        <v>102</v>
+      </c>
+      <c r="B157" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C157" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="157" spans="1:66" s="22" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="92">
-        <v>103</v>
-      </c>
-      <c r="B157" s="102" t="s">
-        <v>174</v>
-      </c>
-      <c r="C157" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="D157" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E157" s="92" t="s">
+      <c r="E157" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F157" s="92" t="s">
+      <c r="F157" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G157" s="74">
+      <c r="G157" s="24">
         <v>401</v>
       </c>
       <c r="H157" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="I157" s="74" t="s">
+      <c r="I157" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J157" s="92" t="s">
+      <c r="J157" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K157" s="92" t="s">
+      <c r="K157" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L157" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M157" s="103" t="s">
+      <c r="L157" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M157" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N157" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O157" s="49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:66" s="22" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A158" s="92">
+        <v>103</v>
+      </c>
+      <c r="B158" s="101" t="s">
+        <v>174</v>
+      </c>
+      <c r="C158" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="N157" s="102" t="s">
+      <c r="D158" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="O157" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="4">
-        <v>105</v>
-      </c>
-      <c r="B158" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="C158" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="D158" s="24">
-        <v>201</v>
-      </c>
-      <c r="E158" s="24" t="s">
+      <c r="E158" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F158" s="24" t="s">
+      <c r="F158" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G158" s="44">
-        <v>400</v>
+      <c r="G158" s="74">
+        <v>401</v>
       </c>
       <c r="H158" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="I158" s="24" t="s">
+      <c r="I158" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J158" s="24" t="s">
+      <c r="J158" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K158" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L158" s="40">
-        <v>1003</v>
-      </c>
-      <c r="M158" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="N158" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="O158" s="32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="159" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="K158" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L158" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M158" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="N158" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="O158" s="93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B159" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C159" s="23" t="s">
-        <v>148</v>
+        <v>264</v>
       </c>
       <c r="D159" s="24">
         <v>201</v>
@@ -34366,7 +34370,7 @@
       <c r="F159" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G159" s="24">
+      <c r="G159" s="44">
         <v>400</v>
       </c>
       <c r="H159" s="65" t="s">
@@ -34379,13 +34383,13 @@
         <v>7</v>
       </c>
       <c r="K159" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="L159" s="25">
-        <v>1004</v>
+        <v>30</v>
+      </c>
+      <c r="L159" s="40">
+        <v>1003</v>
       </c>
       <c r="M159" s="32" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N159" s="32" t="s">
         <v>55</v>
@@ -34394,26 +34398,26 @@
         <v>43</v>
       </c>
     </row>
-    <row r="160" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B160" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C160" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D160" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E160" s="53" t="s">
+      <c r="C160" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D160" s="24">
+        <v>201</v>
+      </c>
+      <c r="E160" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F160" s="53" t="s">
+      <c r="F160" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G160" s="54">
+      <c r="G160" s="24">
         <v>400</v>
       </c>
       <c r="H160" s="65" t="s">
@@ -34422,46 +34426,46 @@
       <c r="I160" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J160" s="53" t="s">
+      <c r="J160" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K160" s="54" t="s">
+      <c r="K160" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L160" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M160" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N160" s="52" t="s">
+      <c r="L160" s="25">
+        <v>1004</v>
+      </c>
+      <c r="M160" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="N160" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O160" s="63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O160" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B161" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C161" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D161" s="24">
-        <v>202</v>
-      </c>
-      <c r="E161" s="24" t="s">
+      <c r="C161" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D161" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E161" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F161" s="24" t="s">
+      <c r="F161" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G161" s="44">
-        <v>403</v>
+      <c r="G161" s="54">
+        <v>400</v>
       </c>
       <c r="H161" s="65" t="s">
         <v>216</v>
@@ -34469,34 +34473,34 @@
       <c r="I161" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J161" s="24" t="s">
+      <c r="J161" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K161" s="24" t="s">
+      <c r="K161" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L161" s="25">
-        <v>1006</v>
-      </c>
-      <c r="M161" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="N161" s="32" t="s">
+      <c r="L161" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M161" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N161" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="O161" s="30" t="s">
-        <v>59</v>
+      <c r="O161" s="63" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B162" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C162" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D162" s="24">
         <v>202</v>
@@ -34520,13 +34524,13 @@
         <v>7</v>
       </c>
       <c r="K162" s="24" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L162" s="25">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="M162" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N162" s="32" t="s">
         <v>55</v>
@@ -34535,15 +34539,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="163" spans="1:15" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B163" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C163" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D163" s="24">
         <v>202</v>
@@ -34554,7 +34558,7 @@
       <c r="F163" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G163" s="24">
+      <c r="G163" s="44">
         <v>403</v>
       </c>
       <c r="H163" s="65" t="s">
@@ -34570,10 +34574,10 @@
         <v>30</v>
       </c>
       <c r="L163" s="25">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M163" s="32" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N163" s="32" t="s">
         <v>55</v>
@@ -34582,15 +34586,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B164" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C164" s="23" t="s">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="D164" s="24">
         <v>202</v>
@@ -34616,11 +34620,11 @@
       <c r="K164" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="L164" s="65">
-        <v>5001</v>
+      <c r="L164" s="25">
+        <v>1008</v>
       </c>
       <c r="M164" s="32" t="s">
-        <v>176</v>
+        <v>16</v>
       </c>
       <c r="N164" s="32" t="s">
         <v>55</v>
@@ -34629,13 +34633,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="165" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="4"/>
+    <row r="165" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="4">
+        <v>110</v>
+      </c>
       <c r="B165" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C165" s="23" t="s">
-        <v>295</v>
+        <v>175</v>
       </c>
       <c r="D165" s="24">
         <v>202</v>
@@ -34649,7 +34655,7 @@
       <c r="G165" s="24">
         <v>403</v>
       </c>
-      <c r="H165" s="24" t="s">
+      <c r="H165" s="65" t="s">
         <v>216</v>
       </c>
       <c r="I165" s="24" t="s">
@@ -34659,13 +34665,13 @@
         <v>7</v>
       </c>
       <c r="K165" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L165" s="24">
-        <v>1011</v>
+        <v>30</v>
+      </c>
+      <c r="L165" s="65">
+        <v>5001</v>
       </c>
       <c r="M165" s="32" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="N165" s="32" t="s">
         <v>55</v>
@@ -34674,15 +34680,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="166" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="4">
-        <v>111</v>
-      </c>
+    <row r="166" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="4"/>
       <c r="B166" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C166" s="23" t="s">
-        <v>203</v>
+        <v>295</v>
       </c>
       <c r="D166" s="24">
         <v>202</v>
@@ -34693,10 +34697,10 @@
       <c r="F166" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G166" s="44">
+      <c r="G166" s="24">
         <v>403</v>
       </c>
-      <c r="H166" s="65" t="s">
+      <c r="H166" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I166" s="24" t="s">
@@ -34718,30 +34722,30 @@
         <v>55</v>
       </c>
       <c r="O166" s="30" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
     </row>
     <row r="167" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B167" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D167" s="4">
+      <c r="C167" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="E167" s="4" t="s">
+      <c r="D167" s="24">
+        <v>202</v>
+      </c>
+      <c r="E167" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F167" s="4" t="s">
+      <c r="F167" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G167" s="24">
-        <v>400</v>
+      <c r="G167" s="44">
+        <v>403</v>
       </c>
       <c r="H167" s="65" t="s">
         <v>216</v>
@@ -34749,34 +34753,34 @@
       <c r="I167" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J167" s="4" t="s">
+      <c r="J167" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K167" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L167" s="20">
-        <v>5005</v>
-      </c>
-      <c r="M167" s="30" t="s">
-        <v>178</v>
+      <c r="K167" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L167" s="24">
+        <v>1011</v>
+      </c>
+      <c r="M167" s="32" t="s">
+        <v>202</v>
       </c>
       <c r="N167" s="32" t="s">
-        <v>214</v>
+        <v>55</v>
       </c>
       <c r="O167" s="30" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" ht="45.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="26">
-        <v>132</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="4">
+        <v>112</v>
       </c>
       <c r="B168" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C168" s="57" t="s">
-        <v>195</v>
+      <c r="C168" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="D168" s="4">
         <v>203</v>
@@ -34796,19 +34800,19 @@
       <c r="I168" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J168" s="58" t="s">
+      <c r="J168" s="4" t="s">
         <v>7</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L168" s="26">
-        <v>3003</v>
-      </c>
-      <c r="M168" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="N168" s="33" t="s">
+      <c r="L168" s="20">
+        <v>5005</v>
+      </c>
+      <c r="M168" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="N168" s="32" t="s">
         <v>214</v>
       </c>
       <c r="O168" s="30" t="s">
@@ -34817,16 +34821,16 @@
     </row>
     <row r="169" spans="1:15" ht="45.75" x14ac:dyDescent="0.25">
       <c r="A169" s="26">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B169" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C169" s="57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D169" s="4">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>140</v>
@@ -34850,30 +34854,30 @@
         <v>11</v>
       </c>
       <c r="L169" s="26">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="M169" s="57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N169" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="O169" s="56" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="8">
-        <v>130</v>
+      <c r="O169" s="30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="A170" s="26">
+        <v>131</v>
       </c>
       <c r="B170" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C170" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>12</v>
+        <v>196</v>
+      </c>
+      <c r="D170" s="4">
+        <v>204</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>140</v>
@@ -34897,30 +34901,30 @@
         <v>11</v>
       </c>
       <c r="L170" s="26">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="M170" s="57" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N170" s="33" t="s">
         <v>214</v>
       </c>
       <c r="O170" s="56" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" ht="30.75" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B171" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C171" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="D171" s="4">
-        <v>203</v>
+        <v>201</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>140</v>
@@ -34944,30 +34948,30 @@
         <v>11</v>
       </c>
       <c r="L171" s="26">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="M171" s="57" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N171" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="O171" s="57" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A172" s="26">
-        <v>129</v>
+      <c r="O171" s="56" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A172" s="8">
+        <v>128</v>
       </c>
       <c r="B172" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C172" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>12</v>
+      <c r="C172" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D172" s="4">
+        <v>203</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>140</v>
@@ -34975,8 +34979,8 @@
       <c r="F172" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G172" s="65">
-        <v>404</v>
+      <c r="G172" s="24">
+        <v>400</v>
       </c>
       <c r="H172" s="65" t="s">
         <v>216</v>
@@ -34990,11 +34994,11 @@
       <c r="K172" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L172" s="66">
-        <v>3007</v>
-      </c>
-      <c r="M172" s="67" t="s">
-        <v>205</v>
+      <c r="L172" s="26">
+        <v>3006</v>
+      </c>
+      <c r="M172" s="57" t="s">
+        <v>198</v>
       </c>
       <c r="N172" s="33" t="s">
         <v>214</v>
@@ -35003,69 +35007,99 @@
         <v>179</v>
       </c>
     </row>
-    <row r="173" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="8">
-        <v>170</v>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="26">
+        <v>129</v>
       </c>
       <c r="B173" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C173" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="D173" s="58" t="s">
+      <c r="C173" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="D173" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E173" s="8" t="s">
+      <c r="E173" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F173" s="8" t="s">
+      <c r="F173" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G173" s="8">
-        <v>401</v>
-      </c>
-      <c r="H173" s="54" t="s">
+      <c r="G173" s="65">
+        <v>404</v>
+      </c>
+      <c r="H173" s="65" t="s">
         <v>216</v>
       </c>
       <c r="I173" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J173" s="92" t="s">
+      <c r="J173" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K173" s="92" t="s">
+      <c r="K173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L173" s="66">
+        <v>3007</v>
+      </c>
+      <c r="M173" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="N173" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="O173" s="57" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="8">
+        <v>170</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C174" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D174" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G174" s="8">
+        <v>401</v>
+      </c>
+      <c r="H174" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="I174" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J174" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K174" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L173" s="8">
+      <c r="L174" s="8">
         <v>1014</v>
       </c>
-      <c r="M173" s="31" t="s">
+      <c r="M174" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="N173" s="64" t="s">
+      <c r="N174" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O173" s="64" t="s">
+      <c r="O174" s="64" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A174" s="20"/>
-      <c r="B174" s="21"/>
-      <c r="C174" s="22"/>
-      <c r="D174" s="20"/>
-      <c r="E174" s="20"/>
-      <c r="F174" s="20"/>
-      <c r="G174" s="45"/>
-      <c r="H174" s="45"/>
-      <c r="I174" s="45"/>
-      <c r="J174" s="20"/>
-      <c r="K174" s="20"/>
-      <c r="L174" s="20"/>
-      <c r="M174" s="34"/>
-      <c r="N174" s="21"/>
-      <c r="O174" s="21"/>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="20"/>
@@ -35079,6 +35113,7 @@
       <c r="I175" s="45"/>
       <c r="J175" s="20"/>
       <c r="K175" s="20"/>
+      <c r="L175" s="20"/>
       <c r="M175" s="34"/>
       <c r="N175" s="21"/>
       <c r="O175" s="21"/>
@@ -35095,7 +35130,6 @@
       <c r="I176" s="45"/>
       <c r="J176" s="20"/>
       <c r="K176" s="20"/>
-      <c r="L176" s="20"/>
       <c r="M176" s="34"/>
       <c r="N176" s="21"/>
       <c r="O176" s="21"/>
@@ -35367,6 +35401,7 @@
       <c r="I192" s="45"/>
       <c r="J192" s="20"/>
       <c r="K192" s="20"/>
+      <c r="L192" s="20"/>
       <c r="M192" s="34"/>
       <c r="N192" s="21"/>
       <c r="O192" s="21"/>
@@ -35383,7 +35418,6 @@
       <c r="I193" s="45"/>
       <c r="J193" s="20"/>
       <c r="K193" s="20"/>
-      <c r="L193" s="20"/>
       <c r="M193" s="34"/>
       <c r="N193" s="21"/>
       <c r="O193" s="21"/>
@@ -40267,34 +40301,51 @@
       <c r="N480" s="21"/>
       <c r="O480" s="21"/>
     </row>
+    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A481" s="20"/>
+      <c r="B481" s="21"/>
+      <c r="C481" s="22"/>
+      <c r="D481" s="20"/>
+      <c r="E481" s="20"/>
+      <c r="F481" s="20"/>
+      <c r="G481" s="45"/>
+      <c r="H481" s="45"/>
+      <c r="I481" s="45"/>
+      <c r="J481" s="20"/>
+      <c r="K481" s="20"/>
+      <c r="L481" s="20"/>
+      <c r="M481" s="34"/>
+      <c r="N481" s="21"/>
+      <c r="O481" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="G1:G480" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="G1:G481" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataConsolidate/>
   <mergeCells count="15">
+    <mergeCell ref="A154:O154"/>
+    <mergeCell ref="A155:O155"/>
+    <mergeCell ref="A147:O147"/>
+    <mergeCell ref="A126:O126"/>
+    <mergeCell ref="A130:O130"/>
+    <mergeCell ref="A103:O103"/>
+    <mergeCell ref="A102:O102"/>
+    <mergeCell ref="A129:O129"/>
+    <mergeCell ref="A87:O87"/>
+    <mergeCell ref="A71:O71"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A26:O26"/>
-    <mergeCell ref="A69:O69"/>
-    <mergeCell ref="A85:O85"/>
-    <mergeCell ref="A102:O102"/>
-    <mergeCell ref="A101:O101"/>
-    <mergeCell ref="A128:O128"/>
+    <mergeCell ref="A70:O70"/>
     <mergeCell ref="A86:O86"/>
-    <mergeCell ref="A70:O70"/>
-    <mergeCell ref="A153:O153"/>
-    <mergeCell ref="A154:O154"/>
-    <mergeCell ref="A146:O146"/>
-    <mergeCell ref="A125:O125"/>
-    <mergeCell ref="A129:O129"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J17 J126:J127 J147:J152 J7:J8 J75:J76 J91:J92 J106:J108 J133:J135 J158:J159 J20:J21 J137:J145 J110:J124 J94:J99 J30 J78:J83 J55:J68 J161:J172 J33:J53" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J17 J127:J128 J148:J153 J7:J8 J76:J77 J92:J93 J107:J109 J134:J136 J159:J160 J20:J21 J138:J146 J111:J125 J95:J100 J30 J79:J84 J33:J53 J162:J173 J55:J69" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Error,Warning"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K147:K149 K10:K17 K152 K126:K127 K7:K8 K75:K76 K91:K92 K106:K108 K133:K135 K158:K159 K20:K21 K78:K83 K137:K145 K110:K124 K94:K99 K55:K68 K161:K172 K30:K53" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K148:K150 K10:K17 K153 K127:K128 K7:K8 K76:K77 K92:K93 K107:K109 K134:K136 K159:K160 K20:K21 K79:K84 K138:K146 K111:K125 K95:K100 K30:K53 K162:K173 K55:K69" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Field,Cross Field,Cross Form"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L10:L15 L20:L21 L110:L116 L94:L99 L127 L55:L59 L165:L167 L161:L163 L7:L8 L75:L76 L91:L92 L106:L108 L133:L135 L158:L159 L17 L43:L52 L78:L83 L137:L139 L141:L145 L33 L30 L149 L152 L35:L41" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L10:L15 L20:L21 L111:L117 L95:L100 L128 L35:L41 L166:L168 L162:L164 L7:L8 L76:L77 L92:L93 L107:L109 L134:L136 L159:L160 L17 L43:L52 L79:L84 L138:L140 L142:L146 L33 L30 L150 L153 L55 L57:L60" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -40306,8 +40357,8 @@
   </headerFooter>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="25" max="16383" man="1"/>
-    <brk id="68" max="16383" man="1"/>
-    <brk id="100" max="9" man="1"/>
+    <brk id="69" max="16383" man="1"/>
+    <brk id="101" max="9" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/PIT3/validation-rules/Employer_Submission_RPN_Validation_Rules.xlsx
+++ b/PIT3/validation-rules/Employer_Submission_RPN_Validation_Rules.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0FF0B1-1AF1-4AD8-8269-A463F72441D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294E2B46-C888-47A2-B9A7-0B7C96ADE6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2340" windowWidth="23940" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Document Control" sheetId="5" r:id="rId1"/>
     <sheet name="ValidationRules" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ValidationRules!$G$1:$G$481</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ValidationRules!$G$1:$G$480</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Document Control'!$A$1:$E$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">ValidationRules!$A$1:$M$150</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">ValidationRules!$A$1:$M$149</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">ValidationRules!$1:$1</definedName>
     <definedName name="ValidationCodes">#REF!</definedName>
   </definedNames>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="300">
   <si>
     <t>Payslip</t>
   </si>
@@ -1003,9 +1003,6 @@
   <si>
     <t>165, 166, 167, 168, 169, 170</t>
   </si>
-  <si>
-    <t>A PRSI class and number of insurable week(s) should be included when PRSI Exemption Reason is of type “Employment of certain family members”, “Under 16 years of age”, “Employment on certain social welfare schemes” or “other” is used</t>
-  </si>
 </sst>
 </file>
 
@@ -1301,7 +1298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1571,6 +1568,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -22279,18 +22279,18 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="104"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
     </row>
     <row r="11" spans="2:13" ht="30.2" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
@@ -22592,7 +22592,7 @@
       <c r="K30" s="13"/>
       <c r="M30" s="12"/>
     </row>
-    <row r="31" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="30.2" x14ac:dyDescent="0.25">
       <c r="B31" s="17"/>
       <c r="C31" s="68" t="s">
         <v>224</v>
@@ -22614,7 +22614,7 @@
       <c r="K32" s="13"/>
       <c r="M32" s="12"/>
     </row>
-    <row r="33" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" ht="30.2" x14ac:dyDescent="0.25">
       <c r="B33" s="79"/>
       <c r="C33" s="81" t="s">
         <v>139</v>
@@ -22925,7 +22925,7 @@
       <c r="C67" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="D67" s="100" t="s">
+      <c r="D67" s="101" t="s">
         <v>162</v>
       </c>
     </row>
@@ -22966,13 +22966,9 @@
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B72" s="79"/>
-      <c r="C72" s="79">
-        <v>171</v>
-      </c>
-      <c r="D72" s="80" t="s">
-        <v>162</v>
-      </c>
+      <c r="B72" s="100"/>
+      <c r="C72" s="100"/>
+      <c r="D72" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -22989,7 +22985,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BN481"/>
+  <dimension ref="A1:BN480"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" outlineLevelRow="2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -23106,23 +23102,23 @@
       <c r="BN1" s="20"/>
     </row>
     <row r="2" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
       <c r="P2" s="21"/>
       <c r="Q2" s="21"/>
       <c r="R2" s="21"/>
@@ -23176,23 +23172,23 @@
       <c r="BN2" s="21"/>
     </row>
     <row r="3" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="107" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
@@ -23445,10 +23441,10 @@
       <c r="A6" s="92">
         <v>2</v>
       </c>
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="102" t="s">
+      <c r="C6" s="103" t="s">
         <v>147</v>
       </c>
       <c r="D6" s="92" t="s">
@@ -23478,10 +23474,10 @@
       <c r="L6" s="92">
         <v>1013</v>
       </c>
-      <c r="M6" s="102" t="s">
+      <c r="M6" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="N6" s="101" t="s">
+      <c r="N6" s="102" t="s">
         <v>12</v>
       </c>
       <c r="O6" s="93" t="s">
@@ -24358,23 +24354,23 @@
       </c>
     </row>
     <row r="26" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="107" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="106"/>
+      <c r="B26" s="107"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="107"/>
+      <c r="I26" s="107"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="107"/>
+      <c r="M26" s="107"/>
+      <c r="N26" s="107"/>
+      <c r="O26" s="107"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
       <c r="R26" s="21"/>
@@ -26300,65 +26296,65 @@
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:66" ht="78.75" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>171</v>
-      </c>
-      <c r="B56" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>300</v>
+      <c r="C56" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="D56" s="5">
         <v>31</v>
       </c>
-      <c r="E56" s="38" t="s">
+      <c r="E56" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F56" s="38" t="s">
+      <c r="F56" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="38">
+      <c r="G56" s="24">
         <v>200</v>
       </c>
-      <c r="H56" s="38" t="s">
+      <c r="H56" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="I56" s="38" t="s">
+      <c r="I56" s="24" t="s">
         <v>220</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L56" s="5">
-        <v>2061</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>300</v>
+        <v>11</v>
+      </c>
+      <c r="L56" s="8">
+        <v>2037</v>
+      </c>
+      <c r="M56" s="30" t="s">
+        <v>21</v>
       </c>
       <c r="N56" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="O56" s="31" t="s">
-        <v>104</v>
+      <c r="O56" s="37" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>67</v>
+        <v>160</v>
       </c>
       <c r="D57" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>140</v>
@@ -26382,30 +26378,30 @@
         <v>11</v>
       </c>
       <c r="L57" s="8">
-        <v>2037</v>
-      </c>
-      <c r="M57" s="30" t="s">
-        <v>21</v>
+        <v>2036</v>
+      </c>
+      <c r="M57" s="32" t="s">
+        <v>161</v>
       </c>
       <c r="N57" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="O57" s="37" t="s">
-        <v>120</v>
+      <c r="O57" s="31" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B58" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>160</v>
+      <c r="C58" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="D58" s="5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>140</v>
@@ -26426,127 +26422,178 @@
         <v>7</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L58" s="8">
-        <v>2036</v>
-      </c>
-      <c r="M58" s="32" t="s">
-        <v>161</v>
+        <v>2038</v>
+      </c>
+      <c r="M58" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="N58" s="31" t="s">
         <v>0</v>
       </c>
       <c r="O58" s="31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
-        <v>48</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:66" s="73" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A59" s="58">
+        <v>49</v>
       </c>
       <c r="B59" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D59" s="5">
-        <v>35</v>
-      </c>
-      <c r="E59" s="24" t="s">
+      <c r="C59" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D59" s="58">
+        <v>39</v>
+      </c>
+      <c r="E59" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="F59" s="24" t="s">
+      <c r="F59" s="58" t="s">
         <v>140</v>
       </c>
       <c r="G59" s="24">
         <v>200</v>
       </c>
-      <c r="H59" s="24" t="s">
+      <c r="H59" s="74" t="s">
         <v>217</v>
       </c>
       <c r="I59" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="J59" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K59" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L59" s="8">
-        <v>2038</v>
-      </c>
-      <c r="M59" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="N59" s="31" t="s">
+      <c r="K59" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="L59" s="61">
+        <v>2039</v>
+      </c>
+      <c r="M59" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="N59" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="O59" s="31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:66" s="73" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A60" s="58">
-        <v>49</v>
+      <c r="O59" s="59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>50</v>
       </c>
       <c r="B60" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" s="58">
-        <v>39</v>
-      </c>
-      <c r="E60" s="58" t="s">
+      <c r="C60" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D60" s="4">
+        <v>19</v>
+      </c>
+      <c r="E60" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F60" s="58" t="s">
+      <c r="F60" s="24" t="s">
         <v>140</v>
       </c>
       <c r="G60" s="24">
         <v>200</v>
       </c>
-      <c r="H60" s="74" t="s">
+      <c r="H60" s="24" t="s">
         <v>217</v>
       </c>
       <c r="I60" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="J60" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="K60" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="L60" s="61">
-        <v>2039</v>
-      </c>
-      <c r="M60" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="N60" s="59" t="s">
+      <c r="J60" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60" s="10">
+        <v>2044</v>
+      </c>
+      <c r="M60" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="N60" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="O60" s="59" t="s">
-        <v>58</v>
-      </c>
+      <c r="O60" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="P60" s="22"/>
+      <c r="Q60" s="22"/>
+      <c r="R60" s="22"/>
+      <c r="S60" s="22"/>
+      <c r="T60" s="22"/>
+      <c r="U60" s="22"/>
+      <c r="V60" s="22"/>
+      <c r="W60" s="22"/>
+      <c r="X60" s="22"/>
+      <c r="Y60" s="22"/>
+      <c r="Z60" s="22"/>
+      <c r="AA60" s="22"/>
+      <c r="AB60" s="22"/>
+      <c r="AC60" s="22"/>
+      <c r="AD60" s="22"/>
+      <c r="AE60" s="22"/>
+      <c r="AF60" s="22"/>
+      <c r="AG60" s="22"/>
+      <c r="AH60" s="22"/>
+      <c r="AI60" s="22"/>
+      <c r="AJ60" s="22"/>
+      <c r="AK60" s="22"/>
+      <c r="AL60" s="22"/>
+      <c r="AM60" s="22"/>
+      <c r="AN60" s="22"/>
+      <c r="AO60" s="22"/>
+      <c r="AP60" s="22"/>
+      <c r="AQ60" s="22"/>
+      <c r="AR60" s="22"/>
+      <c r="AS60" s="22"/>
+      <c r="AT60" s="22"/>
+      <c r="AU60" s="22"/>
+      <c r="AV60" s="22"/>
+      <c r="AW60" s="22"/>
+      <c r="AX60" s="22"/>
+      <c r="AY60" s="22"/>
+      <c r="AZ60" s="22"/>
+      <c r="BA60" s="22"/>
+      <c r="BB60" s="22"/>
+      <c r="BC60" s="22"/>
+      <c r="BD60" s="22"/>
+      <c r="BE60" s="22"/>
+      <c r="BF60" s="22"/>
+      <c r="BG60" s="22"/>
+      <c r="BH60" s="22"/>
+      <c r="BI60" s="22"/>
+      <c r="BJ60" s="22"/>
+      <c r="BK60" s="22"/>
+      <c r="BL60" s="22"/>
+      <c r="BM60" s="22"/>
+      <c r="BN60" s="22"/>
     </row>
     <row r="61" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B61" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C61" s="51" t="s">
-        <v>144</v>
+      <c r="C61" s="87" t="s">
+        <v>237</v>
       </c>
       <c r="D61" s="4">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E61" s="24" t="s">
         <v>140</v>
@@ -26570,16 +26617,16 @@
         <v>32</v>
       </c>
       <c r="L61" s="10">
-        <v>2044</v>
-      </c>
-      <c r="M61" s="30" t="s">
-        <v>143</v>
+        <v>2045</v>
+      </c>
+      <c r="M61" s="90" t="s">
+        <v>237</v>
       </c>
       <c r="N61" s="30" t="s">
         <v>0</v>
       </c>
       <c r="O61" s="30" t="s">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="P61" s="22"/>
       <c r="Q61" s="22"/>
@@ -26635,24 +26682,24 @@
     </row>
     <row r="62" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>51</v>
-      </c>
-      <c r="B62" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="C62" s="87" t="s">
-        <v>237</v>
-      </c>
-      <c r="D62" s="4">
-        <v>8</v>
-      </c>
-      <c r="E62" s="24" t="s">
+      <c r="C62" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="G62" s="24">
+      <c r="G62" s="54">
         <v>200</v>
       </c>
       <c r="H62" s="24" t="s">
@@ -26661,23 +26708,23 @@
       <c r="I62" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="J62" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L62" s="10">
-        <v>2045</v>
-      </c>
-      <c r="M62" s="90" t="s">
-        <v>237</v>
-      </c>
-      <c r="N62" s="30" t="s">
+      <c r="J62" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="K62" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="L62" s="53">
+        <v>2047</v>
+      </c>
+      <c r="M62" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="N62" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="O62" s="30" t="s">
-        <v>1</v>
+      <c r="O62" s="63" t="s">
+        <v>0</v>
       </c>
       <c r="P62" s="22"/>
       <c r="Q62" s="22"/>
@@ -26731,51 +26778,51 @@
       <c r="BM62" s="22"/>
       <c r="BN62" s="22"/>
     </row>
-    <row r="63" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>122</v>
-      </c>
-      <c r="B63" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="D63" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="54" t="s">
+      <c r="C63" s="85" t="s">
+        <v>276</v>
+      </c>
+      <c r="D63" s="4">
+        <v>16</v>
+      </c>
+      <c r="E63" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F63" s="54" t="s">
+      <c r="F63" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G63" s="54">
+      <c r="G63" s="24">
         <v>200</v>
       </c>
       <c r="H63" s="24" t="s">
         <v>217</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="J63" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="K63" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="L63" s="53">
-        <v>2047</v>
-      </c>
-      <c r="M63" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="N63" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L63" s="10">
+        <v>2052</v>
+      </c>
+      <c r="M63" s="85" t="s">
+        <v>276</v>
+      </c>
+      <c r="N63" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="O63" s="63" t="s">
-        <v>0</v>
+      <c r="O63" s="30" t="s">
+        <v>277</v>
       </c>
       <c r="P63" s="22"/>
       <c r="Q63" s="22"/>
@@ -26829,18 +26876,18 @@
       <c r="BM63" s="22"/>
       <c r="BN63" s="22"/>
     </row>
-    <row r="64" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:66" s="7" customFormat="1" ht="220.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B64" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C64" s="85" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D64" s="4">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E64" s="24" t="s">
         <v>140</v>
@@ -26857,23 +26904,23 @@
       <c r="I64" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="J64" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>32</v>
+      <c r="J64" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="L64" s="10">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="M64" s="85" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="N64" s="30" t="s">
         <v>0</v>
       </c>
       <c r="O64" s="30" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="P64" s="22"/>
       <c r="Q64" s="22"/>
@@ -26927,51 +26974,51 @@
       <c r="BM64" s="22"/>
       <c r="BN64" s="22"/>
     </row>
-    <row r="65" spans="1:66" s="7" customFormat="1" ht="220.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
-        <v>157</v>
+    <row r="65" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>159</v>
       </c>
       <c r="B65" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C65" s="85" t="s">
-        <v>283</v>
-      </c>
-      <c r="D65" s="4">
-        <v>55</v>
-      </c>
-      <c r="E65" s="24" t="s">
+      <c r="C65" s="99" t="s">
+        <v>285</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F65" s="24" t="s">
+      <c r="F65" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G65" s="24">
+      <c r="G65" s="10">
         <v>200</v>
       </c>
-      <c r="H65" s="24" t="s">
+      <c r="H65" s="10" t="s">
         <v>217</v>
       </c>
       <c r="I65" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="J65" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="K65" s="5" t="s">
+      <c r="J65" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K65" s="58" t="s">
         <v>11</v>
       </c>
       <c r="L65" s="10">
-        <v>2053</v>
-      </c>
-      <c r="M65" s="85" t="s">
-        <v>282</v>
+        <v>2056</v>
+      </c>
+      <c r="M65" s="99" t="s">
+        <v>285</v>
       </c>
       <c r="N65" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="O65" s="30" t="s">
-        <v>281</v>
+      <c r="O65" s="99" t="s">
+        <v>12</v>
       </c>
       <c r="P65" s="22"/>
       <c r="Q65" s="22"/>
@@ -27027,13 +27074,13 @@
     </row>
     <row r="66" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B66" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C66" s="99" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>12</v>
@@ -27060,10 +27107,10 @@
         <v>11</v>
       </c>
       <c r="L66" s="10">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="M66" s="99" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N66" s="30" t="s">
         <v>0</v>
@@ -27125,13 +27172,13 @@
     </row>
     <row r="67" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B67" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C67" s="99" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>12</v>
@@ -27158,10 +27205,10 @@
         <v>11</v>
       </c>
       <c r="L67" s="10">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="M67" s="99" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N67" s="30" t="s">
         <v>0</v>
@@ -27223,13 +27270,13 @@
     </row>
     <row r="68" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B68" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C68" s="99" t="s">
-        <v>287</v>
+      <c r="C68" s="30" t="s">
+        <v>290</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>12</v>
@@ -27256,10 +27303,10 @@
         <v>11</v>
       </c>
       <c r="L68" s="10">
-        <v>2058</v>
-      </c>
-      <c r="M68" s="99" t="s">
-        <v>287</v>
+        <v>2060</v>
+      </c>
+      <c r="M68" s="30" t="s">
+        <v>290</v>
       </c>
       <c r="N68" s="30" t="s">
         <v>0</v>
@@ -27319,122 +27366,94 @@
       <c r="BM68" s="22"/>
       <c r="BN68" s="22"/>
     </row>
-    <row r="69" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A69" s="10">
-        <v>163</v>
-      </c>
-      <c r="B69" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="G69" s="10">
-        <v>200</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="I69" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K69" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="L69" s="10">
-        <v>2060</v>
-      </c>
-      <c r="M69" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="N69" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="O69" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="P69" s="22"/>
-      <c r="Q69" s="22"/>
-      <c r="R69" s="22"/>
-      <c r="S69" s="22"/>
-      <c r="T69" s="22"/>
-      <c r="U69" s="22"/>
-      <c r="V69" s="22"/>
-      <c r="W69" s="22"/>
-      <c r="X69" s="22"/>
-      <c r="Y69" s="22"/>
-      <c r="Z69" s="22"/>
-      <c r="AA69" s="22"/>
-      <c r="AB69" s="22"/>
-      <c r="AC69" s="22"/>
-      <c r="AD69" s="22"/>
-      <c r="AE69" s="22"/>
-      <c r="AF69" s="22"/>
-      <c r="AG69" s="22"/>
-      <c r="AH69" s="22"/>
-      <c r="AI69" s="22"/>
-      <c r="AJ69" s="22"/>
-      <c r="AK69" s="22"/>
-      <c r="AL69" s="22"/>
-      <c r="AM69" s="22"/>
-      <c r="AN69" s="22"/>
-      <c r="AO69" s="22"/>
-      <c r="AP69" s="22"/>
-      <c r="AQ69" s="22"/>
-      <c r="AR69" s="22"/>
-      <c r="AS69" s="22"/>
-      <c r="AT69" s="22"/>
-      <c r="AU69" s="22"/>
-      <c r="AV69" s="22"/>
-      <c r="AW69" s="22"/>
-      <c r="AX69" s="22"/>
-      <c r="AY69" s="22"/>
-      <c r="AZ69" s="22"/>
-      <c r="BA69" s="22"/>
-      <c r="BB69" s="22"/>
-      <c r="BC69" s="22"/>
-      <c r="BD69" s="22"/>
-      <c r="BE69" s="22"/>
-      <c r="BF69" s="22"/>
-      <c r="BG69" s="22"/>
-      <c r="BH69" s="22"/>
-      <c r="BI69" s="22"/>
-      <c r="BJ69" s="22"/>
-      <c r="BK69" s="22"/>
-      <c r="BL69" s="22"/>
-      <c r="BM69" s="22"/>
-      <c r="BN69" s="22"/>
-    </row>
-    <row r="70" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="108" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="109"/>
+      <c r="C69" s="109"/>
+      <c r="D69" s="109"/>
+      <c r="E69" s="109"/>
+      <c r="F69" s="109"/>
+      <c r="G69" s="109"/>
+      <c r="H69" s="109"/>
+      <c r="I69" s="109"/>
+      <c r="J69" s="109"/>
+      <c r="K69" s="109"/>
+      <c r="L69" s="109"/>
+      <c r="M69" s="109"/>
+      <c r="N69" s="109"/>
+      <c r="O69" s="110"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="21"/>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
+      <c r="X69" s="21"/>
+      <c r="Y69" s="21"/>
+      <c r="Z69" s="21"/>
+      <c r="AA69" s="21"/>
+      <c r="AB69" s="21"/>
+      <c r="AC69" s="21"/>
+      <c r="AD69" s="21"/>
+      <c r="AE69" s="21"/>
+      <c r="AF69" s="21"/>
+      <c r="AG69" s="21"/>
+      <c r="AH69" s="21"/>
+      <c r="AI69" s="21"/>
+      <c r="AJ69" s="21"/>
+      <c r="AK69" s="21"/>
+      <c r="AL69" s="21"/>
+      <c r="AM69" s="21"/>
+      <c r="AN69" s="21"/>
+      <c r="AO69" s="21"/>
+      <c r="AP69" s="21"/>
+      <c r="AQ69" s="21"/>
+      <c r="AR69" s="21"/>
+      <c r="AS69" s="21"/>
+      <c r="AT69" s="21"/>
+      <c r="AU69" s="21"/>
+      <c r="AV69" s="21"/>
+      <c r="AW69" s="21"/>
+      <c r="AX69" s="21"/>
+      <c r="AY69" s="21"/>
+      <c r="AZ69" s="21"/>
+      <c r="BA69" s="21"/>
+      <c r="BB69" s="21"/>
+      <c r="BC69" s="21"/>
+      <c r="BD69" s="21"/>
+      <c r="BE69" s="21"/>
+      <c r="BF69" s="21"/>
+      <c r="BG69" s="21"/>
+      <c r="BH69" s="21"/>
+      <c r="BI69" s="21"/>
+      <c r="BJ69" s="21"/>
+      <c r="BK69" s="21"/>
+      <c r="BL69" s="21"/>
+      <c r="BM69" s="21"/>
+      <c r="BN69" s="21"/>
+    </row>
+    <row r="70" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A70" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="108"/>
-      <c r="C70" s="108"/>
-      <c r="D70" s="108"/>
-      <c r="E70" s="108"/>
-      <c r="F70" s="108"/>
-      <c r="G70" s="108"/>
-      <c r="H70" s="108"/>
-      <c r="I70" s="108"/>
-      <c r="J70" s="108"/>
-      <c r="K70" s="108"/>
-      <c r="L70" s="108"/>
-      <c r="M70" s="108"/>
-      <c r="N70" s="108"/>
-      <c r="O70" s="109"/>
+        <v>146</v>
+      </c>
+      <c r="B70" s="107"/>
+      <c r="C70" s="107"/>
+      <c r="D70" s="107"/>
+      <c r="E70" s="107"/>
+      <c r="F70" s="107"/>
+      <c r="G70" s="107"/>
+      <c r="H70" s="107"/>
+      <c r="I70" s="107"/>
+      <c r="J70" s="107"/>
+      <c r="K70" s="107"/>
+      <c r="L70" s="107"/>
+      <c r="M70" s="107"/>
+      <c r="N70" s="107"/>
+      <c r="O70" s="107"/>
       <c r="P70" s="21"/>
       <c r="Q70" s="21"/>
       <c r="R70" s="21"/>
@@ -27487,24 +27506,52 @@
       <c r="BM70" s="21"/>
       <c r="BN70" s="21"/>
     </row>
-    <row r="71" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="106" t="s">
-        <v>146</v>
-      </c>
-      <c r="B71" s="106"/>
-      <c r="C71" s="106"/>
-      <c r="D71" s="106"/>
-      <c r="E71" s="106"/>
-      <c r="F71" s="106"/>
-      <c r="G71" s="106"/>
-      <c r="H71" s="106"/>
-      <c r="I71" s="106"/>
-      <c r="J71" s="106"/>
-      <c r="K71" s="106"/>
-      <c r="L71" s="106"/>
-      <c r="M71" s="106"/>
-      <c r="N71" s="106"/>
-      <c r="O71" s="106"/>
+    <row r="71" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="92">
+        <v>148</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" s="93" t="s">
+        <v>253</v>
+      </c>
+      <c r="D71" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="F71" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="G71" s="92">
+        <v>403</v>
+      </c>
+      <c r="H71" s="92" t="s">
+        <v>216</v>
+      </c>
+      <c r="I71" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J71" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K71" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L71" s="92">
+        <v>1111</v>
+      </c>
+      <c r="M71" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="N71" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O71" s="30" t="s">
+        <v>59</v>
+      </c>
       <c r="P71" s="21"/>
       <c r="Q71" s="21"/>
       <c r="R71" s="21"/>
@@ -27557,15 +27604,15 @@
       <c r="BM71" s="21"/>
       <c r="BN71" s="21"/>
     </row>
-    <row r="72" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A72" s="92">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B72" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C72" s="93" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D72" s="92" t="s">
         <v>12</v>
@@ -27592,16 +27639,16 @@
         <v>32</v>
       </c>
       <c r="L72" s="92">
-        <v>1111</v>
+        <v>1016</v>
       </c>
       <c r="M72" s="93" t="s">
-        <v>252</v>
-      </c>
-      <c r="N72" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O72" s="30" t="s">
-        <v>59</v>
+        <v>245</v>
+      </c>
+      <c r="N72" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O72" s="93" t="s">
+        <v>12</v>
       </c>
       <c r="P72" s="21"/>
       <c r="Q72" s="21"/>
@@ -27655,50 +27702,50 @@
       <c r="BM72" s="21"/>
       <c r="BN72" s="21"/>
     </row>
-    <row r="73" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="92">
-        <v>146</v>
+    <row r="73" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <v>52</v>
       </c>
       <c r="B73" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D73" s="92" t="s">
+      <c r="C73" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E73" s="92" t="s">
+      <c r="E73" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F73" s="92" t="s">
+      <c r="F73" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="92">
-        <v>403</v>
-      </c>
-      <c r="H73" s="92" t="s">
+      <c r="G73" s="24">
+        <v>401</v>
+      </c>
+      <c r="H73" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I73" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J73" s="92" t="s">
+      <c r="J73" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K73" s="92" t="s">
+      <c r="K73" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L73" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M73" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N73" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O73" s="93" t="s">
+      <c r="L73" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M73" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N73" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O73" s="49" t="s">
         <v>12</v>
       </c>
       <c r="P73" s="21"/>
@@ -27753,160 +27800,160 @@
       <c r="BM73" s="21"/>
       <c r="BN73" s="21"/>
     </row>
-    <row r="74" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
-        <v>52</v>
-      </c>
-      <c r="B74" s="30" t="s">
+    <row r="74" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A74" s="92">
+        <v>53</v>
+      </c>
+      <c r="B74" s="104" t="s">
         <v>99</v>
       </c>
-      <c r="C74" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D74" s="4" t="s">
+      <c r="C74" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="D74" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="24">
+      <c r="G74" s="74">
         <v>401</v>
       </c>
       <c r="H74" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I74" s="24" t="s">
+      <c r="I74" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J74" s="4" t="s">
+      <c r="J74" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K74" s="4" t="s">
+      <c r="K74" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L74" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M74" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N74" s="32" t="s">
+      <c r="L74" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M74" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="N74" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="O74" s="49" t="s">
+      <c r="O74" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="P74" s="21"/>
-      <c r="Q74" s="21"/>
-      <c r="R74" s="21"/>
-      <c r="S74" s="21"/>
-      <c r="T74" s="21"/>
-      <c r="U74" s="21"/>
-      <c r="V74" s="21"/>
-      <c r="W74" s="21"/>
-      <c r="X74" s="21"/>
-      <c r="Y74" s="21"/>
-      <c r="Z74" s="21"/>
-      <c r="AA74" s="21"/>
-      <c r="AB74" s="21"/>
-      <c r="AC74" s="21"/>
-      <c r="AD74" s="21"/>
-      <c r="AE74" s="21"/>
-      <c r="AF74" s="21"/>
-      <c r="AG74" s="21"/>
-      <c r="AH74" s="21"/>
-      <c r="AI74" s="21"/>
-      <c r="AJ74" s="21"/>
-      <c r="AK74" s="21"/>
-      <c r="AL74" s="21"/>
-      <c r="AM74" s="21"/>
-      <c r="AN74" s="21"/>
-      <c r="AO74" s="21"/>
-      <c r="AP74" s="21"/>
-      <c r="AQ74" s="21"/>
-      <c r="AR74" s="21"/>
-      <c r="AS74" s="21"/>
-      <c r="AT74" s="21"/>
-      <c r="AU74" s="21"/>
-      <c r="AV74" s="21"/>
-      <c r="AW74" s="21"/>
-      <c r="AX74" s="21"/>
-      <c r="AY74" s="21"/>
-      <c r="AZ74" s="21"/>
-      <c r="BA74" s="21"/>
-      <c r="BB74" s="21"/>
-      <c r="BC74" s="21"/>
-      <c r="BD74" s="21"/>
-      <c r="BE74" s="21"/>
-      <c r="BF74" s="21"/>
-      <c r="BG74" s="21"/>
-      <c r="BH74" s="21"/>
-      <c r="BI74" s="21"/>
-      <c r="BJ74" s="21"/>
-      <c r="BK74" s="21"/>
-      <c r="BL74" s="21"/>
-      <c r="BM74" s="21"/>
-      <c r="BN74" s="21"/>
-    </row>
-    <row r="75" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A75" s="92">
-        <v>53</v>
-      </c>
-      <c r="B75" s="103" t="s">
+    </row>
+    <row r="75" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <v>55</v>
+      </c>
+      <c r="B75" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C75" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75" s="92" t="s">
+      <c r="C75" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E75" s="92" t="s">
+      <c r="E75" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F75" s="92" t="s">
+      <c r="F75" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="74">
-        <v>401</v>
+      <c r="G75" s="24">
+        <v>400</v>
       </c>
       <c r="H75" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I75" s="74" t="s">
+      <c r="I75" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J75" s="92" t="s">
+      <c r="J75" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K75" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L75" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M75" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="N75" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="O75" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K75" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L75" s="24">
+        <v>1003</v>
+      </c>
+      <c r="M75" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="N75" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O75" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
+      <c r="Z75" s="22"/>
+      <c r="AA75" s="22"/>
+      <c r="AB75" s="22"/>
+      <c r="AC75" s="22"/>
+      <c r="AD75" s="22"/>
+      <c r="AE75" s="22"/>
+      <c r="AF75" s="22"/>
+      <c r="AG75" s="22"/>
+      <c r="AH75" s="22"/>
+      <c r="AI75" s="22"/>
+      <c r="AJ75" s="22"/>
+      <c r="AK75" s="22"/>
+      <c r="AL75" s="22"/>
+      <c r="AM75" s="22"/>
+      <c r="AN75" s="22"/>
+      <c r="AO75" s="22"/>
+      <c r="AP75" s="22"/>
+      <c r="AQ75" s="22"/>
+      <c r="AR75" s="22"/>
+      <c r="AS75" s="22"/>
+      <c r="AT75" s="22"/>
+      <c r="AU75" s="22"/>
+      <c r="AV75" s="22"/>
+      <c r="AW75" s="22"/>
+      <c r="AX75" s="22"/>
+      <c r="AY75" s="22"/>
+      <c r="AZ75" s="22"/>
+      <c r="BA75" s="22"/>
+      <c r="BB75" s="22"/>
+      <c r="BC75" s="22"/>
+      <c r="BD75" s="22"/>
+      <c r="BE75" s="22"/>
+      <c r="BF75" s="22"/>
+      <c r="BG75" s="22"/>
+      <c r="BH75" s="22"/>
+      <c r="BI75" s="22"/>
+      <c r="BJ75" s="22"/>
+      <c r="BK75" s="22"/>
+      <c r="BL75" s="22"/>
+      <c r="BM75" s="22"/>
+      <c r="BN75" s="22"/>
+    </row>
+    <row r="76" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B76" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>264</v>
+        <v>86</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>12</v>
@@ -27930,13 +27977,13 @@
         <v>7</v>
       </c>
       <c r="K76" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L76" s="24">
-        <v>1003</v>
+        <v>11</v>
+      </c>
+      <c r="L76" s="25">
+        <v>1004</v>
       </c>
       <c r="M76" s="32" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N76" s="30" t="s">
         <v>60</v>
@@ -27996,26 +28043,26 @@
       <c r="BM76" s="22"/>
       <c r="BN76" s="22"/>
     </row>
-    <row r="77" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="B77" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C77" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D77" s="4" t="s">
+      <c r="C77" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D77" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="24">
+      <c r="G77" s="54">
         <v>400</v>
       </c>
       <c r="H77" s="58" t="s">
@@ -28024,97 +28071,46 @@
       <c r="I77" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J77" s="24" t="s">
+      <c r="J77" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K77" s="24" t="s">
+      <c r="K77" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L77" s="25">
-        <v>1004</v>
-      </c>
-      <c r="M77" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="N77" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O77" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P77" s="22"/>
-      <c r="Q77" s="22"/>
-      <c r="R77" s="22"/>
-      <c r="S77" s="22"/>
-      <c r="T77" s="22"/>
-      <c r="U77" s="22"/>
-      <c r="V77" s="22"/>
-      <c r="W77" s="22"/>
-      <c r="X77" s="22"/>
-      <c r="Y77" s="22"/>
-      <c r="Z77" s="22"/>
-      <c r="AA77" s="22"/>
-      <c r="AB77" s="22"/>
-      <c r="AC77" s="22"/>
-      <c r="AD77" s="22"/>
-      <c r="AE77" s="22"/>
-      <c r="AF77" s="22"/>
-      <c r="AG77" s="22"/>
-      <c r="AH77" s="22"/>
-      <c r="AI77" s="22"/>
-      <c r="AJ77" s="22"/>
-      <c r="AK77" s="22"/>
-      <c r="AL77" s="22"/>
-      <c r="AM77" s="22"/>
-      <c r="AN77" s="22"/>
-      <c r="AO77" s="22"/>
-      <c r="AP77" s="22"/>
-      <c r="AQ77" s="22"/>
-      <c r="AR77" s="22"/>
-      <c r="AS77" s="22"/>
-      <c r="AT77" s="22"/>
-      <c r="AU77" s="22"/>
-      <c r="AV77" s="22"/>
-      <c r="AW77" s="22"/>
-      <c r="AX77" s="22"/>
-      <c r="AY77" s="22"/>
-      <c r="AZ77" s="22"/>
-      <c r="BA77" s="22"/>
-      <c r="BB77" s="22"/>
-      <c r="BC77" s="22"/>
-      <c r="BD77" s="22"/>
-      <c r="BE77" s="22"/>
-      <c r="BF77" s="22"/>
-      <c r="BG77" s="22"/>
-      <c r="BH77" s="22"/>
-      <c r="BI77" s="22"/>
-      <c r="BJ77" s="22"/>
-      <c r="BK77" s="22"/>
-      <c r="BL77" s="22"/>
-      <c r="BM77" s="22"/>
-      <c r="BN77" s="22"/>
-    </row>
-    <row r="78" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="L77" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M77" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N77" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O77" s="63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B78" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C78" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D78" s="53" t="s">
+      <c r="C78" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E78" s="53" t="s">
+      <c r="E78" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F78" s="53" t="s">
+      <c r="F78" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="54">
-        <v>400</v>
+      <c r="G78" s="24">
+        <v>403</v>
       </c>
       <c r="H78" s="58" t="s">
         <v>216</v>
@@ -28122,34 +28118,85 @@
       <c r="I78" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J78" s="53" t="s">
+      <c r="J78" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K78" s="54" t="s">
+      <c r="K78" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L78" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M78" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N78" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O78" s="63" t="s">
-        <v>12</v>
-      </c>
+      <c r="L78" s="25">
+        <v>1006</v>
+      </c>
+      <c r="M78" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="N78" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O78" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="T78" s="22"/>
+      <c r="U78" s="22"/>
+      <c r="V78" s="22"/>
+      <c r="W78" s="22"/>
+      <c r="X78" s="22"/>
+      <c r="Y78" s="22"/>
+      <c r="Z78" s="22"/>
+      <c r="AA78" s="22"/>
+      <c r="AB78" s="22"/>
+      <c r="AC78" s="22"/>
+      <c r="AD78" s="22"/>
+      <c r="AE78" s="22"/>
+      <c r="AF78" s="22"/>
+      <c r="AG78" s="22"/>
+      <c r="AH78" s="22"/>
+      <c r="AI78" s="22"/>
+      <c r="AJ78" s="22"/>
+      <c r="AK78" s="22"/>
+      <c r="AL78" s="22"/>
+      <c r="AM78" s="22"/>
+      <c r="AN78" s="22"/>
+      <c r="AO78" s="22"/>
+      <c r="AP78" s="22"/>
+      <c r="AQ78" s="22"/>
+      <c r="AR78" s="22"/>
+      <c r="AS78" s="22"/>
+      <c r="AT78" s="22"/>
+      <c r="AU78" s="22"/>
+      <c r="AV78" s="22"/>
+      <c r="AW78" s="22"/>
+      <c r="AX78" s="22"/>
+      <c r="AY78" s="22"/>
+      <c r="AZ78" s="22"/>
+      <c r="BA78" s="22"/>
+      <c r="BB78" s="22"/>
+      <c r="BC78" s="22"/>
+      <c r="BD78" s="22"/>
+      <c r="BE78" s="22"/>
+      <c r="BF78" s="22"/>
+      <c r="BG78" s="22"/>
+      <c r="BH78" s="22"/>
+      <c r="BI78" s="22"/>
+      <c r="BJ78" s="22"/>
+      <c r="BK78" s="22"/>
+      <c r="BL78" s="22"/>
+      <c r="BM78" s="22"/>
+      <c r="BN78" s="22"/>
     </row>
     <row r="79" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B79" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>12</v>
@@ -28173,13 +28220,13 @@
         <v>7</v>
       </c>
       <c r="K79" s="24" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L79" s="25">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M79" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N79" s="30" t="s">
         <v>60</v>
@@ -28241,13 +28288,13 @@
     </row>
     <row r="80" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B80" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>12</v>
@@ -28274,10 +28321,10 @@
         <v>30</v>
       </c>
       <c r="L80" s="25">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M80" s="32" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N80" s="30" t="s">
         <v>60</v>
@@ -28337,29 +28384,27 @@
       <c r="BM80" s="22"/>
       <c r="BN80" s="22"/>
     </row>
-    <row r="81" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A81" s="4">
-        <v>59</v>
-      </c>
+    <row r="81" spans="1:66" ht="21" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A81" s="4"/>
       <c r="B81" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D81" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D81" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G81" s="24">
+      <c r="G81" s="44">
         <v>403</v>
       </c>
-      <c r="H81" s="58" t="s">
+      <c r="H81" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I81" s="24" t="s">
@@ -28369,93 +28414,44 @@
         <v>7</v>
       </c>
       <c r="K81" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L81" s="25">
-        <v>1008</v>
+        <v>32</v>
+      </c>
+      <c r="L81" s="24">
+        <v>1011</v>
       </c>
       <c r="M81" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="N81" s="30" t="s">
-        <v>60</v>
+        <v>202</v>
+      </c>
+      <c r="N81" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O81" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="P81" s="22"/>
-      <c r="Q81" s="22"/>
-      <c r="R81" s="22"/>
-      <c r="S81" s="22"/>
-      <c r="T81" s="22"/>
-      <c r="U81" s="22"/>
-      <c r="V81" s="22"/>
-      <c r="W81" s="22"/>
-      <c r="X81" s="22"/>
-      <c r="Y81" s="22"/>
-      <c r="Z81" s="22"/>
-      <c r="AA81" s="22"/>
-      <c r="AB81" s="22"/>
-      <c r="AC81" s="22"/>
-      <c r="AD81" s="22"/>
-      <c r="AE81" s="22"/>
-      <c r="AF81" s="22"/>
-      <c r="AG81" s="22"/>
-      <c r="AH81" s="22"/>
-      <c r="AI81" s="22"/>
-      <c r="AJ81" s="22"/>
-      <c r="AK81" s="22"/>
-      <c r="AL81" s="22"/>
-      <c r="AM81" s="22"/>
-      <c r="AN81" s="22"/>
-      <c r="AO81" s="22"/>
-      <c r="AP81" s="22"/>
-      <c r="AQ81" s="22"/>
-      <c r="AR81" s="22"/>
-      <c r="AS81" s="22"/>
-      <c r="AT81" s="22"/>
-      <c r="AU81" s="22"/>
-      <c r="AV81" s="22"/>
-      <c r="AW81" s="22"/>
-      <c r="AX81" s="22"/>
-      <c r="AY81" s="22"/>
-      <c r="AZ81" s="22"/>
-      <c r="BA81" s="22"/>
-      <c r="BB81" s="22"/>
-      <c r="BC81" s="22"/>
-      <c r="BD81" s="22"/>
-      <c r="BE81" s="22"/>
-      <c r="BF81" s="22"/>
-      <c r="BG81" s="22"/>
-      <c r="BH81" s="22"/>
-      <c r="BI81" s="22"/>
-      <c r="BJ81" s="22"/>
-      <c r="BK81" s="22"/>
-      <c r="BL81" s="22"/>
-      <c r="BM81" s="22"/>
-      <c r="BN81" s="22"/>
-    </row>
-    <row r="82" spans="1:66" ht="21" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
+    </row>
+    <row r="82" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>60</v>
+      </c>
       <c r="B82" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
       <c r="D82" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E82" s="24" t="s">
+      <c r="E82" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F82" s="24" t="s">
+      <c r="F82" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G82" s="44">
+      <c r="G82" s="24">
         <v>403</v>
       </c>
-      <c r="H82" s="24" t="s">
+      <c r="H82" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I82" s="24" t="s">
@@ -28473,24 +28469,75 @@
       <c r="M82" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N82" s="32" t="s">
-        <v>55</v>
+      <c r="N82" s="30" t="s">
+        <v>60</v>
       </c>
       <c r="O82" s="30" t="s">
-        <v>59</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="T82" s="22"/>
+      <c r="U82" s="22"/>
+      <c r="V82" s="22"/>
+      <c r="W82" s="22"/>
+      <c r="X82" s="22"/>
+      <c r="Y82" s="22"/>
+      <c r="Z82" s="22"/>
+      <c r="AA82" s="22"/>
+      <c r="AB82" s="22"/>
+      <c r="AC82" s="22"/>
+      <c r="AD82" s="22"/>
+      <c r="AE82" s="22"/>
+      <c r="AF82" s="22"/>
+      <c r="AG82" s="22"/>
+      <c r="AH82" s="22"/>
+      <c r="AI82" s="22"/>
+      <c r="AJ82" s="22"/>
+      <c r="AK82" s="22"/>
+      <c r="AL82" s="22"/>
+      <c r="AM82" s="22"/>
+      <c r="AN82" s="22"/>
+      <c r="AO82" s="22"/>
+      <c r="AP82" s="22"/>
+      <c r="AQ82" s="22"/>
+      <c r="AR82" s="22"/>
+      <c r="AS82" s="22"/>
+      <c r="AT82" s="22"/>
+      <c r="AU82" s="22"/>
+      <c r="AV82" s="22"/>
+      <c r="AW82" s="22"/>
+      <c r="AX82" s="22"/>
+      <c r="AY82" s="22"/>
+      <c r="AZ82" s="22"/>
+      <c r="BA82" s="22"/>
+      <c r="BB82" s="22"/>
+      <c r="BC82" s="22"/>
+      <c r="BD82" s="22"/>
+      <c r="BE82" s="22"/>
+      <c r="BF82" s="22"/>
+      <c r="BG82" s="22"/>
+      <c r="BH82" s="22"/>
+      <c r="BI82" s="22"/>
+      <c r="BJ82" s="22"/>
+      <c r="BK82" s="22"/>
+      <c r="BL82" s="22"/>
+      <c r="BM82" s="22"/>
+      <c r="BN82" s="22"/>
     </row>
     <row r="83" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B83" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D83" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="4" t="s">
@@ -28500,7 +28547,7 @@
         <v>140</v>
       </c>
       <c r="G83" s="24">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H83" s="58" t="s">
         <v>216</v>
@@ -28508,23 +28555,23 @@
       <c r="I83" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J83" s="24" t="s">
+      <c r="J83" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K83" s="24" t="s">
+      <c r="K83" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L83" s="24">
-        <v>1011</v>
-      </c>
-      <c r="M83" s="32" t="s">
-        <v>202</v>
+      <c r="L83" s="4">
+        <v>2501</v>
+      </c>
+      <c r="M83" s="30" t="s">
+        <v>40</v>
       </c>
       <c r="N83" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O83" s="30" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="P83" s="22"/>
       <c r="Q83" s="22"/>
@@ -28578,169 +28625,141 @@
       <c r="BM83" s="22"/>
       <c r="BN83" s="22"/>
     </row>
-    <row r="84" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A84" s="4">
-        <v>61</v>
+    <row r="84" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>166</v>
       </c>
       <c r="B84" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C84" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="C84" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D84" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E84" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G84" s="24">
-        <v>404</v>
-      </c>
-      <c r="H84" s="58" t="s">
+      <c r="G84" s="8">
+        <v>401</v>
+      </c>
+      <c r="H84" s="54" t="s">
         <v>216</v>
       </c>
       <c r="I84" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J84" s="4" t="s">
+      <c r="J84" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K84" s="4" t="s">
+      <c r="K84" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L84" s="4">
-        <v>2501</v>
-      </c>
-      <c r="M84" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="N84" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="O84" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="P84" s="22"/>
-      <c r="Q84" s="22"/>
-      <c r="R84" s="22"/>
-      <c r="S84" s="22"/>
-      <c r="T84" s="22"/>
-      <c r="U84" s="22"/>
-      <c r="V84" s="22"/>
-      <c r="W84" s="22"/>
-      <c r="X84" s="22"/>
-      <c r="Y84" s="22"/>
-      <c r="Z84" s="22"/>
-      <c r="AA84" s="22"/>
-      <c r="AB84" s="22"/>
-      <c r="AC84" s="22"/>
-      <c r="AD84" s="22"/>
-      <c r="AE84" s="22"/>
-      <c r="AF84" s="22"/>
-      <c r="AG84" s="22"/>
-      <c r="AH84" s="22"/>
-      <c r="AI84" s="22"/>
-      <c r="AJ84" s="22"/>
-      <c r="AK84" s="22"/>
-      <c r="AL84" s="22"/>
-      <c r="AM84" s="22"/>
-      <c r="AN84" s="22"/>
-      <c r="AO84" s="22"/>
-      <c r="AP84" s="22"/>
-      <c r="AQ84" s="22"/>
-      <c r="AR84" s="22"/>
-      <c r="AS84" s="22"/>
-      <c r="AT84" s="22"/>
-      <c r="AU84" s="22"/>
-      <c r="AV84" s="22"/>
-      <c r="AW84" s="22"/>
-      <c r="AX84" s="22"/>
-      <c r="AY84" s="22"/>
-      <c r="AZ84" s="22"/>
-      <c r="BA84" s="22"/>
-      <c r="BB84" s="22"/>
-      <c r="BC84" s="22"/>
-      <c r="BD84" s="22"/>
-      <c r="BE84" s="22"/>
-      <c r="BF84" s="22"/>
-      <c r="BG84" s="22"/>
-      <c r="BH84" s="22"/>
-      <c r="BI84" s="22"/>
-      <c r="BJ84" s="22"/>
-      <c r="BK84" s="22"/>
-      <c r="BL84" s="22"/>
-      <c r="BM84" s="22"/>
-      <c r="BN84" s="22"/>
-    </row>
-    <row r="85" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="8">
-        <v>166</v>
-      </c>
-      <c r="B85" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C85" s="31" t="s">
+      <c r="L84" s="8">
+        <v>1014</v>
+      </c>
+      <c r="M84" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="D85" s="58" t="s">
+      <c r="N84" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="E85" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="G85" s="8">
-        <v>401</v>
-      </c>
-      <c r="H85" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="I85" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J85" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K85" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L85" s="8">
-        <v>1014</v>
-      </c>
-      <c r="M85" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="N85" s="64" t="s">
+      <c r="O84" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O85" s="64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="105" t="s">
+    </row>
+    <row r="85" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="B86" s="105"/>
-      <c r="C86" s="105"/>
-      <c r="D86" s="105"/>
-      <c r="E86" s="105"/>
-      <c r="F86" s="105"/>
-      <c r="G86" s="105"/>
-      <c r="H86" s="105"/>
-      <c r="I86" s="105"/>
-      <c r="J86" s="105"/>
-      <c r="K86" s="105"/>
-      <c r="L86" s="105"/>
-      <c r="M86" s="105"/>
-      <c r="N86" s="105"/>
-      <c r="O86" s="105"/>
+      <c r="B85" s="106"/>
+      <c r="C85" s="106"/>
+      <c r="D85" s="106"/>
+      <c r="E85" s="106"/>
+      <c r="F85" s="106"/>
+      <c r="G85" s="106"/>
+      <c r="H85" s="106"/>
+      <c r="I85" s="106"/>
+      <c r="J85" s="106"/>
+      <c r="K85" s="106"/>
+      <c r="L85" s="106"/>
+      <c r="M85" s="106"/>
+      <c r="N85" s="106"/>
+      <c r="O85" s="106"/>
+      <c r="P85" s="21"/>
+      <c r="Q85" s="21"/>
+      <c r="R85" s="21"/>
+      <c r="S85" s="21"/>
+      <c r="T85" s="21"/>
+      <c r="U85" s="21"/>
+      <c r="V85" s="21"/>
+      <c r="W85" s="21"/>
+      <c r="X85" s="21"/>
+      <c r="Y85" s="21"/>
+      <c r="Z85" s="21"/>
+      <c r="AA85" s="21"/>
+      <c r="AB85" s="21"/>
+      <c r="AC85" s="21"/>
+      <c r="AD85" s="21"/>
+      <c r="AE85" s="21"/>
+      <c r="AF85" s="21"/>
+      <c r="AG85" s="21"/>
+      <c r="AH85" s="21"/>
+      <c r="AI85" s="21"/>
+      <c r="AJ85" s="21"/>
+      <c r="AK85" s="21"/>
+      <c r="AL85" s="21"/>
+      <c r="AM85" s="21"/>
+      <c r="AN85" s="21"/>
+      <c r="AO85" s="21"/>
+      <c r="AP85" s="21"/>
+      <c r="AQ85" s="21"/>
+      <c r="AR85" s="21"/>
+      <c r="AS85" s="21"/>
+      <c r="AT85" s="21"/>
+      <c r="AU85" s="21"/>
+      <c r="AV85" s="21"/>
+      <c r="AW85" s="21"/>
+      <c r="AX85" s="21"/>
+      <c r="AY85" s="21"/>
+      <c r="AZ85" s="21"/>
+      <c r="BA85" s="21"/>
+      <c r="BB85" s="21"/>
+      <c r="BC85" s="21"/>
+      <c r="BD85" s="21"/>
+      <c r="BE85" s="21"/>
+      <c r="BF85" s="21"/>
+      <c r="BG85" s="21"/>
+      <c r="BH85" s="21"/>
+      <c r="BI85" s="21"/>
+      <c r="BJ85" s="21"/>
+      <c r="BK85" s="21"/>
+      <c r="BL85" s="21"/>
+      <c r="BM85" s="21"/>
+      <c r="BN85" s="21"/>
+    </row>
+    <row r="86" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="107" t="s">
+        <v>146</v>
+      </c>
+      <c r="B86" s="107"/>
+      <c r="C86" s="107"/>
+      <c r="D86" s="107"/>
+      <c r="E86" s="107"/>
+      <c r="F86" s="107"/>
+      <c r="G86" s="107"/>
+      <c r="H86" s="107"/>
+      <c r="I86" s="107"/>
+      <c r="J86" s="107"/>
+      <c r="K86" s="107"/>
+      <c r="L86" s="107"/>
+      <c r="M86" s="107"/>
+      <c r="N86" s="107"/>
+      <c r="O86" s="107"/>
       <c r="P86" s="21"/>
       <c r="Q86" s="21"/>
       <c r="R86" s="21"/>
@@ -28793,24 +28812,52 @@
       <c r="BM86" s="21"/>
       <c r="BN86" s="21"/>
     </row>
-    <row r="87" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="106" t="s">
-        <v>146</v>
-      </c>
-      <c r="B87" s="106"/>
-      <c r="C87" s="106"/>
-      <c r="D87" s="106"/>
-      <c r="E87" s="106"/>
-      <c r="F87" s="106"/>
-      <c r="G87" s="106"/>
-      <c r="H87" s="106"/>
-      <c r="I87" s="106"/>
-      <c r="J87" s="106"/>
-      <c r="K87" s="106"/>
-      <c r="L87" s="106"/>
-      <c r="M87" s="106"/>
-      <c r="N87" s="106"/>
-      <c r="O87" s="106"/>
+    <row r="87" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="92">
+        <v>148</v>
+      </c>
+      <c r="B87" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C87" s="93" t="s">
+        <v>253</v>
+      </c>
+      <c r="D87" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="F87" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="G87" s="92">
+        <v>403</v>
+      </c>
+      <c r="H87" s="92" t="s">
+        <v>216</v>
+      </c>
+      <c r="I87" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J87" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K87" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L87" s="92">
+        <v>1111</v>
+      </c>
+      <c r="M87" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="N87" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O87" s="30" t="s">
+        <v>59</v>
+      </c>
       <c r="P87" s="21"/>
       <c r="Q87" s="21"/>
       <c r="R87" s="21"/>
@@ -28863,15 +28910,15 @@
       <c r="BM87" s="21"/>
       <c r="BN87" s="21"/>
     </row>
-    <row r="88" spans="1:66" s="11" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="92">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B88" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C88" s="93" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D88" s="92" t="s">
         <v>12</v>
@@ -28898,16 +28945,16 @@
         <v>32</v>
       </c>
       <c r="L88" s="92">
-        <v>1111</v>
+        <v>1016</v>
       </c>
       <c r="M88" s="93" t="s">
-        <v>252</v>
-      </c>
-      <c r="N88" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O88" s="30" t="s">
-        <v>59</v>
+        <v>245</v>
+      </c>
+      <c r="N88" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O88" s="93" t="s">
+        <v>12</v>
       </c>
       <c r="P88" s="21"/>
       <c r="Q88" s="21"/>
@@ -28961,50 +29008,50 @@
       <c r="BM88" s="21"/>
       <c r="BN88" s="21"/>
     </row>
-    <row r="89" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="92">
-        <v>146</v>
+    <row r="89" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <v>62</v>
       </c>
       <c r="B89" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C89" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D89" s="92" t="s">
+      <c r="C89" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E89" s="92" t="s">
+      <c r="E89" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F89" s="92" t="s">
+      <c r="F89" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G89" s="92">
-        <v>403</v>
-      </c>
-      <c r="H89" s="92" t="s">
+      <c r="G89" s="24">
+        <v>401</v>
+      </c>
+      <c r="H89" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I89" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J89" s="92" t="s">
+      <c r="J89" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K89" s="92" t="s">
+      <c r="K89" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L89" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M89" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N89" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O89" s="93" t="s">
+      <c r="L89" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M89" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N89" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O89" s="49" t="s">
         <v>12</v>
       </c>
       <c r="P89" s="21"/>
@@ -29059,160 +29106,160 @@
       <c r="BM89" s="21"/>
       <c r="BN89" s="21"/>
     </row>
-    <row r="90" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
-        <v>62</v>
-      </c>
-      <c r="B90" s="30" t="s">
+    <row r="90" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A90" s="92">
+        <v>63</v>
+      </c>
+      <c r="B90" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="C90" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="D90" s="4" t="s">
+      <c r="C90" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="D90" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E90" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G90" s="24">
+      <c r="G90" s="74">
         <v>401</v>
       </c>
       <c r="H90" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I90" s="24" t="s">
+      <c r="I90" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J90" s="4" t="s">
+      <c r="J90" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K90" s="4" t="s">
+      <c r="K90" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L90" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M90" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N90" s="32" t="s">
+      <c r="L90" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M90" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="N90" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="O90" s="49" t="s">
+      <c r="O90" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="P90" s="21"/>
-      <c r="Q90" s="21"/>
-      <c r="R90" s="21"/>
-      <c r="S90" s="21"/>
-      <c r="T90" s="21"/>
-      <c r="U90" s="21"/>
-      <c r="V90" s="21"/>
-      <c r="W90" s="21"/>
-      <c r="X90" s="21"/>
-      <c r="Y90" s="21"/>
-      <c r="Z90" s="21"/>
-      <c r="AA90" s="21"/>
-      <c r="AB90" s="21"/>
-      <c r="AC90" s="21"/>
-      <c r="AD90" s="21"/>
-      <c r="AE90" s="21"/>
-      <c r="AF90" s="21"/>
-      <c r="AG90" s="21"/>
-      <c r="AH90" s="21"/>
-      <c r="AI90" s="21"/>
-      <c r="AJ90" s="21"/>
-      <c r="AK90" s="21"/>
-      <c r="AL90" s="21"/>
-      <c r="AM90" s="21"/>
-      <c r="AN90" s="21"/>
-      <c r="AO90" s="21"/>
-      <c r="AP90" s="21"/>
-      <c r="AQ90" s="21"/>
-      <c r="AR90" s="21"/>
-      <c r="AS90" s="21"/>
-      <c r="AT90" s="21"/>
-      <c r="AU90" s="21"/>
-      <c r="AV90" s="21"/>
-      <c r="AW90" s="21"/>
-      <c r="AX90" s="21"/>
-      <c r="AY90" s="21"/>
-      <c r="AZ90" s="21"/>
-      <c r="BA90" s="21"/>
-      <c r="BB90" s="21"/>
-      <c r="BC90" s="21"/>
-      <c r="BD90" s="21"/>
-      <c r="BE90" s="21"/>
-      <c r="BF90" s="21"/>
-      <c r="BG90" s="21"/>
-      <c r="BH90" s="21"/>
-      <c r="BI90" s="21"/>
-      <c r="BJ90" s="21"/>
-      <c r="BK90" s="21"/>
-      <c r="BL90" s="21"/>
-      <c r="BM90" s="21"/>
-      <c r="BN90" s="21"/>
-    </row>
-    <row r="91" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A91" s="92">
-        <v>63</v>
-      </c>
-      <c r="B91" s="103" t="s">
+    </row>
+    <row r="91" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <v>65</v>
+      </c>
+      <c r="B91" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C91" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="D91" s="92" t="s">
+      <c r="C91" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E91" s="92" t="s">
+      <c r="E91" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F91" s="92" t="s">
+      <c r="F91" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G91" s="74">
-        <v>401</v>
+      <c r="G91" s="24">
+        <v>400</v>
       </c>
       <c r="H91" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I91" s="74" t="s">
+      <c r="I91" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J91" s="92" t="s">
+      <c r="J91" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="K91" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L91" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M91" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="N91" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="O91" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K91" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L91" s="25">
+        <v>1003</v>
+      </c>
+      <c r="M91" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="N91" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P91" s="22"/>
+      <c r="Q91" s="22"/>
+      <c r="R91" s="22"/>
+      <c r="S91" s="22"/>
+      <c r="T91" s="22"/>
+      <c r="U91" s="22"/>
+      <c r="V91" s="22"/>
+      <c r="W91" s="22"/>
+      <c r="X91" s="22"/>
+      <c r="Y91" s="22"/>
+      <c r="Z91" s="22"/>
+      <c r="AA91" s="22"/>
+      <c r="AB91" s="22"/>
+      <c r="AC91" s="22"/>
+      <c r="AD91" s="22"/>
+      <c r="AE91" s="22"/>
+      <c r="AF91" s="22"/>
+      <c r="AG91" s="22"/>
+      <c r="AH91" s="22"/>
+      <c r="AI91" s="22"/>
+      <c r="AJ91" s="22"/>
+      <c r="AK91" s="22"/>
+      <c r="AL91" s="22"/>
+      <c r="AM91" s="22"/>
+      <c r="AN91" s="22"/>
+      <c r="AO91" s="22"/>
+      <c r="AP91" s="22"/>
+      <c r="AQ91" s="22"/>
+      <c r="AR91" s="22"/>
+      <c r="AS91" s="22"/>
+      <c r="AT91" s="22"/>
+      <c r="AU91" s="22"/>
+      <c r="AV91" s="22"/>
+      <c r="AW91" s="22"/>
+      <c r="AX91" s="22"/>
+      <c r="AY91" s="22"/>
+      <c r="AZ91" s="22"/>
+      <c r="BA91" s="22"/>
+      <c r="BB91" s="22"/>
+      <c r="BC91" s="22"/>
+      <c r="BD91" s="22"/>
+      <c r="BE91" s="22"/>
+      <c r="BF91" s="22"/>
+      <c r="BG91" s="22"/>
+      <c r="BH91" s="22"/>
+      <c r="BI91" s="22"/>
+      <c r="BJ91" s="22"/>
+      <c r="BK91" s="22"/>
+      <c r="BL91" s="22"/>
+      <c r="BM91" s="22"/>
+      <c r="BN91" s="22"/>
+    </row>
+    <row r="92" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B92" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>264</v>
+        <v>86</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>12</v>
@@ -29232,22 +29279,22 @@
       <c r="I92" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J92" s="25" t="s">
+      <c r="J92" s="24" t="s">
         <v>7</v>
       </c>
       <c r="K92" s="24" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L92" s="25">
-        <v>1003</v>
-      </c>
-      <c r="M92" s="47" t="s">
-        <v>14</v>
+        <v>1004</v>
+      </c>
+      <c r="M92" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="N92" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="O92" s="4" t="s">
+      <c r="O92" s="30" t="s">
         <v>43</v>
       </c>
       <c r="P92" s="22"/>
@@ -29302,26 +29349,26 @@
       <c r="BM92" s="22"/>
       <c r="BN92" s="22"/>
     </row>
-    <row r="93" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="B93" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C93" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D93" s="4" t="s">
+      <c r="C93" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D93" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="E93" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="F93" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G93" s="24">
+      <c r="G93" s="54">
         <v>400</v>
       </c>
       <c r="H93" s="58" t="s">
@@ -29330,97 +29377,46 @@
       <c r="I93" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J93" s="24" t="s">
+      <c r="J93" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K93" s="24" t="s">
+      <c r="K93" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L93" s="25">
-        <v>1004</v>
-      </c>
-      <c r="M93" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="N93" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O93" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P93" s="22"/>
-      <c r="Q93" s="22"/>
-      <c r="R93" s="22"/>
-      <c r="S93" s="22"/>
-      <c r="T93" s="22"/>
-      <c r="U93" s="22"/>
-      <c r="V93" s="22"/>
-      <c r="W93" s="22"/>
-      <c r="X93" s="22"/>
-      <c r="Y93" s="22"/>
-      <c r="Z93" s="22"/>
-      <c r="AA93" s="22"/>
-      <c r="AB93" s="22"/>
-      <c r="AC93" s="22"/>
-      <c r="AD93" s="22"/>
-      <c r="AE93" s="22"/>
-      <c r="AF93" s="22"/>
-      <c r="AG93" s="22"/>
-      <c r="AH93" s="22"/>
-      <c r="AI93" s="22"/>
-      <c r="AJ93" s="22"/>
-      <c r="AK93" s="22"/>
-      <c r="AL93" s="22"/>
-      <c r="AM93" s="22"/>
-      <c r="AN93" s="22"/>
-      <c r="AO93" s="22"/>
-      <c r="AP93" s="22"/>
-      <c r="AQ93" s="22"/>
-      <c r="AR93" s="22"/>
-      <c r="AS93" s="22"/>
-      <c r="AT93" s="22"/>
-      <c r="AU93" s="22"/>
-      <c r="AV93" s="22"/>
-      <c r="AW93" s="22"/>
-      <c r="AX93" s="22"/>
-      <c r="AY93" s="22"/>
-      <c r="AZ93" s="22"/>
-      <c r="BA93" s="22"/>
-      <c r="BB93" s="22"/>
-      <c r="BC93" s="22"/>
-      <c r="BD93" s="22"/>
-      <c r="BE93" s="22"/>
-      <c r="BF93" s="22"/>
-      <c r="BG93" s="22"/>
-      <c r="BH93" s="22"/>
-      <c r="BI93" s="22"/>
-      <c r="BJ93" s="22"/>
-      <c r="BK93" s="22"/>
-      <c r="BL93" s="22"/>
-      <c r="BM93" s="22"/>
-      <c r="BN93" s="22"/>
-    </row>
-    <row r="94" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="L93" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M93" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N93" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O93" s="63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="B94" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C94" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D94" s="53" t="s">
+      <c r="C94" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E94" s="53" t="s">
+      <c r="E94" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F94" s="53" t="s">
+      <c r="F94" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G94" s="54">
-        <v>400</v>
+      <c r="G94" s="24">
+        <v>403</v>
       </c>
       <c r="H94" s="58" t="s">
         <v>216</v>
@@ -29428,34 +29424,85 @@
       <c r="I94" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J94" s="53" t="s">
+      <c r="J94" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K94" s="54" t="s">
+      <c r="K94" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L94" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M94" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N94" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O94" s="63" t="s">
-        <v>12</v>
-      </c>
+      <c r="L94" s="25">
+        <v>1006</v>
+      </c>
+      <c r="M94" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="N94" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="O94" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="P94" s="22"/>
+      <c r="Q94" s="22"/>
+      <c r="R94" s="22"/>
+      <c r="S94" s="22"/>
+      <c r="T94" s="22"/>
+      <c r="U94" s="22"/>
+      <c r="V94" s="22"/>
+      <c r="W94" s="22"/>
+      <c r="X94" s="22"/>
+      <c r="Y94" s="22"/>
+      <c r="Z94" s="22"/>
+      <c r="AA94" s="22"/>
+      <c r="AB94" s="22"/>
+      <c r="AC94" s="22"/>
+      <c r="AD94" s="22"/>
+      <c r="AE94" s="22"/>
+      <c r="AF94" s="22"/>
+      <c r="AG94" s="22"/>
+      <c r="AH94" s="22"/>
+      <c r="AI94" s="22"/>
+      <c r="AJ94" s="22"/>
+      <c r="AK94" s="22"/>
+      <c r="AL94" s="22"/>
+      <c r="AM94" s="22"/>
+      <c r="AN94" s="22"/>
+      <c r="AO94" s="22"/>
+      <c r="AP94" s="22"/>
+      <c r="AQ94" s="22"/>
+      <c r="AR94" s="22"/>
+      <c r="AS94" s="22"/>
+      <c r="AT94" s="22"/>
+      <c r="AU94" s="22"/>
+      <c r="AV94" s="22"/>
+      <c r="AW94" s="22"/>
+      <c r="AX94" s="22"/>
+      <c r="AY94" s="22"/>
+      <c r="AZ94" s="22"/>
+      <c r="BA94" s="22"/>
+      <c r="BB94" s="22"/>
+      <c r="BC94" s="22"/>
+      <c r="BD94" s="22"/>
+      <c r="BE94" s="22"/>
+      <c r="BF94" s="22"/>
+      <c r="BG94" s="22"/>
+      <c r="BH94" s="22"/>
+      <c r="BI94" s="22"/>
+      <c r="BJ94" s="22"/>
+      <c r="BK94" s="22"/>
+      <c r="BL94" s="22"/>
+      <c r="BM94" s="22"/>
+      <c r="BN94" s="22"/>
     </row>
     <row r="95" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B95" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>12</v>
@@ -29479,13 +29526,13 @@
         <v>7</v>
       </c>
       <c r="K95" s="24" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L95" s="25">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M95" s="30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N95" s="30" t="s">
         <v>60</v>
@@ -29547,13 +29594,13 @@
     </row>
     <row r="96" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B96" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>12</v>
@@ -29580,10 +29627,10 @@
         <v>30</v>
       </c>
       <c r="L96" s="25">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M96" s="30" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N96" s="30" t="s">
         <v>60</v>
@@ -29643,29 +29690,27 @@
       <c r="BM96" s="22"/>
       <c r="BN96" s="22"/>
     </row>
-    <row r="97" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A97" s="4">
-        <v>69</v>
-      </c>
+    <row r="97" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A97" s="4"/>
       <c r="B97" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D97" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D97" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="E97" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="F97" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G97" s="24">
+      <c r="G97" s="44">
         <v>403</v>
       </c>
-      <c r="H97" s="58" t="s">
+      <c r="H97" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I97" s="24" t="s">
@@ -29675,16 +29720,16 @@
         <v>7</v>
       </c>
       <c r="K97" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L97" s="25">
-        <v>1008</v>
-      </c>
-      <c r="M97" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="N97" s="30" t="s">
-        <v>60</v>
+        <v>32</v>
+      </c>
+      <c r="L97" s="24">
+        <v>1011</v>
+      </c>
+      <c r="M97" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="N97" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O97" s="30" t="s">
         <v>59</v>
@@ -29741,27 +29786,29 @@
       <c r="BM97" s="22"/>
       <c r="BN97" s="22"/>
     </row>
-    <row r="98" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
+    <row r="98" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>70</v>
+      </c>
       <c r="B98" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
       <c r="D98" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E98" s="24" t="s">
+      <c r="E98" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F98" s="24" t="s">
+      <c r="F98" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G98" s="44">
+      <c r="G98" s="24">
         <v>403</v>
       </c>
-      <c r="H98" s="24" t="s">
+      <c r="H98" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I98" s="24" t="s">
@@ -29779,11 +29826,11 @@
       <c r="M98" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N98" s="32" t="s">
-        <v>55</v>
+      <c r="N98" s="30" t="s">
+        <v>60</v>
       </c>
       <c r="O98" s="30" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="P98" s="22"/>
       <c r="Q98" s="22"/>
@@ -29839,15 +29886,15 @@
     </row>
     <row r="99" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B99" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D99" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="4" t="s">
@@ -29857,7 +29904,7 @@
         <v>140</v>
       </c>
       <c r="G99" s="24">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H99" s="58" t="s">
         <v>216</v>
@@ -29865,23 +29912,23 @@
       <c r="I99" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J99" s="24" t="s">
+      <c r="J99" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K99" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L99" s="24">
-        <v>1011</v>
-      </c>
-      <c r="M99" s="32" t="s">
-        <v>202</v>
+      <c r="K99" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L99" s="10">
+        <v>2506</v>
+      </c>
+      <c r="M99" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="N99" s="30" t="s">
         <v>60</v>
       </c>
       <c r="O99" s="30" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="P99" s="22"/>
       <c r="Q99" s="22"/>
@@ -29935,169 +29982,141 @@
       <c r="BM99" s="22"/>
       <c r="BN99" s="22"/>
     </row>
-    <row r="100" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
-        <v>71</v>
+    <row r="100" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="8">
+        <v>167</v>
       </c>
       <c r="B100" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D100" s="4" t="s">
+      <c r="C100" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D100" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="E100" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G100" s="24">
-        <v>404</v>
-      </c>
-      <c r="H100" s="58" t="s">
+      <c r="G100" s="8">
+        <v>401</v>
+      </c>
+      <c r="H100" s="54" t="s">
         <v>216</v>
       </c>
       <c r="I100" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J100" s="4" t="s">
+      <c r="J100" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K100" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L100" s="10">
-        <v>2506</v>
-      </c>
-      <c r="M100" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="N100" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O100" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P100" s="22"/>
-      <c r="Q100" s="22"/>
-      <c r="R100" s="22"/>
-      <c r="S100" s="22"/>
-      <c r="T100" s="22"/>
-      <c r="U100" s="22"/>
-      <c r="V100" s="22"/>
-      <c r="W100" s="22"/>
-      <c r="X100" s="22"/>
-      <c r="Y100" s="22"/>
-      <c r="Z100" s="22"/>
-      <c r="AA100" s="22"/>
-      <c r="AB100" s="22"/>
-      <c r="AC100" s="22"/>
-      <c r="AD100" s="22"/>
-      <c r="AE100" s="22"/>
-      <c r="AF100" s="22"/>
-      <c r="AG100" s="22"/>
-      <c r="AH100" s="22"/>
-      <c r="AI100" s="22"/>
-      <c r="AJ100" s="22"/>
-      <c r="AK100" s="22"/>
-      <c r="AL100" s="22"/>
-      <c r="AM100" s="22"/>
-      <c r="AN100" s="22"/>
-      <c r="AO100" s="22"/>
-      <c r="AP100" s="22"/>
-      <c r="AQ100" s="22"/>
-      <c r="AR100" s="22"/>
-      <c r="AS100" s="22"/>
-      <c r="AT100" s="22"/>
-      <c r="AU100" s="22"/>
-      <c r="AV100" s="22"/>
-      <c r="AW100" s="22"/>
-      <c r="AX100" s="22"/>
-      <c r="AY100" s="22"/>
-      <c r="AZ100" s="22"/>
-      <c r="BA100" s="22"/>
-      <c r="BB100" s="22"/>
-      <c r="BC100" s="22"/>
-      <c r="BD100" s="22"/>
-      <c r="BE100" s="22"/>
-      <c r="BF100" s="22"/>
-      <c r="BG100" s="22"/>
-      <c r="BH100" s="22"/>
-      <c r="BI100" s="22"/>
-      <c r="BJ100" s="22"/>
-      <c r="BK100" s="22"/>
-      <c r="BL100" s="22"/>
-      <c r="BM100" s="22"/>
-      <c r="BN100" s="22"/>
-    </row>
-    <row r="101" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="8">
-        <v>167</v>
-      </c>
-      <c r="B101" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C101" s="31" t="s">
+      <c r="K100" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L100" s="8">
+        <v>1014</v>
+      </c>
+      <c r="M100" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="D101" s="58" t="s">
+      <c r="N100" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="E101" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="G101" s="8">
-        <v>401</v>
-      </c>
-      <c r="H101" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="I101" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J101" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K101" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L101" s="8">
-        <v>1014</v>
-      </c>
-      <c r="M101" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="N101" s="64" t="s">
+      <c r="O100" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O101" s="64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="105" t="s">
+    </row>
+    <row r="101" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="106" t="s">
         <v>129</v>
       </c>
-      <c r="B102" s="105"/>
-      <c r="C102" s="105"/>
-      <c r="D102" s="105"/>
-      <c r="E102" s="105"/>
-      <c r="F102" s="105"/>
-      <c r="G102" s="105"/>
-      <c r="H102" s="105"/>
-      <c r="I102" s="105"/>
-      <c r="J102" s="105"/>
-      <c r="K102" s="105"/>
-      <c r="L102" s="105"/>
-      <c r="M102" s="105"/>
-      <c r="N102" s="105"/>
-      <c r="O102" s="105"/>
+      <c r="B101" s="106"/>
+      <c r="C101" s="106"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="106"/>
+      <c r="G101" s="106"/>
+      <c r="H101" s="106"/>
+      <c r="I101" s="106"/>
+      <c r="J101" s="106"/>
+      <c r="K101" s="106"/>
+      <c r="L101" s="106"/>
+      <c r="M101" s="106"/>
+      <c r="N101" s="106"/>
+      <c r="O101" s="106"/>
+      <c r="P101" s="21"/>
+      <c r="Q101" s="21"/>
+      <c r="R101" s="21"/>
+      <c r="S101" s="21"/>
+      <c r="T101" s="21"/>
+      <c r="U101" s="21"/>
+      <c r="V101" s="21"/>
+      <c r="W101" s="21"/>
+      <c r="X101" s="21"/>
+      <c r="Y101" s="21"/>
+      <c r="Z101" s="21"/>
+      <c r="AA101" s="21"/>
+      <c r="AB101" s="21"/>
+      <c r="AC101" s="21"/>
+      <c r="AD101" s="21"/>
+      <c r="AE101" s="21"/>
+      <c r="AF101" s="21"/>
+      <c r="AG101" s="21"/>
+      <c r="AH101" s="21"/>
+      <c r="AI101" s="21"/>
+      <c r="AJ101" s="21"/>
+      <c r="AK101" s="21"/>
+      <c r="AL101" s="21"/>
+      <c r="AM101" s="21"/>
+      <c r="AN101" s="21"/>
+      <c r="AO101" s="21"/>
+      <c r="AP101" s="21"/>
+      <c r="AQ101" s="21"/>
+      <c r="AR101" s="21"/>
+      <c r="AS101" s="21"/>
+      <c r="AT101" s="21"/>
+      <c r="AU101" s="21"/>
+      <c r="AV101" s="21"/>
+      <c r="AW101" s="21"/>
+      <c r="AX101" s="21"/>
+      <c r="AY101" s="21"/>
+      <c r="AZ101" s="21"/>
+      <c r="BA101" s="21"/>
+      <c r="BB101" s="21"/>
+      <c r="BC101" s="21"/>
+      <c r="BD101" s="21"/>
+      <c r="BE101" s="21"/>
+      <c r="BF101" s="21"/>
+      <c r="BG101" s="21"/>
+      <c r="BH101" s="21"/>
+      <c r="BI101" s="21"/>
+      <c r="BJ101" s="21"/>
+      <c r="BK101" s="21"/>
+      <c r="BL101" s="21"/>
+      <c r="BM101" s="21"/>
+      <c r="BN101" s="21"/>
+    </row>
+    <row r="102" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="107" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" s="107"/>
+      <c r="C102" s="107"/>
+      <c r="D102" s="107"/>
+      <c r="E102" s="107"/>
+      <c r="F102" s="107"/>
+      <c r="G102" s="107"/>
+      <c r="H102" s="107"/>
+      <c r="I102" s="107"/>
+      <c r="J102" s="107"/>
+      <c r="K102" s="107"/>
+      <c r="L102" s="107"/>
+      <c r="M102" s="107"/>
+      <c r="N102" s="107"/>
+      <c r="O102" s="107"/>
       <c r="P102" s="21"/>
       <c r="Q102" s="21"/>
       <c r="R102" s="21"/>
@@ -30150,24 +30169,52 @@
       <c r="BM102" s="21"/>
       <c r="BN102" s="21"/>
     </row>
-    <row r="103" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="106" t="s">
+    <row r="103" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="92">
         <v>146</v>
       </c>
-      <c r="B103" s="106"/>
-      <c r="C103" s="106"/>
-      <c r="D103" s="106"/>
-      <c r="E103" s="106"/>
-      <c r="F103" s="106"/>
-      <c r="G103" s="106"/>
-      <c r="H103" s="106"/>
-      <c r="I103" s="106"/>
-      <c r="J103" s="106"/>
-      <c r="K103" s="106"/>
-      <c r="L103" s="106"/>
-      <c r="M103" s="106"/>
-      <c r="N103" s="106"/>
-      <c r="O103" s="106"/>
+      <c r="B103" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C103" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D103" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="F103" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="G103" s="92">
+        <v>403</v>
+      </c>
+      <c r="H103" s="92" t="s">
+        <v>216</v>
+      </c>
+      <c r="I103" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J103" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K103" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L103" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M103" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N103" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O103" s="93" t="s">
+        <v>12</v>
+      </c>
       <c r="P103" s="21"/>
       <c r="Q103" s="21"/>
       <c r="R103" s="21"/>
@@ -30220,50 +30267,50 @@
       <c r="BM103" s="21"/>
       <c r="BN103" s="21"/>
     </row>
-    <row r="104" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="92">
-        <v>146</v>
+    <row r="104" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A104" s="4">
+        <v>72</v>
       </c>
       <c r="B104" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C104" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D104" s="92" t="s">
+      <c r="C104" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E104" s="92" t="s">
+      <c r="E104" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F104" s="92" t="s">
+      <c r="F104" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G104" s="92">
-        <v>403</v>
-      </c>
-      <c r="H104" s="92" t="s">
+      <c r="G104" s="24">
+        <v>401</v>
+      </c>
+      <c r="H104" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I104" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J104" s="92" t="s">
+      <c r="J104" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K104" s="92" t="s">
+      <c r="K104" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L104" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M104" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N104" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O104" s="93" t="s">
+      <c r="L104" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M104" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N104" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O104" s="49" t="s">
         <v>12</v>
       </c>
       <c r="P104" s="21"/>
@@ -30318,160 +30365,160 @@
       <c r="BM104" s="21"/>
       <c r="BN104" s="21"/>
     </row>
-    <row r="105" spans="1:66" s="50" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
-        <v>72</v>
-      </c>
-      <c r="B105" s="30" t="s">
+    <row r="105" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A105" s="92">
+        <v>73</v>
+      </c>
+      <c r="B105" s="104" t="s">
         <v>130</v>
       </c>
-      <c r="C105" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="D105" s="4" t="s">
+      <c r="C105" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="D105" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E105" s="4" t="s">
+      <c r="E105" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F105" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G105" s="24">
+      <c r="G105" s="74">
         <v>401</v>
       </c>
       <c r="H105" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I105" s="24" t="s">
+      <c r="I105" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J105" s="4" t="s">
+      <c r="J105" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K105" s="4" t="s">
+      <c r="K105" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L105" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M105" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N105" s="32" t="s">
+      <c r="L105" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M105" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="N105" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="O105" s="49" t="s">
+      <c r="O105" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="P105" s="21"/>
-      <c r="Q105" s="21"/>
-      <c r="R105" s="21"/>
-      <c r="S105" s="21"/>
-      <c r="T105" s="21"/>
-      <c r="U105" s="21"/>
-      <c r="V105" s="21"/>
-      <c r="W105" s="21"/>
-      <c r="X105" s="21"/>
-      <c r="Y105" s="21"/>
-      <c r="Z105" s="21"/>
-      <c r="AA105" s="21"/>
-      <c r="AB105" s="21"/>
-      <c r="AC105" s="21"/>
-      <c r="AD105" s="21"/>
-      <c r="AE105" s="21"/>
-      <c r="AF105" s="21"/>
-      <c r="AG105" s="21"/>
-      <c r="AH105" s="21"/>
-      <c r="AI105" s="21"/>
-      <c r="AJ105" s="21"/>
-      <c r="AK105" s="21"/>
-      <c r="AL105" s="21"/>
-      <c r="AM105" s="21"/>
-      <c r="AN105" s="21"/>
-      <c r="AO105" s="21"/>
-      <c r="AP105" s="21"/>
-      <c r="AQ105" s="21"/>
-      <c r="AR105" s="21"/>
-      <c r="AS105" s="21"/>
-      <c r="AT105" s="21"/>
-      <c r="AU105" s="21"/>
-      <c r="AV105" s="21"/>
-      <c r="AW105" s="21"/>
-      <c r="AX105" s="21"/>
-      <c r="AY105" s="21"/>
-      <c r="AZ105" s="21"/>
-      <c r="BA105" s="21"/>
-      <c r="BB105" s="21"/>
-      <c r="BC105" s="21"/>
-      <c r="BD105" s="21"/>
-      <c r="BE105" s="21"/>
-      <c r="BF105" s="21"/>
-      <c r="BG105" s="21"/>
-      <c r="BH105" s="21"/>
-      <c r="BI105" s="21"/>
-      <c r="BJ105" s="21"/>
-      <c r="BK105" s="21"/>
-      <c r="BL105" s="21"/>
-      <c r="BM105" s="21"/>
-      <c r="BN105" s="21"/>
-    </row>
-    <row r="106" spans="1:66" s="21" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A106" s="92">
-        <v>73</v>
-      </c>
-      <c r="B106" s="103" t="s">
+    </row>
+    <row r="106" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A106" s="4">
+        <v>75</v>
+      </c>
+      <c r="B106" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C106" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="D106" s="92" t="s">
+      <c r="C106" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E106" s="92" t="s">
+      <c r="E106" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F106" s="92" t="s">
+      <c r="F106" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G106" s="74">
-        <v>401</v>
+      <c r="G106" s="24">
+        <v>400</v>
       </c>
       <c r="H106" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I106" s="74" t="s">
+      <c r="I106" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J106" s="92" t="s">
+      <c r="J106" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K106" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L106" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M106" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="N106" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="O106" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K106" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L106" s="10">
+        <v>1003</v>
+      </c>
+      <c r="M106" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="N106" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="O106" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P106" s="22"/>
+      <c r="Q106" s="22"/>
+      <c r="R106" s="22"/>
+      <c r="S106" s="22"/>
+      <c r="T106" s="22"/>
+      <c r="U106" s="22"/>
+      <c r="V106" s="22"/>
+      <c r="W106" s="22"/>
+      <c r="X106" s="22"/>
+      <c r="Y106" s="22"/>
+      <c r="Z106" s="22"/>
+      <c r="AA106" s="22"/>
+      <c r="AB106" s="22"/>
+      <c r="AC106" s="22"/>
+      <c r="AD106" s="22"/>
+      <c r="AE106" s="22"/>
+      <c r="AF106" s="22"/>
+      <c r="AG106" s="22"/>
+      <c r="AH106" s="22"/>
+      <c r="AI106" s="22"/>
+      <c r="AJ106" s="22"/>
+      <c r="AK106" s="22"/>
+      <c r="AL106" s="22"/>
+      <c r="AM106" s="22"/>
+      <c r="AN106" s="22"/>
+      <c r="AO106" s="22"/>
+      <c r="AP106" s="22"/>
+      <c r="AQ106" s="22"/>
+      <c r="AR106" s="22"/>
+      <c r="AS106" s="22"/>
+      <c r="AT106" s="22"/>
+      <c r="AU106" s="22"/>
+      <c r="AV106" s="22"/>
+      <c r="AW106" s="22"/>
+      <c r="AX106" s="22"/>
+      <c r="AY106" s="22"/>
+      <c r="AZ106" s="22"/>
+      <c r="BA106" s="22"/>
+      <c r="BB106" s="22"/>
+      <c r="BC106" s="22"/>
+      <c r="BD106" s="22"/>
+      <c r="BE106" s="22"/>
+      <c r="BF106" s="22"/>
+      <c r="BG106" s="22"/>
+      <c r="BH106" s="22"/>
+      <c r="BI106" s="22"/>
+      <c r="BJ106" s="22"/>
+      <c r="BK106" s="22"/>
+      <c r="BL106" s="22"/>
+      <c r="BM106" s="22"/>
+      <c r="BN106" s="22"/>
+    </row>
+    <row r="107" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B107" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C107" s="23" t="s">
-        <v>264</v>
+      <c r="C107" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>12</v>
@@ -30495,13 +30542,13 @@
         <v>7</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L107" s="10">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M107" s="30" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N107" s="30" t="s">
         <v>131</v>
@@ -30561,15 +30608,15 @@
       <c r="BM107" s="22"/>
       <c r="BN107" s="22"/>
     </row>
-    <row r="108" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B108" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>12</v>
@@ -30593,13 +30640,13 @@
         <v>7</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L108" s="10">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M108" s="30" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="N108" s="30" t="s">
         <v>131</v>
@@ -30659,26 +30706,26 @@
       <c r="BM108" s="22"/>
       <c r="BN108" s="22"/>
     </row>
-    <row r="109" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="B109" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D109" s="4" t="s">
+      <c r="C109" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D109" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E109" s="4" t="s">
+      <c r="E109" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F109" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G109" s="24">
+      <c r="G109" s="54">
         <v>400</v>
       </c>
       <c r="H109" s="58" t="s">
@@ -30687,97 +30734,46 @@
       <c r="I109" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J109" s="4" t="s">
+      <c r="J109" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K109" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L109" s="10">
-        <v>1005</v>
-      </c>
-      <c r="M109" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="N109" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="O109" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P109" s="22"/>
-      <c r="Q109" s="22"/>
-      <c r="R109" s="22"/>
-      <c r="S109" s="22"/>
-      <c r="T109" s="22"/>
-      <c r="U109" s="22"/>
-      <c r="V109" s="22"/>
-      <c r="W109" s="22"/>
-      <c r="X109" s="22"/>
-      <c r="Y109" s="22"/>
-      <c r="Z109" s="22"/>
-      <c r="AA109" s="22"/>
-      <c r="AB109" s="22"/>
-      <c r="AC109" s="22"/>
-      <c r="AD109" s="22"/>
-      <c r="AE109" s="22"/>
-      <c r="AF109" s="22"/>
-      <c r="AG109" s="22"/>
-      <c r="AH109" s="22"/>
-      <c r="AI109" s="22"/>
-      <c r="AJ109" s="22"/>
-      <c r="AK109" s="22"/>
-      <c r="AL109" s="22"/>
-      <c r="AM109" s="22"/>
-      <c r="AN109" s="22"/>
-      <c r="AO109" s="22"/>
-      <c r="AP109" s="22"/>
-      <c r="AQ109" s="22"/>
-      <c r="AR109" s="22"/>
-      <c r="AS109" s="22"/>
-      <c r="AT109" s="22"/>
-      <c r="AU109" s="22"/>
-      <c r="AV109" s="22"/>
-      <c r="AW109" s="22"/>
-      <c r="AX109" s="22"/>
-      <c r="AY109" s="22"/>
-      <c r="AZ109" s="22"/>
-      <c r="BA109" s="22"/>
-      <c r="BB109" s="22"/>
-      <c r="BC109" s="22"/>
-      <c r="BD109" s="22"/>
-      <c r="BE109" s="22"/>
-      <c r="BF109" s="22"/>
-      <c r="BG109" s="22"/>
-      <c r="BH109" s="22"/>
-      <c r="BI109" s="22"/>
-      <c r="BJ109" s="22"/>
-      <c r="BK109" s="22"/>
-      <c r="BL109" s="22"/>
-      <c r="BM109" s="22"/>
-      <c r="BN109" s="22"/>
-    </row>
-    <row r="110" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K109" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L109" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M109" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N109" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O109" s="63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="B110" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C110" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D110" s="53" t="s">
+      <c r="C110" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E110" s="53" t="s">
+      <c r="E110" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F110" s="53" t="s">
+      <c r="F110" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G110" s="54">
-        <v>400</v>
+      <c r="G110" s="24">
+        <v>403</v>
       </c>
       <c r="H110" s="58" t="s">
         <v>216</v>
@@ -30785,34 +30781,85 @@
       <c r="I110" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J110" s="53" t="s">
+      <c r="J110" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K110" s="54" t="s">
+      <c r="K110" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L110" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M110" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N110" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O110" s="63" t="s">
-        <v>12</v>
-      </c>
+      <c r="L110" s="10">
+        <v>1006</v>
+      </c>
+      <c r="M110" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="N110" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="O110" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="P110" s="22"/>
+      <c r="Q110" s="22"/>
+      <c r="R110" s="22"/>
+      <c r="S110" s="22"/>
+      <c r="T110" s="22"/>
+      <c r="U110" s="22"/>
+      <c r="V110" s="22"/>
+      <c r="W110" s="22"/>
+      <c r="X110" s="22"/>
+      <c r="Y110" s="22"/>
+      <c r="Z110" s="22"/>
+      <c r="AA110" s="22"/>
+      <c r="AB110" s="22"/>
+      <c r="AC110" s="22"/>
+      <c r="AD110" s="22"/>
+      <c r="AE110" s="22"/>
+      <c r="AF110" s="22"/>
+      <c r="AG110" s="22"/>
+      <c r="AH110" s="22"/>
+      <c r="AI110" s="22"/>
+      <c r="AJ110" s="22"/>
+      <c r="AK110" s="22"/>
+      <c r="AL110" s="22"/>
+      <c r="AM110" s="22"/>
+      <c r="AN110" s="22"/>
+      <c r="AO110" s="22"/>
+      <c r="AP110" s="22"/>
+      <c r="AQ110" s="22"/>
+      <c r="AR110" s="22"/>
+      <c r="AS110" s="22"/>
+      <c r="AT110" s="22"/>
+      <c r="AU110" s="22"/>
+      <c r="AV110" s="22"/>
+      <c r="AW110" s="22"/>
+      <c r="AX110" s="22"/>
+      <c r="AY110" s="22"/>
+      <c r="AZ110" s="22"/>
+      <c r="BA110" s="22"/>
+      <c r="BB110" s="22"/>
+      <c r="BC110" s="22"/>
+      <c r="BD110" s="22"/>
+      <c r="BE110" s="22"/>
+      <c r="BF110" s="22"/>
+      <c r="BG110" s="22"/>
+      <c r="BH110" s="22"/>
+      <c r="BI110" s="22"/>
+      <c r="BJ110" s="22"/>
+      <c r="BK110" s="22"/>
+      <c r="BL110" s="22"/>
+      <c r="BM110" s="22"/>
+      <c r="BN110" s="22"/>
     </row>
     <row r="111" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B111" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>12</v>
@@ -30836,13 +30883,13 @@
         <v>7</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L111" s="10">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M111" s="30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N111" s="30" t="s">
         <v>131</v>
@@ -30902,15 +30949,15 @@
       <c r="BM111" s="22"/>
       <c r="BN111" s="22"/>
     </row>
-    <row r="112" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B112" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>12</v>
@@ -30937,10 +30984,10 @@
         <v>30</v>
       </c>
       <c r="L112" s="10">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M112" s="30" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N112" s="30" t="s">
         <v>131</v>
@@ -31000,48 +31047,46 @@
       <c r="BM112" s="22"/>
       <c r="BN112" s="22"/>
     </row>
-    <row r="113" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A113" s="4">
-        <v>80</v>
-      </c>
+    <row r="113" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A113" s="4"/>
       <c r="B113" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C113" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D113" s="4" t="s">
+      <c r="C113" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D113" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="E113" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F113" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G113" s="24">
+      <c r="G113" s="44">
         <v>403</v>
       </c>
-      <c r="H113" s="58" t="s">
+      <c r="H113" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I113" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J113" s="4" t="s">
+      <c r="J113" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K113" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L113" s="10">
-        <v>1008</v>
-      </c>
-      <c r="M113" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="N113" s="30" t="s">
-        <v>131</v>
+      <c r="K113" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L113" s="24">
+        <v>1011</v>
+      </c>
+      <c r="M113" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="N113" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O113" s="30" t="s">
         <v>59</v>
@@ -31098,49 +31143,51 @@
       <c r="BM113" s="22"/>
       <c r="BN113" s="22"/>
     </row>
-    <row r="114" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
+    <row r="114" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A114" s="4">
+        <v>81</v>
+      </c>
       <c r="B114" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C114" s="23" t="s">
-        <v>295</v>
+      <c r="C114" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="D114" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E114" s="24" t="s">
+      <c r="E114" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F114" s="24" t="s">
+      <c r="F114" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G114" s="44">
+      <c r="G114" s="24">
         <v>403</v>
       </c>
-      <c r="H114" s="24" t="s">
+      <c r="H114" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I114" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J114" s="24" t="s">
+      <c r="J114" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K114" s="24" t="s">
+      <c r="K114" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L114" s="24">
+      <c r="L114" s="4">
         <v>1011</v>
       </c>
       <c r="M114" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N114" s="32" t="s">
-        <v>55</v>
+      <c r="N114" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="O114" s="30" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="P114" s="22"/>
       <c r="Q114" s="22"/>
@@ -31194,27 +31241,27 @@
       <c r="BM114" s="22"/>
       <c r="BN114" s="22"/>
     </row>
-    <row r="115" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B115" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D115" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>140</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G115" s="24">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H115" s="58" t="s">
         <v>216</v>
@@ -31228,17 +31275,17 @@
       <c r="K115" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L115" s="4">
-        <v>1011</v>
-      </c>
-      <c r="M115" s="32" t="s">
-        <v>202</v>
+      <c r="L115" s="10">
+        <v>3001</v>
+      </c>
+      <c r="M115" s="30" t="s">
+        <v>211</v>
       </c>
       <c r="N115" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O115" s="30" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="P115" s="22"/>
       <c r="Q115" s="22"/>
@@ -31292,15 +31339,15 @@
       <c r="BM115" s="22"/>
       <c r="BN115" s="22"/>
     </row>
-    <row r="116" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B116" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>210</v>
+        <v>113</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>12</v>
@@ -31309,7 +31356,7 @@
         <v>140</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G116" s="24">
         <v>400</v>
@@ -31324,19 +31371,19 @@
         <v>7</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="L116" s="10">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="M116" s="30" t="s">
-        <v>211</v>
+        <v>28</v>
       </c>
       <c r="N116" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O116" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P116" s="22"/>
       <c r="Q116" s="22"/>
@@ -31391,14 +31438,14 @@
       <c r="BN116" s="22"/>
     </row>
     <row r="117" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A117" s="4">
-        <v>83</v>
+      <c r="A117" s="26">
+        <v>137</v>
       </c>
       <c r="B117" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>113</v>
+      <c r="C117" s="71" t="s">
+        <v>207</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>12</v>
@@ -31406,8 +31453,8 @@
       <c r="E117" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F117" s="4" t="s">
-        <v>140</v>
+      <c r="F117" s="26" t="s">
+        <v>141</v>
       </c>
       <c r="G117" s="24">
         <v>400</v>
@@ -31424,17 +31471,17 @@
       <c r="K117" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L117" s="10">
-        <v>3002</v>
-      </c>
-      <c r="M117" s="30" t="s">
-        <v>28</v>
+      <c r="L117" s="26">
+        <v>3009</v>
+      </c>
+      <c r="M117" s="71" t="s">
+        <v>207</v>
       </c>
       <c r="N117" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O117" s="30" t="s">
-        <v>66</v>
+      <c r="O117" s="33" t="s">
+        <v>212</v>
       </c>
       <c r="P117" s="22"/>
       <c r="Q117" s="22"/>
@@ -31488,15 +31535,15 @@
       <c r="BM117" s="22"/>
       <c r="BN117" s="22"/>
     </row>
-    <row r="118" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="26">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B118" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C118" s="71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>12</v>
@@ -31520,81 +31567,81 @@
         <v>7</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L118" s="26">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="M118" s="71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N118" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O118" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="P118" s="22"/>
-      <c r="Q118" s="22"/>
-      <c r="R118" s="22"/>
-      <c r="S118" s="22"/>
-      <c r="T118" s="22"/>
-      <c r="U118" s="22"/>
-      <c r="V118" s="22"/>
-      <c r="W118" s="22"/>
-      <c r="X118" s="22"/>
-      <c r="Y118" s="22"/>
-      <c r="Z118" s="22"/>
-      <c r="AA118" s="22"/>
-      <c r="AB118" s="22"/>
-      <c r="AC118" s="22"/>
-      <c r="AD118" s="22"/>
-      <c r="AE118" s="22"/>
-      <c r="AF118" s="22"/>
-      <c r="AG118" s="22"/>
-      <c r="AH118" s="22"/>
-      <c r="AI118" s="22"/>
-      <c r="AJ118" s="22"/>
-      <c r="AK118" s="22"/>
-      <c r="AL118" s="22"/>
-      <c r="AM118" s="22"/>
-      <c r="AN118" s="22"/>
-      <c r="AO118" s="22"/>
-      <c r="AP118" s="22"/>
-      <c r="AQ118" s="22"/>
-      <c r="AR118" s="22"/>
-      <c r="AS118" s="22"/>
-      <c r="AT118" s="22"/>
-      <c r="AU118" s="22"/>
-      <c r="AV118" s="22"/>
-      <c r="AW118" s="22"/>
-      <c r="AX118" s="22"/>
-      <c r="AY118" s="22"/>
-      <c r="AZ118" s="22"/>
-      <c r="BA118" s="22"/>
-      <c r="BB118" s="22"/>
-      <c r="BC118" s="22"/>
-      <c r="BD118" s="22"/>
-      <c r="BE118" s="22"/>
-      <c r="BF118" s="22"/>
-      <c r="BG118" s="22"/>
-      <c r="BH118" s="22"/>
-      <c r="BI118" s="22"/>
-      <c r="BJ118" s="22"/>
-      <c r="BK118" s="22"/>
-      <c r="BL118" s="22"/>
-      <c r="BM118" s="22"/>
-      <c r="BN118" s="22"/>
-    </row>
-    <row r="119" spans="1:66" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="P118" s="21"/>
+      <c r="Q118" s="21"/>
+      <c r="R118" s="21"/>
+      <c r="S118" s="21"/>
+      <c r="T118" s="21"/>
+      <c r="U118" s="21"/>
+      <c r="V118" s="21"/>
+      <c r="W118" s="21"/>
+      <c r="X118" s="21"/>
+      <c r="Y118" s="21"/>
+      <c r="Z118" s="21"/>
+      <c r="AA118" s="21"/>
+      <c r="AB118" s="21"/>
+      <c r="AC118" s="21"/>
+      <c r="AD118" s="21"/>
+      <c r="AE118" s="21"/>
+      <c r="AF118" s="21"/>
+      <c r="AG118" s="21"/>
+      <c r="AH118" s="21"/>
+      <c r="AI118" s="21"/>
+      <c r="AJ118" s="21"/>
+      <c r="AK118" s="21"/>
+      <c r="AL118" s="21"/>
+      <c r="AM118" s="21"/>
+      <c r="AN118" s="21"/>
+      <c r="AO118" s="21"/>
+      <c r="AP118" s="21"/>
+      <c r="AQ118" s="21"/>
+      <c r="AR118" s="21"/>
+      <c r="AS118" s="21"/>
+      <c r="AT118" s="21"/>
+      <c r="AU118" s="21"/>
+      <c r="AV118" s="21"/>
+      <c r="AW118" s="21"/>
+      <c r="AX118" s="21"/>
+      <c r="AY118" s="21"/>
+      <c r="AZ118" s="21"/>
+      <c r="BA118" s="21"/>
+      <c r="BB118" s="21"/>
+      <c r="BC118" s="21"/>
+      <c r="BD118" s="21"/>
+      <c r="BE118" s="21"/>
+      <c r="BF118" s="21"/>
+      <c r="BG118" s="21"/>
+      <c r="BH118" s="21"/>
+      <c r="BI118" s="21"/>
+      <c r="BJ118" s="21"/>
+      <c r="BK118" s="21"/>
+      <c r="BL118" s="21"/>
+      <c r="BM118" s="21"/>
+      <c r="BN118" s="21"/>
+    </row>
+    <row r="119" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A119" s="26">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B119" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C119" s="71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>12</v>
@@ -31621,10 +31668,10 @@
         <v>30</v>
       </c>
       <c r="L119" s="26">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="M119" s="71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N119" s="30" t="s">
         <v>131</v>
@@ -31684,15 +31731,15 @@
       <c r="BM119" s="21"/>
       <c r="BN119" s="21"/>
     </row>
-    <row r="120" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A120" s="26">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B120" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C120" s="71" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>12</v>
@@ -31704,7 +31751,7 @@
         <v>141</v>
       </c>
       <c r="G120" s="24">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H120" s="58" t="s">
         <v>216</v>
@@ -31719,16 +31766,16 @@
         <v>30</v>
       </c>
       <c r="L120" s="26">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="M120" s="71" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="N120" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O120" s="33" t="s">
-        <v>213</v>
+      <c r="O120" s="30" t="s">
+        <v>12</v>
       </c>
       <c r="P120" s="21"/>
       <c r="Q120" s="21"/>
@@ -31784,13 +31831,13 @@
     </row>
     <row r="121" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A121" s="26">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B121" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C121" s="71" t="s">
-        <v>221</v>
+      <c r="C121" s="84" t="s">
+        <v>229</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>12</v>
@@ -31798,11 +31845,11 @@
       <c r="E121" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F121" s="26" t="s">
-        <v>141</v>
+      <c r="F121" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="G121" s="24">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H121" s="58" t="s">
         <v>216</v>
@@ -31817,16 +31864,16 @@
         <v>30</v>
       </c>
       <c r="L121" s="26">
-        <v>3012</v>
-      </c>
-      <c r="M121" s="71" t="s">
-        <v>222</v>
+        <v>3013</v>
+      </c>
+      <c r="M121" s="84" t="s">
+        <v>230</v>
       </c>
       <c r="N121" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O121" s="30" t="s">
-        <v>12</v>
+        <v>231</v>
       </c>
       <c r="P121" s="21"/>
       <c r="Q121" s="21"/>
@@ -31880,26 +31927,26 @@
       <c r="BM121" s="21"/>
       <c r="BN121" s="21"/>
     </row>
-    <row r="122" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A122" s="26">
-        <v>141</v>
-      </c>
-      <c r="B122" s="30" t="s">
+    <row r="122" spans="1:66" s="50" customFormat="1" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A122" s="58">
+        <v>84</v>
+      </c>
+      <c r="B122" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C122" s="84" t="s">
-        <v>229</v>
-      </c>
-      <c r="D122" s="4" t="s">
+      <c r="C122" s="60" t="s">
+        <v>165</v>
+      </c>
+      <c r="D122" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E122" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="F122" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="G122" s="24">
+      <c r="G122" s="58">
         <v>400</v>
       </c>
       <c r="H122" s="58" t="s">
@@ -31908,23 +31955,23 @@
       <c r="I122" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J122" s="4" t="s">
+      <c r="J122" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K122" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L122" s="26">
-        <v>3013</v>
-      </c>
-      <c r="M122" s="84" t="s">
-        <v>230</v>
-      </c>
-      <c r="N122" s="30" t="s">
+      <c r="K122" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="L122" s="58">
+        <v>1002</v>
+      </c>
+      <c r="M122" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="N122" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="O122" s="30" t="s">
-        <v>231</v>
+      <c r="O122" s="59" t="s">
+        <v>66</v>
       </c>
       <c r="P122" s="21"/>
       <c r="Q122" s="21"/>
@@ -31980,13 +32027,13 @@
     </row>
     <row r="123" spans="1:66" s="50" customFormat="1" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="B123" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C123" s="60" t="s">
-        <v>165</v>
+      <c r="C123" s="97" t="s">
+        <v>280</v>
       </c>
       <c r="D123" s="58" t="s">
         <v>12</v>
@@ -32013,16 +32060,16 @@
         <v>11</v>
       </c>
       <c r="L123" s="58">
-        <v>1002</v>
-      </c>
-      <c r="M123" s="59" t="s">
-        <v>167</v>
-      </c>
-      <c r="N123" s="59" t="s">
+        <v>3014</v>
+      </c>
+      <c r="M123" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="N123" s="30" t="s">
         <v>131</v>
       </c>
       <c r="O123" s="59" t="s">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="P123" s="21"/>
       <c r="Q123" s="21"/>
@@ -32076,365 +32123,337 @@
       <c r="BM123" s="21"/>
       <c r="BN123" s="21"/>
     </row>
-    <row r="124" spans="1:66" s="50" customFormat="1" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A124" s="58">
-        <v>156</v>
-      </c>
-      <c r="B124" s="59" t="s">
+    <row r="124" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="8">
+        <v>168</v>
+      </c>
+      <c r="B124" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C124" s="97" t="s">
-        <v>280</v>
+      <c r="C124" s="31" t="s">
+        <v>298</v>
       </c>
       <c r="D124" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E124" s="72" t="s">
+      <c r="E124" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F124" s="72" t="s">
+      <c r="F124" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G124" s="58">
-        <v>400</v>
-      </c>
-      <c r="H124" s="58" t="s">
+      <c r="G124" s="8">
+        <v>401</v>
+      </c>
+      <c r="H124" s="54" t="s">
         <v>216</v>
       </c>
       <c r="I124" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J124" s="58" t="s">
+      <c r="J124" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K124" s="58" t="s">
+      <c r="K124" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L124" s="8">
+        <v>1014</v>
+      </c>
+      <c r="M124" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="N124" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O124" s="64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A125" s="107" t="s">
+        <v>145</v>
+      </c>
+      <c r="B125" s="107"/>
+      <c r="C125" s="107"/>
+      <c r="D125" s="107"/>
+      <c r="E125" s="107"/>
+      <c r="F125" s="107"/>
+      <c r="G125" s="107"/>
+      <c r="H125" s="107"/>
+      <c r="I125" s="107"/>
+      <c r="J125" s="107"/>
+      <c r="K125" s="107"/>
+      <c r="L125" s="107"/>
+      <c r="M125" s="107"/>
+      <c r="N125" s="107"/>
+      <c r="O125" s="107"/>
+      <c r="P125" s="21"/>
+      <c r="Q125" s="21"/>
+      <c r="R125" s="21"/>
+      <c r="S125" s="21"/>
+      <c r="T125" s="21"/>
+      <c r="U125" s="21"/>
+      <c r="V125" s="21"/>
+      <c r="W125" s="21"/>
+      <c r="X125" s="21"/>
+      <c r="Y125" s="21"/>
+      <c r="Z125" s="21"/>
+      <c r="AA125" s="21"/>
+      <c r="AB125" s="21"/>
+      <c r="AC125" s="21"/>
+      <c r="AD125" s="21"/>
+      <c r="AE125" s="21"/>
+      <c r="AF125" s="21"/>
+      <c r="AG125" s="21"/>
+      <c r="AH125" s="21"/>
+      <c r="AI125" s="21"/>
+      <c r="AJ125" s="21"/>
+      <c r="AK125" s="21"/>
+      <c r="AL125" s="21"/>
+      <c r="AM125" s="21"/>
+      <c r="AN125" s="21"/>
+      <c r="AO125" s="21"/>
+      <c r="AP125" s="21"/>
+      <c r="AQ125" s="21"/>
+      <c r="AR125" s="21"/>
+      <c r="AS125" s="21"/>
+      <c r="AT125" s="21"/>
+      <c r="AU125" s="21"/>
+      <c r="AV125" s="21"/>
+      <c r="AW125" s="21"/>
+      <c r="AX125" s="21"/>
+      <c r="AY125" s="21"/>
+      <c r="AZ125" s="21"/>
+      <c r="BA125" s="21"/>
+      <c r="BB125" s="21"/>
+      <c r="BC125" s="21"/>
+      <c r="BD125" s="21"/>
+      <c r="BE125" s="21"/>
+      <c r="BF125" s="21"/>
+      <c r="BG125" s="21"/>
+      <c r="BH125" s="21"/>
+      <c r="BI125" s="21"/>
+      <c r="BJ125" s="21"/>
+      <c r="BK125" s="21"/>
+      <c r="BL125" s="21"/>
+      <c r="BM125" s="21"/>
+      <c r="BN125" s="21"/>
+    </row>
+    <row r="126" spans="1:66" s="36" customFormat="1" ht="49.7" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A126" s="38">
+        <v>145</v>
+      </c>
+      <c r="B126" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C126" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D126" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F126" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="G126" s="24">
+        <v>400</v>
+      </c>
+      <c r="H126" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="I126" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J126" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="K126" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L124" s="58">
-        <v>3014</v>
-      </c>
-      <c r="M124" s="97" t="s">
-        <v>280</v>
-      </c>
-      <c r="N124" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="O124" s="59" t="s">
-        <v>279</v>
-      </c>
-      <c r="P124" s="21"/>
-      <c r="Q124" s="21"/>
-      <c r="R124" s="21"/>
-      <c r="S124" s="21"/>
-      <c r="T124" s="21"/>
-      <c r="U124" s="21"/>
-      <c r="V124" s="21"/>
-      <c r="W124" s="21"/>
-      <c r="X124" s="21"/>
-      <c r="Y124" s="21"/>
-      <c r="Z124" s="21"/>
-      <c r="AA124" s="21"/>
-      <c r="AB124" s="21"/>
-      <c r="AC124" s="21"/>
-      <c r="AD124" s="21"/>
-      <c r="AE124" s="21"/>
-      <c r="AF124" s="21"/>
-      <c r="AG124" s="21"/>
-      <c r="AH124" s="21"/>
-      <c r="AI124" s="21"/>
-      <c r="AJ124" s="21"/>
-      <c r="AK124" s="21"/>
-      <c r="AL124" s="21"/>
-      <c r="AM124" s="21"/>
-      <c r="AN124" s="21"/>
-      <c r="AO124" s="21"/>
-      <c r="AP124" s="21"/>
-      <c r="AQ124" s="21"/>
-      <c r="AR124" s="21"/>
-      <c r="AS124" s="21"/>
-      <c r="AT124" s="21"/>
-      <c r="AU124" s="21"/>
-      <c r="AV124" s="21"/>
-      <c r="AW124" s="21"/>
-      <c r="AX124" s="21"/>
-      <c r="AY124" s="21"/>
-      <c r="AZ124" s="21"/>
-      <c r="BA124" s="21"/>
-      <c r="BB124" s="21"/>
-      <c r="BC124" s="21"/>
-      <c r="BD124" s="21"/>
-      <c r="BE124" s="21"/>
-      <c r="BF124" s="21"/>
-      <c r="BG124" s="21"/>
-      <c r="BH124" s="21"/>
-      <c r="BI124" s="21"/>
-      <c r="BJ124" s="21"/>
-      <c r="BK124" s="21"/>
-      <c r="BL124" s="21"/>
-      <c r="BM124" s="21"/>
-      <c r="BN124" s="21"/>
-    </row>
-    <row r="125" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="8">
-        <v>168</v>
-      </c>
-      <c r="B125" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C125" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="D125" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="G125" s="8">
-        <v>401</v>
-      </c>
-      <c r="H125" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="I125" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J125" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K125" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L125" s="8">
-        <v>1014</v>
-      </c>
-      <c r="M125" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="N125" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O125" s="64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A126" s="106" t="s">
-        <v>145</v>
-      </c>
-      <c r="B126" s="106"/>
-      <c r="C126" s="106"/>
-      <c r="D126" s="106"/>
-      <c r="E126" s="106"/>
-      <c r="F126" s="106"/>
-      <c r="G126" s="106"/>
-      <c r="H126" s="106"/>
-      <c r="I126" s="106"/>
-      <c r="J126" s="106"/>
-      <c r="K126" s="106"/>
-      <c r="L126" s="106"/>
-      <c r="M126" s="106"/>
-      <c r="N126" s="106"/>
-      <c r="O126" s="106"/>
-      <c r="P126" s="21"/>
-      <c r="Q126" s="21"/>
-      <c r="R126" s="21"/>
-      <c r="S126" s="21"/>
-      <c r="T126" s="21"/>
-      <c r="U126" s="21"/>
-      <c r="V126" s="21"/>
-      <c r="W126" s="21"/>
-      <c r="X126" s="21"/>
-      <c r="Y126" s="21"/>
-      <c r="Z126" s="21"/>
-      <c r="AA126" s="21"/>
-      <c r="AB126" s="21"/>
-      <c r="AC126" s="21"/>
-      <c r="AD126" s="21"/>
-      <c r="AE126" s="21"/>
-      <c r="AF126" s="21"/>
-      <c r="AG126" s="21"/>
-      <c r="AH126" s="21"/>
-      <c r="AI126" s="21"/>
-      <c r="AJ126" s="21"/>
-      <c r="AK126" s="21"/>
-      <c r="AL126" s="21"/>
-      <c r="AM126" s="21"/>
-      <c r="AN126" s="21"/>
-      <c r="AO126" s="21"/>
-      <c r="AP126" s="21"/>
-      <c r="AQ126" s="21"/>
-      <c r="AR126" s="21"/>
-      <c r="AS126" s="21"/>
-      <c r="AT126" s="21"/>
-      <c r="AU126" s="21"/>
-      <c r="AV126" s="21"/>
-      <c r="AW126" s="21"/>
-      <c r="AX126" s="21"/>
-      <c r="AY126" s="21"/>
-      <c r="AZ126" s="21"/>
-      <c r="BA126" s="21"/>
-      <c r="BB126" s="21"/>
-      <c r="BC126" s="21"/>
-      <c r="BD126" s="21"/>
-      <c r="BE126" s="21"/>
-      <c r="BF126" s="21"/>
-      <c r="BG126" s="21"/>
-      <c r="BH126" s="21"/>
-      <c r="BI126" s="21"/>
-      <c r="BJ126" s="21"/>
-      <c r="BK126" s="21"/>
-      <c r="BL126" s="21"/>
-      <c r="BM126" s="21"/>
-      <c r="BN126" s="21"/>
-    </row>
-    <row r="127" spans="1:66" s="36" customFormat="1" ht="49.7" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A127" s="38">
-        <v>145</v>
+      <c r="L126" s="86">
+        <v>3008</v>
+      </c>
+      <c r="M126" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="N126" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="O126" s="87" t="s">
+        <v>242</v>
+      </c>
+      <c r="P126" s="35"/>
+      <c r="Q126" s="35"/>
+      <c r="R126" s="35"/>
+      <c r="S126" s="35"/>
+      <c r="T126" s="35"/>
+      <c r="U126" s="35"/>
+      <c r="V126" s="35"/>
+      <c r="W126" s="35"/>
+      <c r="X126" s="35"/>
+      <c r="Y126" s="35"/>
+      <c r="Z126" s="35"/>
+      <c r="AA126" s="35"/>
+      <c r="AB126" s="35"/>
+      <c r="AC126" s="35"/>
+      <c r="AD126" s="35"/>
+      <c r="AE126" s="35"/>
+      <c r="AF126" s="35"/>
+      <c r="AG126" s="35"/>
+      <c r="AH126" s="35"/>
+      <c r="AI126" s="35"/>
+      <c r="AJ126" s="35"/>
+      <c r="AK126" s="35"/>
+      <c r="AL126" s="35"/>
+      <c r="AM126" s="35"/>
+      <c r="AN126" s="35"/>
+      <c r="AO126" s="35"/>
+      <c r="AP126" s="35"/>
+      <c r="AQ126" s="35"/>
+      <c r="AR126" s="35"/>
+      <c r="AS126" s="35"/>
+      <c r="AT126" s="35"/>
+      <c r="AU126" s="35"/>
+      <c r="AV126" s="35"/>
+      <c r="AW126" s="35"/>
+      <c r="AX126" s="35"/>
+      <c r="AY126" s="35"/>
+      <c r="AZ126" s="35"/>
+      <c r="BA126" s="35"/>
+      <c r="BB126" s="35"/>
+      <c r="BC126" s="35"/>
+      <c r="BD126" s="35"/>
+      <c r="BE126" s="35"/>
+      <c r="BF126" s="35"/>
+      <c r="BG126" s="35"/>
+      <c r="BH126" s="35"/>
+      <c r="BI126" s="35"/>
+      <c r="BJ126" s="35"/>
+      <c r="BK126" s="35"/>
+      <c r="BL126" s="35"/>
+      <c r="BM126" s="35"/>
+      <c r="BN126" s="35"/>
+    </row>
+    <row r="127" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A127" s="4">
+        <v>85</v>
       </c>
       <c r="B127" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C127" s="41" t="s">
-        <v>241</v>
-      </c>
-      <c r="D127" s="38" t="s">
-        <v>12</v>
+      <c r="C127" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D127" s="4">
+        <v>8</v>
       </c>
       <c r="E127" s="24" t="s">
         <v>140</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="G127" s="24">
-        <v>400</v>
+        <v>140</v>
+      </c>
+      <c r="G127" s="44">
+        <v>200</v>
       </c>
       <c r="H127" s="24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I127" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J127" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="J127" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K127" s="38" t="s">
+      <c r="K127" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L127" s="86">
-        <v>3008</v>
-      </c>
-      <c r="M127" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="N127" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="O127" s="87" t="s">
-        <v>242</v>
-      </c>
-      <c r="P127" s="35"/>
-      <c r="Q127" s="35"/>
-      <c r="R127" s="35"/>
-      <c r="S127" s="35"/>
-      <c r="T127" s="35"/>
-      <c r="U127" s="35"/>
-      <c r="V127" s="35"/>
-      <c r="W127" s="35"/>
-      <c r="X127" s="35"/>
-      <c r="Y127" s="35"/>
-      <c r="Z127" s="35"/>
-      <c r="AA127" s="35"/>
-      <c r="AB127" s="35"/>
-      <c r="AC127" s="35"/>
-      <c r="AD127" s="35"/>
-      <c r="AE127" s="35"/>
-      <c r="AF127" s="35"/>
-      <c r="AG127" s="35"/>
-      <c r="AH127" s="35"/>
-      <c r="AI127" s="35"/>
-      <c r="AJ127" s="35"/>
-      <c r="AK127" s="35"/>
-      <c r="AL127" s="35"/>
-      <c r="AM127" s="35"/>
-      <c r="AN127" s="35"/>
-      <c r="AO127" s="35"/>
-      <c r="AP127" s="35"/>
-      <c r="AQ127" s="35"/>
-      <c r="AR127" s="35"/>
-      <c r="AS127" s="35"/>
-      <c r="AT127" s="35"/>
-      <c r="AU127" s="35"/>
-      <c r="AV127" s="35"/>
-      <c r="AW127" s="35"/>
-      <c r="AX127" s="35"/>
-      <c r="AY127" s="35"/>
-      <c r="AZ127" s="35"/>
-      <c r="BA127" s="35"/>
-      <c r="BB127" s="35"/>
-      <c r="BC127" s="35"/>
-      <c r="BD127" s="35"/>
-      <c r="BE127" s="35"/>
-      <c r="BF127" s="35"/>
-      <c r="BG127" s="35"/>
-      <c r="BH127" s="35"/>
-      <c r="BI127" s="35"/>
-      <c r="BJ127" s="35"/>
-      <c r="BK127" s="35"/>
-      <c r="BL127" s="35"/>
-      <c r="BM127" s="35"/>
-      <c r="BN127" s="35"/>
-    </row>
-    <row r="128" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A128" s="4">
-        <v>85</v>
-      </c>
-      <c r="B128" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D128" s="4">
-        <v>8</v>
-      </c>
-      <c r="E128" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="F128" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="G128" s="44">
-        <v>200</v>
-      </c>
-      <c r="H128" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="I128" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="J128" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L128" s="4">
+      <c r="L127" s="4">
         <v>1010</v>
       </c>
-      <c r="M128" s="30" t="s">
+      <c r="M127" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="N128" s="30" t="s">
+      <c r="N127" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O128" s="30" t="s">
+      <c r="O127" s="30" t="s">
         <v>1</v>
       </c>
+      <c r="P127" s="22"/>
+      <c r="Q127" s="22"/>
+      <c r="R127" s="22"/>
+      <c r="S127" s="22"/>
+      <c r="T127" s="22"/>
+      <c r="U127" s="22"/>
+      <c r="V127" s="22"/>
+      <c r="W127" s="22"/>
+      <c r="X127" s="22"/>
+      <c r="Y127" s="22"/>
+      <c r="Z127" s="22"/>
+      <c r="AA127" s="22"/>
+      <c r="AB127" s="22"/>
+      <c r="AC127" s="22"/>
+      <c r="AD127" s="22"/>
+      <c r="AE127" s="22"/>
+      <c r="AF127" s="22"/>
+      <c r="AG127" s="22"/>
+      <c r="AH127" s="22"/>
+      <c r="AI127" s="22"/>
+      <c r="AJ127" s="22"/>
+      <c r="AK127" s="22"/>
+      <c r="AL127" s="22"/>
+      <c r="AM127" s="22"/>
+      <c r="AN127" s="22"/>
+      <c r="AO127" s="22"/>
+      <c r="AP127" s="22"/>
+      <c r="AQ127" s="22"/>
+      <c r="AR127" s="22"/>
+      <c r="AS127" s="22"/>
+      <c r="AT127" s="22"/>
+      <c r="AU127" s="22"/>
+      <c r="AV127" s="22"/>
+      <c r="AW127" s="22"/>
+      <c r="AX127" s="22"/>
+      <c r="AY127" s="22"/>
+      <c r="AZ127" s="22"/>
+      <c r="BA127" s="22"/>
+      <c r="BB127" s="22"/>
+      <c r="BC127" s="22"/>
+      <c r="BD127" s="22"/>
+      <c r="BE127" s="22"/>
+      <c r="BF127" s="22"/>
+      <c r="BG127" s="22"/>
+      <c r="BH127" s="22"/>
+      <c r="BI127" s="22"/>
+      <c r="BJ127" s="22"/>
+      <c r="BK127" s="22"/>
+      <c r="BL127" s="22"/>
+      <c r="BM127" s="22"/>
+      <c r="BN127" s="22"/>
+    </row>
+    <row r="128" spans="1:66" s="7" customFormat="1" ht="18.75" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A128" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="B128" s="106"/>
+      <c r="C128" s="106"/>
+      <c r="D128" s="106"/>
+      <c r="E128" s="106"/>
+      <c r="F128" s="106"/>
+      <c r="G128" s="106"/>
+      <c r="H128" s="106"/>
+      <c r="I128" s="106"/>
+      <c r="J128" s="106"/>
+      <c r="K128" s="106"/>
+      <c r="L128" s="106"/>
+      <c r="M128" s="106"/>
+      <c r="N128" s="106"/>
+      <c r="O128" s="106"/>
       <c r="P128" s="22"/>
       <c r="Q128" s="22"/>
       <c r="R128" s="22"/>
@@ -32487,24 +32506,24 @@
       <c r="BM128" s="22"/>
       <c r="BN128" s="22"/>
     </row>
-    <row r="129" spans="1:66" s="7" customFormat="1" ht="18.75" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A129" s="105" t="s">
-        <v>132</v>
-      </c>
-      <c r="B129" s="105"/>
-      <c r="C129" s="105"/>
-      <c r="D129" s="105"/>
-      <c r="E129" s="105"/>
-      <c r="F129" s="105"/>
-      <c r="G129" s="105"/>
-      <c r="H129" s="105"/>
-      <c r="I129" s="105"/>
-      <c r="J129" s="105"/>
-      <c r="K129" s="105"/>
-      <c r="L129" s="105"/>
-      <c r="M129" s="105"/>
-      <c r="N129" s="105"/>
-      <c r="O129" s="105"/>
+    <row r="129" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A129" s="107" t="s">
+        <v>146</v>
+      </c>
+      <c r="B129" s="107"/>
+      <c r="C129" s="107"/>
+      <c r="D129" s="107"/>
+      <c r="E129" s="107"/>
+      <c r="F129" s="107"/>
+      <c r="G129" s="107"/>
+      <c r="H129" s="107"/>
+      <c r="I129" s="107"/>
+      <c r="J129" s="107"/>
+      <c r="K129" s="107"/>
+      <c r="L129" s="107"/>
+      <c r="M129" s="107"/>
+      <c r="N129" s="107"/>
+      <c r="O129" s="107"/>
       <c r="P129" s="22"/>
       <c r="Q129" s="22"/>
       <c r="R129" s="22"/>
@@ -32557,277 +32576,305 @@
       <c r="BM129" s="22"/>
       <c r="BN129" s="22"/>
     </row>
-    <row r="130" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A130" s="106" t="s">
+    <row r="130" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="92">
         <v>146</v>
       </c>
-      <c r="B130" s="106"/>
-      <c r="C130" s="106"/>
-      <c r="D130" s="106"/>
-      <c r="E130" s="106"/>
-      <c r="F130" s="106"/>
-      <c r="G130" s="106"/>
-      <c r="H130" s="106"/>
-      <c r="I130" s="106"/>
-      <c r="J130" s="106"/>
-      <c r="K130" s="106"/>
-      <c r="L130" s="106"/>
-      <c r="M130" s="106"/>
-      <c r="N130" s="106"/>
-      <c r="O130" s="106"/>
-      <c r="P130" s="22"/>
-      <c r="Q130" s="22"/>
-      <c r="R130" s="22"/>
-      <c r="S130" s="22"/>
-      <c r="T130" s="22"/>
-      <c r="U130" s="22"/>
-      <c r="V130" s="22"/>
-      <c r="W130" s="22"/>
-      <c r="X130" s="22"/>
-      <c r="Y130" s="22"/>
-      <c r="Z130" s="22"/>
-      <c r="AA130" s="22"/>
-      <c r="AB130" s="22"/>
-      <c r="AC130" s="22"/>
-      <c r="AD130" s="22"/>
-      <c r="AE130" s="22"/>
-      <c r="AF130" s="22"/>
-      <c r="AG130" s="22"/>
-      <c r="AH130" s="22"/>
-      <c r="AI130" s="22"/>
-      <c r="AJ130" s="22"/>
-      <c r="AK130" s="22"/>
-      <c r="AL130" s="22"/>
-      <c r="AM130" s="22"/>
-      <c r="AN130" s="22"/>
-      <c r="AO130" s="22"/>
-      <c r="AP130" s="22"/>
-      <c r="AQ130" s="22"/>
-      <c r="AR130" s="22"/>
-      <c r="AS130" s="22"/>
-      <c r="AT130" s="22"/>
-      <c r="AU130" s="22"/>
-      <c r="AV130" s="22"/>
-      <c r="AW130" s="22"/>
-      <c r="AX130" s="22"/>
-      <c r="AY130" s="22"/>
-      <c r="AZ130" s="22"/>
-      <c r="BA130" s="22"/>
-      <c r="BB130" s="22"/>
-      <c r="BC130" s="22"/>
-      <c r="BD130" s="22"/>
-      <c r="BE130" s="22"/>
-      <c r="BF130" s="22"/>
-      <c r="BG130" s="22"/>
-      <c r="BH130" s="22"/>
-      <c r="BI130" s="22"/>
-      <c r="BJ130" s="22"/>
-      <c r="BK130" s="22"/>
-      <c r="BL130" s="22"/>
-      <c r="BM130" s="22"/>
-      <c r="BN130" s="22"/>
-    </row>
-    <row r="131" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="92">
-        <v>146</v>
+      <c r="B130" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C130" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D130" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="F130" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="G130" s="92">
+        <v>403</v>
+      </c>
+      <c r="H130" s="92" t="s">
+        <v>216</v>
+      </c>
+      <c r="I130" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J130" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="K130" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L130" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M130" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N130" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O130" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="P130" s="21"/>
+      <c r="Q130" s="21"/>
+      <c r="R130" s="21"/>
+      <c r="S130" s="21"/>
+      <c r="T130" s="21"/>
+      <c r="U130" s="21"/>
+      <c r="V130" s="21"/>
+      <c r="W130" s="21"/>
+      <c r="X130" s="21"/>
+      <c r="Y130" s="21"/>
+      <c r="Z130" s="21"/>
+      <c r="AA130" s="21"/>
+      <c r="AB130" s="21"/>
+      <c r="AC130" s="21"/>
+      <c r="AD130" s="21"/>
+      <c r="AE130" s="21"/>
+      <c r="AF130" s="21"/>
+      <c r="AG130" s="21"/>
+      <c r="AH130" s="21"/>
+      <c r="AI130" s="21"/>
+      <c r="AJ130" s="21"/>
+      <c r="AK130" s="21"/>
+      <c r="AL130" s="21"/>
+      <c r="AM130" s="21"/>
+      <c r="AN130" s="21"/>
+      <c r="AO130" s="21"/>
+      <c r="AP130" s="21"/>
+      <c r="AQ130" s="21"/>
+      <c r="AR130" s="21"/>
+      <c r="AS130" s="21"/>
+      <c r="AT130" s="21"/>
+      <c r="AU130" s="21"/>
+      <c r="AV130" s="21"/>
+      <c r="AW130" s="21"/>
+      <c r="AX130" s="21"/>
+      <c r="AY130" s="21"/>
+      <c r="AZ130" s="21"/>
+      <c r="BA130" s="21"/>
+      <c r="BB130" s="21"/>
+      <c r="BC130" s="21"/>
+      <c r="BD130" s="21"/>
+      <c r="BE130" s="21"/>
+      <c r="BF130" s="21"/>
+      <c r="BG130" s="21"/>
+      <c r="BH130" s="21"/>
+      <c r="BI130" s="21"/>
+      <c r="BJ130" s="21"/>
+      <c r="BK130" s="21"/>
+      <c r="BL130" s="21"/>
+      <c r="BM130" s="21"/>
+      <c r="BN130" s="21"/>
+    </row>
+    <row r="131" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A131" s="4">
+        <v>86</v>
       </c>
       <c r="B131" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C131" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D131" s="92" t="s">
+      <c r="C131" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E131" s="92" t="s">
+      <c r="E131" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F131" s="92" t="s">
+      <c r="F131" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G131" s="92">
-        <v>403</v>
-      </c>
-      <c r="H131" s="92" t="s">
+      <c r="G131" s="24">
+        <v>401</v>
+      </c>
+      <c r="H131" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I131" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J131" s="92" t="s">
+      <c r="J131" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K131" s="92" t="s">
+      <c r="K131" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L131" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M131" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N131" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O131" s="93" t="s">
+      <c r="L131" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M131" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N131" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="P131" s="21"/>
-      <c r="Q131" s="21"/>
-      <c r="R131" s="21"/>
-      <c r="S131" s="21"/>
-      <c r="T131" s="21"/>
-      <c r="U131" s="21"/>
-      <c r="V131" s="21"/>
-      <c r="W131" s="21"/>
-      <c r="X131" s="21"/>
-      <c r="Y131" s="21"/>
-      <c r="Z131" s="21"/>
-      <c r="AA131" s="21"/>
-      <c r="AB131" s="21"/>
-      <c r="AC131" s="21"/>
-      <c r="AD131" s="21"/>
-      <c r="AE131" s="21"/>
-      <c r="AF131" s="21"/>
-      <c r="AG131" s="21"/>
-      <c r="AH131" s="21"/>
-      <c r="AI131" s="21"/>
-      <c r="AJ131" s="21"/>
-      <c r="AK131" s="21"/>
-      <c r="AL131" s="21"/>
-      <c r="AM131" s="21"/>
-      <c r="AN131" s="21"/>
-      <c r="AO131" s="21"/>
-      <c r="AP131" s="21"/>
-      <c r="AQ131" s="21"/>
-      <c r="AR131" s="21"/>
-      <c r="AS131" s="21"/>
-      <c r="AT131" s="21"/>
-      <c r="AU131" s="21"/>
-      <c r="AV131" s="21"/>
-      <c r="AW131" s="21"/>
-      <c r="AX131" s="21"/>
-      <c r="AY131" s="21"/>
-      <c r="AZ131" s="21"/>
-      <c r="BA131" s="21"/>
-      <c r="BB131" s="21"/>
-      <c r="BC131" s="21"/>
-      <c r="BD131" s="21"/>
-      <c r="BE131" s="21"/>
-      <c r="BF131" s="21"/>
-      <c r="BG131" s="21"/>
-      <c r="BH131" s="21"/>
-      <c r="BI131" s="21"/>
-      <c r="BJ131" s="21"/>
-      <c r="BK131" s="21"/>
-      <c r="BL131" s="21"/>
-      <c r="BM131" s="21"/>
-      <c r="BN131" s="21"/>
-    </row>
-    <row r="132" spans="1:66" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A132" s="4">
-        <v>86</v>
-      </c>
-      <c r="B132" s="30" t="s">
+      <c r="O131" s="49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:66" s="22" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A132" s="92">
+        <v>87</v>
+      </c>
+      <c r="B132" s="104" t="s">
         <v>133</v>
       </c>
-      <c r="C132" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="D132" s="4" t="s">
+      <c r="C132" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="D132" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E132" s="4" t="s">
+      <c r="E132" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="F132" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G132" s="24">
+      <c r="G132" s="74">
         <v>401</v>
       </c>
       <c r="H132" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I132" s="24" t="s">
+      <c r="I132" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J132" s="4" t="s">
+      <c r="J132" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K132" s="4" t="s">
+      <c r="K132" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L132" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M132" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N132" s="32" t="s">
+      <c r="L132" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M132" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="N132" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="O132" s="49" t="s">
+      <c r="O132" s="93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:66" s="22" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A133" s="92">
-        <v>87</v>
-      </c>
-      <c r="B133" s="103" t="s">
+    <row r="133" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A133" s="4">
+        <v>89</v>
+      </c>
+      <c r="B133" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C133" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="D133" s="92" t="s">
+      <c r="C133" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E133" s="92" t="s">
+      <c r="E133" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F133" s="92" t="s">
+      <c r="F133" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G133" s="74">
-        <v>401</v>
+      <c r="G133" s="24">
+        <v>400</v>
       </c>
       <c r="H133" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="I133" s="74" t="s">
+      <c r="I133" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J133" s="92" t="s">
+      <c r="J133" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K133" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L133" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M133" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="N133" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="O133" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="K133" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L133" s="10">
+        <v>1003</v>
+      </c>
+      <c r="M133" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="N133" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="O133" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P133" s="22"/>
+      <c r="Q133" s="22"/>
+      <c r="R133" s="22"/>
+      <c r="S133" s="22"/>
+      <c r="T133" s="22"/>
+      <c r="U133" s="22"/>
+      <c r="V133" s="22"/>
+      <c r="W133" s="22"/>
+      <c r="X133" s="22"/>
+      <c r="Y133" s="22"/>
+      <c r="Z133" s="22"/>
+      <c r="AA133" s="22"/>
+      <c r="AB133" s="22"/>
+      <c r="AC133" s="22"/>
+      <c r="AD133" s="22"/>
+      <c r="AE133" s="22"/>
+      <c r="AF133" s="22"/>
+      <c r="AG133" s="22"/>
+      <c r="AH133" s="22"/>
+      <c r="AI133" s="22"/>
+      <c r="AJ133" s="22"/>
+      <c r="AK133" s="22"/>
+      <c r="AL133" s="22"/>
+      <c r="AM133" s="22"/>
+      <c r="AN133" s="22"/>
+      <c r="AO133" s="22"/>
+      <c r="AP133" s="22"/>
+      <c r="AQ133" s="22"/>
+      <c r="AR133" s="22"/>
+      <c r="AS133" s="22"/>
+      <c r="AT133" s="22"/>
+      <c r="AU133" s="22"/>
+      <c r="AV133" s="22"/>
+      <c r="AW133" s="22"/>
+      <c r="AX133" s="22"/>
+      <c r="AY133" s="22"/>
+      <c r="AZ133" s="22"/>
+      <c r="BA133" s="22"/>
+      <c r="BB133" s="22"/>
+      <c r="BC133" s="22"/>
+      <c r="BD133" s="22"/>
+      <c r="BE133" s="22"/>
+      <c r="BF133" s="22"/>
+      <c r="BG133" s="22"/>
+      <c r="BH133" s="22"/>
+      <c r="BI133" s="22"/>
+      <c r="BJ133" s="22"/>
+      <c r="BK133" s="22"/>
+      <c r="BL133" s="22"/>
+      <c r="BM133" s="22"/>
+      <c r="BN133" s="22"/>
+    </row>
+    <row r="134" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B134" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="23" t="s">
-        <v>264</v>
+      <c r="C134" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>12</v>
@@ -32851,13 +32898,13 @@
         <v>7</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L134" s="10">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M134" s="30" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N134" s="30" t="s">
         <v>134</v>
@@ -32917,15 +32964,15 @@
       <c r="BM134" s="22"/>
       <c r="BN134" s="22"/>
     </row>
-    <row r="135" spans="1:66" s="7" customFormat="1" ht="47.25" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B135" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>12</v>
@@ -32949,13 +32996,13 @@
         <v>7</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L135" s="10">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M135" s="30" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="N135" s="30" t="s">
         <v>134</v>
@@ -33015,26 +33062,26 @@
       <c r="BM135" s="22"/>
       <c r="BN135" s="22"/>
     </row>
-    <row r="136" spans="1:66" s="7" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:66" s="7" customFormat="1" ht="33.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="B136" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D136" s="4" t="s">
+      <c r="C136" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D136" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E136" s="4" t="s">
+      <c r="E136" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F136" s="4" t="s">
+      <c r="F136" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G136" s="24">
+      <c r="G136" s="54">
         <v>400</v>
       </c>
       <c r="H136" s="58" t="s">
@@ -33043,23 +33090,23 @@
       <c r="I136" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J136" s="4" t="s">
+      <c r="J136" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K136" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L136" s="10">
-        <v>1005</v>
-      </c>
-      <c r="M136" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="N136" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="O136" s="30" t="s">
-        <v>43</v>
+      <c r="K136" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L136" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M136" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N136" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O136" s="63" t="s">
+        <v>12</v>
       </c>
       <c r="P136" s="22"/>
       <c r="Q136" s="22"/>
@@ -33113,27 +33160,27 @@
       <c r="BM136" s="22"/>
       <c r="BN136" s="22"/>
     </row>
-    <row r="137" spans="1:66" s="7" customFormat="1" ht="33.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="B137" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C137" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D137" s="53" t="s">
+      <c r="C137" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E137" s="53" t="s">
+      <c r="E137" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F137" s="53" t="s">
+      <c r="F137" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G137" s="54">
-        <v>400</v>
+      <c r="G137" s="24">
+        <v>404</v>
       </c>
       <c r="H137" s="58" t="s">
         <v>216</v>
@@ -33141,85 +33188,85 @@
       <c r="I137" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J137" s="53" t="s">
+      <c r="J137" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K137" s="54" t="s">
+      <c r="K137" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L137" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M137" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N137" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="O137" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="P137" s="22"/>
-      <c r="Q137" s="22"/>
-      <c r="R137" s="22"/>
-      <c r="S137" s="22"/>
-      <c r="T137" s="22"/>
-      <c r="U137" s="22"/>
-      <c r="V137" s="22"/>
-      <c r="W137" s="22"/>
-      <c r="X137" s="22"/>
-      <c r="Y137" s="22"/>
-      <c r="Z137" s="22"/>
-      <c r="AA137" s="22"/>
-      <c r="AB137" s="22"/>
-      <c r="AC137" s="22"/>
-      <c r="AD137" s="22"/>
-      <c r="AE137" s="22"/>
-      <c r="AF137" s="22"/>
-      <c r="AG137" s="22"/>
-      <c r="AH137" s="22"/>
-      <c r="AI137" s="22"/>
-      <c r="AJ137" s="22"/>
-      <c r="AK137" s="22"/>
-      <c r="AL137" s="22"/>
-      <c r="AM137" s="22"/>
-      <c r="AN137" s="22"/>
-      <c r="AO137" s="22"/>
-      <c r="AP137" s="22"/>
-      <c r="AQ137" s="22"/>
-      <c r="AR137" s="22"/>
-      <c r="AS137" s="22"/>
-      <c r="AT137" s="22"/>
-      <c r="AU137" s="22"/>
-      <c r="AV137" s="22"/>
-      <c r="AW137" s="22"/>
-      <c r="AX137" s="22"/>
-      <c r="AY137" s="22"/>
-      <c r="AZ137" s="22"/>
-      <c r="BA137" s="22"/>
-      <c r="BB137" s="22"/>
-      <c r="BC137" s="22"/>
-      <c r="BD137" s="22"/>
-      <c r="BE137" s="22"/>
-      <c r="BF137" s="22"/>
-      <c r="BG137" s="22"/>
-      <c r="BH137" s="22"/>
-      <c r="BI137" s="22"/>
-      <c r="BJ137" s="22"/>
-      <c r="BK137" s="22"/>
-      <c r="BL137" s="22"/>
-      <c r="BM137" s="22"/>
-      <c r="BN137" s="22"/>
-    </row>
-    <row r="138" spans="1:66" s="11" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="L137" s="10">
+        <v>1006</v>
+      </c>
+      <c r="M137" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="N137" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="O137" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="P137" s="21"/>
+      <c r="Q137" s="21"/>
+      <c r="R137" s="21"/>
+      <c r="S137" s="21"/>
+      <c r="T137" s="21"/>
+      <c r="U137" s="21"/>
+      <c r="V137" s="21"/>
+      <c r="W137" s="21"/>
+      <c r="X137" s="21"/>
+      <c r="Y137" s="21"/>
+      <c r="Z137" s="21"/>
+      <c r="AA137" s="21"/>
+      <c r="AB137" s="21"/>
+      <c r="AC137" s="21"/>
+      <c r="AD137" s="21"/>
+      <c r="AE137" s="21"/>
+      <c r="AF137" s="21"/>
+      <c r="AG137" s="21"/>
+      <c r="AH137" s="21"/>
+      <c r="AI137" s="21"/>
+      <c r="AJ137" s="21"/>
+      <c r="AK137" s="21"/>
+      <c r="AL137" s="21"/>
+      <c r="AM137" s="21"/>
+      <c r="AN137" s="21"/>
+      <c r="AO137" s="21"/>
+      <c r="AP137" s="21"/>
+      <c r="AQ137" s="21"/>
+      <c r="AR137" s="21"/>
+      <c r="AS137" s="21"/>
+      <c r="AT137" s="21"/>
+      <c r="AU137" s="21"/>
+      <c r="AV137" s="21"/>
+      <c r="AW137" s="21"/>
+      <c r="AX137" s="21"/>
+      <c r="AY137" s="21"/>
+      <c r="AZ137" s="21"/>
+      <c r="BA137" s="21"/>
+      <c r="BB137" s="21"/>
+      <c r="BC137" s="21"/>
+      <c r="BD137" s="21"/>
+      <c r="BE137" s="21"/>
+      <c r="BF137" s="21"/>
+      <c r="BG137" s="21"/>
+      <c r="BH137" s="21"/>
+      <c r="BI137" s="21"/>
+      <c r="BJ137" s="21"/>
+      <c r="BK137" s="21"/>
+      <c r="BL137" s="21"/>
+      <c r="BM137" s="21"/>
+      <c r="BN137" s="21"/>
+    </row>
+    <row r="138" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B138" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>12</v>
@@ -33243,13 +33290,13 @@
         <v>7</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L138" s="10">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M138" s="30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N138" s="30" t="s">
         <v>134</v>
@@ -33257,67 +33304,16 @@
       <c r="O138" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="P138" s="21"/>
-      <c r="Q138" s="21"/>
-      <c r="R138" s="21"/>
-      <c r="S138" s="21"/>
-      <c r="T138" s="21"/>
-      <c r="U138" s="21"/>
-      <c r="V138" s="21"/>
-      <c r="W138" s="21"/>
-      <c r="X138" s="21"/>
-      <c r="Y138" s="21"/>
-      <c r="Z138" s="21"/>
-      <c r="AA138" s="21"/>
-      <c r="AB138" s="21"/>
-      <c r="AC138" s="21"/>
-      <c r="AD138" s="21"/>
-      <c r="AE138" s="21"/>
-      <c r="AF138" s="21"/>
-      <c r="AG138" s="21"/>
-      <c r="AH138" s="21"/>
-      <c r="AI138" s="21"/>
-      <c r="AJ138" s="21"/>
-      <c r="AK138" s="21"/>
-      <c r="AL138" s="21"/>
-      <c r="AM138" s="21"/>
-      <c r="AN138" s="21"/>
-      <c r="AO138" s="21"/>
-      <c r="AP138" s="21"/>
-      <c r="AQ138" s="21"/>
-      <c r="AR138" s="21"/>
-      <c r="AS138" s="21"/>
-      <c r="AT138" s="21"/>
-      <c r="AU138" s="21"/>
-      <c r="AV138" s="21"/>
-      <c r="AW138" s="21"/>
-      <c r="AX138" s="21"/>
-      <c r="AY138" s="21"/>
-      <c r="AZ138" s="21"/>
-      <c r="BA138" s="21"/>
-      <c r="BB138" s="21"/>
-      <c r="BC138" s="21"/>
-      <c r="BD138" s="21"/>
-      <c r="BE138" s="21"/>
-      <c r="BF138" s="21"/>
-      <c r="BG138" s="21"/>
-      <c r="BH138" s="21"/>
-      <c r="BI138" s="21"/>
-      <c r="BJ138" s="21"/>
-      <c r="BK138" s="21"/>
-      <c r="BL138" s="21"/>
-      <c r="BM138" s="21"/>
-      <c r="BN138" s="21"/>
-    </row>
-    <row r="139" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B139" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>12</v>
@@ -33329,7 +33325,7 @@
         <v>140</v>
       </c>
       <c r="G139" s="24">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H139" s="58" t="s">
         <v>216</v>
@@ -33344,10 +33340,10 @@
         <v>30</v>
       </c>
       <c r="L139" s="10">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M139" s="30" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N139" s="30" t="s">
         <v>134</v>
@@ -33356,15 +33352,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A140" s="4">
-        <v>94</v>
+    <row r="140" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A140" s="26">
+        <v>141</v>
       </c>
       <c r="B140" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>89</v>
+      <c r="C140" s="84" t="s">
+        <v>229</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>12</v>
@@ -33372,11 +33368,11 @@
       <c r="E140" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F140" s="4" t="s">
+      <c r="F140" s="26" t="s">
         <v>140</v>
       </c>
       <c r="G140" s="24">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H140" s="58" t="s">
         <v>216</v>
@@ -33390,64 +33386,113 @@
       <c r="K140" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L140" s="10">
-        <v>1008</v>
-      </c>
-      <c r="M140" s="30" t="s">
-        <v>16</v>
+      <c r="L140" s="26">
+        <v>3013</v>
+      </c>
+      <c r="M140" s="84" t="s">
+        <v>230</v>
       </c>
       <c r="N140" s="30" t="s">
         <v>134</v>
       </c>
       <c r="O140" s="30" t="s">
-        <v>59</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="P140" s="21"/>
+      <c r="Q140" s="21"/>
+      <c r="R140" s="21"/>
+      <c r="S140" s="21"/>
+      <c r="T140" s="21"/>
+      <c r="U140" s="21"/>
+      <c r="V140" s="21"/>
+      <c r="W140" s="21"/>
+      <c r="X140" s="21"/>
+      <c r="Y140" s="21"/>
+      <c r="Z140" s="21"/>
+      <c r="AA140" s="21"/>
+      <c r="AB140" s="21"/>
+      <c r="AC140" s="21"/>
+      <c r="AD140" s="21"/>
+      <c r="AE140" s="21"/>
+      <c r="AF140" s="21"/>
+      <c r="AG140" s="21"/>
+      <c r="AH140" s="21"/>
+      <c r="AI140" s="21"/>
+      <c r="AJ140" s="21"/>
+      <c r="AK140" s="21"/>
+      <c r="AL140" s="21"/>
+      <c r="AM140" s="21"/>
+      <c r="AN140" s="21"/>
+      <c r="AO140" s="21"/>
+      <c r="AP140" s="21"/>
+      <c r="AQ140" s="21"/>
+      <c r="AR140" s="21"/>
+      <c r="AS140" s="21"/>
+      <c r="AT140" s="21"/>
+      <c r="AU140" s="21"/>
+      <c r="AV140" s="21"/>
+      <c r="AW140" s="21"/>
+      <c r="AX140" s="21"/>
+      <c r="AY140" s="21"/>
+      <c r="AZ140" s="21"/>
+      <c r="BA140" s="21"/>
+      <c r="BB140" s="21"/>
+      <c r="BC140" s="21"/>
+      <c r="BD140" s="21"/>
+      <c r="BE140" s="21"/>
+      <c r="BF140" s="21"/>
+      <c r="BG140" s="21"/>
+      <c r="BH140" s="21"/>
+      <c r="BI140" s="21"/>
+      <c r="BJ140" s="21"/>
+      <c r="BK140" s="21"/>
+      <c r="BL140" s="21"/>
+      <c r="BM140" s="21"/>
+      <c r="BN140" s="21"/>
     </row>
     <row r="141" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A141" s="26">
-        <v>141</v>
-      </c>
+      <c r="A141" s="26"/>
       <c r="B141" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C141" s="84" t="s">
-        <v>229</v>
-      </c>
-      <c r="D141" s="4" t="s">
+      <c r="C141" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D141" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E141" s="4" t="s">
+      <c r="E141" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F141" s="26" t="s">
+      <c r="F141" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G141" s="24">
-        <v>400</v>
-      </c>
-      <c r="H141" s="58" t="s">
+      <c r="G141" s="44">
+        <v>403</v>
+      </c>
+      <c r="H141" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I141" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J141" s="4" t="s">
+      <c r="J141" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K141" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L141" s="26">
-        <v>3013</v>
-      </c>
-      <c r="M141" s="84" t="s">
-        <v>230</v>
-      </c>
-      <c r="N141" s="30" t="s">
-        <v>134</v>
+      <c r="K141" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L141" s="24">
+        <v>1011</v>
+      </c>
+      <c r="M141" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="N141" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="O141" s="30" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="P141" s="21"/>
       <c r="Q141" s="21"/>
@@ -33501,113 +33546,64 @@
       <c r="BM141" s="21"/>
       <c r="BN141" s="21"/>
     </row>
-    <row r="142" spans="1:66" s="50" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A142" s="26"/>
+    <row r="142" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A142" s="4">
+        <v>95</v>
+      </c>
       <c r="B142" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C142" s="23" t="s">
-        <v>295</v>
+      <c r="C142" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="D142" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E142" s="24" t="s">
+      <c r="E142" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F142" s="24" t="s">
+      <c r="F142" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G142" s="44">
+      <c r="G142" s="24">
         <v>403</v>
       </c>
-      <c r="H142" s="24" t="s">
+      <c r="H142" s="58" t="s">
         <v>216</v>
       </c>
       <c r="I142" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J142" s="24" t="s">
+      <c r="J142" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K142" s="24" t="s">
+      <c r="K142" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L142" s="24">
+      <c r="L142" s="4">
         <v>1011</v>
       </c>
       <c r="M142" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="N142" s="32" t="s">
-        <v>55</v>
+      <c r="N142" s="30" t="s">
+        <v>134</v>
       </c>
       <c r="O142" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="P142" s="21"/>
-      <c r="Q142" s="21"/>
-      <c r="R142" s="21"/>
-      <c r="S142" s="21"/>
-      <c r="T142" s="21"/>
-      <c r="U142" s="21"/>
-      <c r="V142" s="21"/>
-      <c r="W142" s="21"/>
-      <c r="X142" s="21"/>
-      <c r="Y142" s="21"/>
-      <c r="Z142" s="21"/>
-      <c r="AA142" s="21"/>
-      <c r="AB142" s="21"/>
-      <c r="AC142" s="21"/>
-      <c r="AD142" s="21"/>
-      <c r="AE142" s="21"/>
-      <c r="AF142" s="21"/>
-      <c r="AG142" s="21"/>
-      <c r="AH142" s="21"/>
-      <c r="AI142" s="21"/>
-      <c r="AJ142" s="21"/>
-      <c r="AK142" s="21"/>
-      <c r="AL142" s="21"/>
-      <c r="AM142" s="21"/>
-      <c r="AN142" s="21"/>
-      <c r="AO142" s="21"/>
-      <c r="AP142" s="21"/>
-      <c r="AQ142" s="21"/>
-      <c r="AR142" s="21"/>
-      <c r="AS142" s="21"/>
-      <c r="AT142" s="21"/>
-      <c r="AU142" s="21"/>
-      <c r="AV142" s="21"/>
-      <c r="AW142" s="21"/>
-      <c r="AX142" s="21"/>
-      <c r="AY142" s="21"/>
-      <c r="AZ142" s="21"/>
-      <c r="BA142" s="21"/>
-      <c r="BB142" s="21"/>
-      <c r="BC142" s="21"/>
-      <c r="BD142" s="21"/>
-      <c r="BE142" s="21"/>
-      <c r="BF142" s="21"/>
-      <c r="BG142" s="21"/>
-      <c r="BH142" s="21"/>
-      <c r="BI142" s="21"/>
-      <c r="BJ142" s="21"/>
-      <c r="BK142" s="21"/>
-      <c r="BL142" s="21"/>
-      <c r="BM142" s="21"/>
-      <c r="BN142" s="21"/>
-    </row>
-    <row r="143" spans="1:66" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B143" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D143" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="4" t="s">
@@ -33617,7 +33613,7 @@
         <v>140</v>
       </c>
       <c r="G143" s="24">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H143" s="58" t="s">
         <v>216</v>
@@ -33631,234 +33627,234 @@
       <c r="K143" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L143" s="4">
-        <v>1011</v>
-      </c>
-      <c r="M143" s="32" t="s">
-        <v>202</v>
+      <c r="L143" s="10">
+        <v>4001</v>
+      </c>
+      <c r="M143" s="30" t="s">
+        <v>19</v>
       </c>
       <c r="N143" s="30" t="s">
         <v>134</v>
       </c>
       <c r="O143" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:66" s="7" customFormat="1" ht="31.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A144" s="4">
-        <v>96</v>
+        <v>63</v>
+      </c>
+      <c r="P143" s="22"/>
+      <c r="Q143" s="22"/>
+      <c r="R143" s="22"/>
+      <c r="S143" s="22"/>
+      <c r="T143" s="22"/>
+      <c r="U143" s="22"/>
+      <c r="V143" s="22"/>
+      <c r="W143" s="22"/>
+      <c r="X143" s="22"/>
+      <c r="Y143" s="22"/>
+      <c r="Z143" s="22"/>
+      <c r="AA143" s="22"/>
+      <c r="AB143" s="22"/>
+      <c r="AC143" s="22"/>
+      <c r="AD143" s="22"/>
+      <c r="AE143" s="22"/>
+      <c r="AF143" s="22"/>
+      <c r="AG143" s="22"/>
+      <c r="AH143" s="22"/>
+      <c r="AI143" s="22"/>
+      <c r="AJ143" s="22"/>
+      <c r="AK143" s="22"/>
+      <c r="AL143" s="22"/>
+      <c r="AM143" s="22"/>
+      <c r="AN143" s="22"/>
+      <c r="AO143" s="22"/>
+      <c r="AP143" s="22"/>
+      <c r="AQ143" s="22"/>
+      <c r="AR143" s="22"/>
+      <c r="AS143" s="22"/>
+      <c r="AT143" s="22"/>
+      <c r="AU143" s="22"/>
+      <c r="AV143" s="22"/>
+      <c r="AW143" s="22"/>
+      <c r="AX143" s="22"/>
+      <c r="AY143" s="22"/>
+      <c r="AZ143" s="22"/>
+      <c r="BA143" s="22"/>
+      <c r="BB143" s="22"/>
+      <c r="BC143" s="22"/>
+      <c r="BD143" s="22"/>
+      <c r="BE143" s="22"/>
+      <c r="BF143" s="22"/>
+      <c r="BG143" s="22"/>
+      <c r="BH143" s="22"/>
+      <c r="BI143" s="22"/>
+      <c r="BJ143" s="22"/>
+      <c r="BK143" s="22"/>
+      <c r="BL143" s="22"/>
+      <c r="BM143" s="22"/>
+      <c r="BN143" s="22"/>
+    </row>
+    <row r="144" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A144" s="26">
+        <v>142</v>
       </c>
       <c r="B144" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D144" s="4" t="s">
+      <c r="C144" s="84" t="s">
+        <v>236</v>
+      </c>
+      <c r="D144" s="26"/>
+      <c r="E144" s="26"/>
+      <c r="F144" s="26"/>
+      <c r="G144" s="65">
+        <v>413</v>
+      </c>
+      <c r="H144" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="I144" s="65"/>
+      <c r="J144" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="K144" s="26"/>
+      <c r="L144" s="26"/>
+      <c r="M144" s="84" t="s">
+        <v>236</v>
+      </c>
+      <c r="N144" s="33"/>
+      <c r="O144" s="33"/>
+    </row>
+    <row r="145" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="8">
+        <v>169</v>
+      </c>
+      <c r="B145" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C145" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D145" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E144" s="4" t="s">
+      <c r="E145" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F144" s="4" t="s">
+      <c r="F145" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G144" s="24">
-        <v>400</v>
-      </c>
-      <c r="H144" s="58" t="s">
+      <c r="G145" s="8">
+        <v>401</v>
+      </c>
+      <c r="H145" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="I144" s="24" t="s">
+      <c r="I145" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J144" s="4" t="s">
+      <c r="J145" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K144" s="4" t="s">
+      <c r="K145" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L144" s="10">
-        <v>4001</v>
-      </c>
-      <c r="M144" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="N144" s="30" t="s">
+      <c r="L145" s="8">
+        <v>1014</v>
+      </c>
+      <c r="M145" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="N145" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O145" s="64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A146" s="107" t="s">
+        <v>145</v>
+      </c>
+      <c r="B146" s="107"/>
+      <c r="C146" s="107"/>
+      <c r="D146" s="107"/>
+      <c r="E146" s="107"/>
+      <c r="F146" s="107"/>
+      <c r="G146" s="107"/>
+      <c r="H146" s="107"/>
+      <c r="I146" s="107"/>
+      <c r="J146" s="107"/>
+      <c r="K146" s="107"/>
+      <c r="L146" s="107"/>
+      <c r="M146" s="107"/>
+      <c r="N146" s="107"/>
+      <c r="O146" s="107"/>
+    </row>
+    <row r="147" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="4">
+        <v>154</v>
+      </c>
+      <c r="B147" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C147" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G147" s="4">
+        <v>200</v>
+      </c>
+      <c r="H147" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="I147" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="J147" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L147" s="4">
+        <v>4006</v>
+      </c>
+      <c r="M147" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="N147" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O144" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="P144" s="22"/>
-      <c r="Q144" s="22"/>
-      <c r="R144" s="22"/>
-      <c r="S144" s="22"/>
-      <c r="T144" s="22"/>
-      <c r="U144" s="22"/>
-      <c r="V144" s="22"/>
-      <c r="W144" s="22"/>
-      <c r="X144" s="22"/>
-      <c r="Y144" s="22"/>
-      <c r="Z144" s="22"/>
-      <c r="AA144" s="22"/>
-      <c r="AB144" s="22"/>
-      <c r="AC144" s="22"/>
-      <c r="AD144" s="22"/>
-      <c r="AE144" s="22"/>
-      <c r="AF144" s="22"/>
-      <c r="AG144" s="22"/>
-      <c r="AH144" s="22"/>
-      <c r="AI144" s="22"/>
-      <c r="AJ144" s="22"/>
-      <c r="AK144" s="22"/>
-      <c r="AL144" s="22"/>
-      <c r="AM144" s="22"/>
-      <c r="AN144" s="22"/>
-      <c r="AO144" s="22"/>
-      <c r="AP144" s="22"/>
-      <c r="AQ144" s="22"/>
-      <c r="AR144" s="22"/>
-      <c r="AS144" s="22"/>
-      <c r="AT144" s="22"/>
-      <c r="AU144" s="22"/>
-      <c r="AV144" s="22"/>
-      <c r="AW144" s="22"/>
-      <c r="AX144" s="22"/>
-      <c r="AY144" s="22"/>
-      <c r="AZ144" s="22"/>
-      <c r="BA144" s="22"/>
-      <c r="BB144" s="22"/>
-      <c r="BC144" s="22"/>
-      <c r="BD144" s="22"/>
-      <c r="BE144" s="22"/>
-      <c r="BF144" s="22"/>
-      <c r="BG144" s="22"/>
-      <c r="BH144" s="22"/>
-      <c r="BI144" s="22"/>
-      <c r="BJ144" s="22"/>
-      <c r="BK144" s="22"/>
-      <c r="BL144" s="22"/>
-      <c r="BM144" s="22"/>
-      <c r="BN144" s="22"/>
-    </row>
-    <row r="145" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A145" s="26">
-        <v>142</v>
-      </c>
-      <c r="B145" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C145" s="84" t="s">
-        <v>236</v>
-      </c>
-      <c r="D145" s="26"/>
-      <c r="E145" s="26"/>
-      <c r="F145" s="26"/>
-      <c r="G145" s="65">
-        <v>413</v>
-      </c>
-      <c r="H145" s="65" t="s">
-        <v>216</v>
-      </c>
-      <c r="I145" s="65"/>
-      <c r="J145" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="K145" s="26"/>
-      <c r="L145" s="26"/>
-      <c r="M145" s="84" t="s">
-        <v>236</v>
-      </c>
-      <c r="N145" s="33"/>
-      <c r="O145" s="33"/>
-    </row>
-    <row r="146" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="8">
-        <v>169</v>
-      </c>
-      <c r="B146" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="C146" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="D146" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F146" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="G146" s="8">
-        <v>401</v>
-      </c>
-      <c r="H146" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="I146" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J146" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K146" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L146" s="8">
-        <v>1014</v>
-      </c>
-      <c r="M146" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="N146" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O146" s="64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A147" s="106" t="s">
-        <v>145</v>
-      </c>
-      <c r="B147" s="106"/>
-      <c r="C147" s="106"/>
-      <c r="D147" s="106"/>
-      <c r="E147" s="106"/>
-      <c r="F147" s="106"/>
-      <c r="G147" s="106"/>
-      <c r="H147" s="106"/>
-      <c r="I147" s="106"/>
-      <c r="J147" s="106"/>
-      <c r="K147" s="106"/>
-      <c r="L147" s="106"/>
-      <c r="M147" s="106"/>
-      <c r="N147" s="106"/>
-      <c r="O147" s="106"/>
+      <c r="O147" s="49" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="148" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="4">
-        <v>154</v>
+      <c r="A148" s="8">
+        <v>151</v>
       </c>
       <c r="B148" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C148" s="49" t="s">
-        <v>274</v>
+      <c r="C148" s="96" t="s">
+        <v>268</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E148" s="4" t="s">
+      <c r="E148" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="F148" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="G148" s="4">
+      <c r="G148" s="38">
         <v>200</v>
       </c>
       <c r="H148" s="24" t="s">
@@ -33873,28 +33869,28 @@
       <c r="K148" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L148" s="4">
-        <v>4006</v>
-      </c>
-      <c r="M148" s="49" t="s">
-        <v>274</v>
+      <c r="L148" s="8">
+        <v>4005</v>
+      </c>
+      <c r="M148" s="96" t="s">
+        <v>268</v>
       </c>
       <c r="N148" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O148" s="49" t="s">
-        <v>275</v>
+      <c r="O148" s="96" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="149" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="8">
-        <v>151</v>
+      <c r="A149" s="4">
+        <v>97</v>
       </c>
       <c r="B149" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C149" s="96" t="s">
-        <v>268</v>
+      <c r="C149" s="23" t="s">
+        <v>85</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>12</v>
@@ -33917,33 +33913,33 @@
       <c r="J149" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K149" s="4" t="s">
-        <v>11</v>
+      <c r="K149" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="L149" s="8">
-        <v>4005</v>
-      </c>
-      <c r="M149" s="96" t="s">
-        <v>268</v>
+        <v>4002</v>
+      </c>
+      <c r="M149" s="32" t="s">
+        <v>38</v>
       </c>
       <c r="N149" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O149" s="96" t="s">
-        <v>267</v>
+      <c r="O149" s="31" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="150" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B150" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C150" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D150" s="5" t="s">
+      <c r="C150" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D150" s="26" t="s">
         <v>12</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -33964,31 +33960,31 @@
       <c r="J150" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K150" s="5" t="s">
+      <c r="K150" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="L150" s="8">
-        <v>4002</v>
+      <c r="L150" s="26">
+        <v>4003</v>
       </c>
       <c r="M150" s="32" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="N150" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O150" s="31" t="s">
-        <v>62</v>
+      <c r="O150" s="33" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B151" s="31" t="s">
         <v>133</v>
       </c>
       <c r="C151" s="27" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="D151" s="26" t="s">
         <v>12</v>
@@ -34015,35 +34011,35 @@
         <v>30</v>
       </c>
       <c r="L151" s="26">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="M151" s="32" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="N151" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="O151" s="33" t="s">
-        <v>1</v>
+      <c r="O151" s="31" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="152" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B152" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C152" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="D152" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E152" s="5" t="s">
+      <c r="C152" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D152" s="4">
+        <v>8</v>
+      </c>
+      <c r="E152" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="F152" s="24" t="s">
         <v>140</v>
       </c>
       <c r="G152" s="38">
@@ -34055,311 +34051,311 @@
       <c r="I152" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="J152" s="5" t="s">
+      <c r="J152" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K152" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="L152" s="26">
-        <v>4004</v>
-      </c>
-      <c r="M152" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="N152" s="31" t="s">
+      <c r="K152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L152" s="4">
+        <v>1010</v>
+      </c>
+      <c r="M152" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="N152" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="O152" s="31" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="153" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="4">
-        <v>99</v>
-      </c>
-      <c r="B153" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D153" s="4">
-        <v>8</v>
-      </c>
-      <c r="E153" s="24" t="s">
+      <c r="O152" s="30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:66" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A153" s="106" t="s">
+        <v>173</v>
+      </c>
+      <c r="B153" s="106"/>
+      <c r="C153" s="106"/>
+      <c r="D153" s="106"/>
+      <c r="E153" s="106"/>
+      <c r="F153" s="106"/>
+      <c r="G153" s="106"/>
+      <c r="H153" s="106"/>
+      <c r="I153" s="106"/>
+      <c r="J153" s="106"/>
+      <c r="K153" s="106"/>
+      <c r="L153" s="106"/>
+      <c r="M153" s="106"/>
+      <c r="N153" s="106"/>
+      <c r="O153" s="106"/>
+    </row>
+    <row r="154" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A154" s="107" t="s">
+        <v>146</v>
+      </c>
+      <c r="B154" s="107"/>
+      <c r="C154" s="107"/>
+      <c r="D154" s="107"/>
+      <c r="E154" s="107"/>
+      <c r="F154" s="107"/>
+      <c r="G154" s="107"/>
+      <c r="H154" s="107"/>
+      <c r="I154" s="107"/>
+      <c r="J154" s="107"/>
+      <c r="K154" s="107"/>
+      <c r="L154" s="107"/>
+      <c r="M154" s="107"/>
+      <c r="N154" s="107"/>
+      <c r="O154" s="107"/>
+    </row>
+    <row r="155" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="92">
+        <v>146</v>
+      </c>
+      <c r="B155" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C155" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D155" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F153" s="24" t="s">
+      <c r="F155" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G153" s="38">
-        <v>200</v>
-      </c>
-      <c r="H153" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="I153" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="J153" s="4" t="s">
+      <c r="G155" s="92">
+        <v>403</v>
+      </c>
+      <c r="H155" s="92" t="s">
+        <v>216</v>
+      </c>
+      <c r="I155" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="J155" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K153" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L153" s="4">
-        <v>1010</v>
-      </c>
-      <c r="M153" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="N153" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="O153" s="30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:66" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="105" t="s">
-        <v>173</v>
-      </c>
-      <c r="B154" s="105"/>
-      <c r="C154" s="105"/>
-      <c r="D154" s="105"/>
-      <c r="E154" s="105"/>
-      <c r="F154" s="105"/>
-      <c r="G154" s="105"/>
-      <c r="H154" s="105"/>
-      <c r="I154" s="105"/>
-      <c r="J154" s="105"/>
-      <c r="K154" s="105"/>
-      <c r="L154" s="105"/>
-      <c r="M154" s="105"/>
-      <c r="N154" s="105"/>
-      <c r="O154" s="105"/>
-    </row>
-    <row r="155" spans="1:66" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A155" s="106" t="s">
-        <v>146</v>
-      </c>
-      <c r="B155" s="106"/>
-      <c r="C155" s="106"/>
-      <c r="D155" s="106"/>
-      <c r="E155" s="106"/>
-      <c r="F155" s="106"/>
-      <c r="G155" s="106"/>
-      <c r="H155" s="106"/>
-      <c r="I155" s="106"/>
-      <c r="J155" s="106"/>
-      <c r="K155" s="106"/>
-      <c r="L155" s="106"/>
-      <c r="M155" s="106"/>
-      <c r="N155" s="106"/>
-      <c r="O155" s="106"/>
-    </row>
-    <row r="156" spans="1:66" s="11" customFormat="1" ht="40.700000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="92">
-        <v>146</v>
+      <c r="K155" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L155" s="92">
+        <v>1016</v>
+      </c>
+      <c r="M155" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="N155" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="O155" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="P155" s="21"/>
+      <c r="Q155" s="21"/>
+      <c r="R155" s="21"/>
+      <c r="S155" s="21"/>
+      <c r="T155" s="21"/>
+      <c r="U155" s="21"/>
+      <c r="V155" s="21"/>
+      <c r="W155" s="21"/>
+      <c r="X155" s="21"/>
+      <c r="Y155" s="21"/>
+      <c r="Z155" s="21"/>
+      <c r="AA155" s="21"/>
+      <c r="AB155" s="21"/>
+      <c r="AC155" s="21"/>
+      <c r="AD155" s="21"/>
+      <c r="AE155" s="21"/>
+      <c r="AF155" s="21"/>
+      <c r="AG155" s="21"/>
+      <c r="AH155" s="21"/>
+      <c r="AI155" s="21"/>
+      <c r="AJ155" s="21"/>
+      <c r="AK155" s="21"/>
+      <c r="AL155" s="21"/>
+      <c r="AM155" s="21"/>
+      <c r="AN155" s="21"/>
+      <c r="AO155" s="21"/>
+      <c r="AP155" s="21"/>
+      <c r="AQ155" s="21"/>
+      <c r="AR155" s="21"/>
+      <c r="AS155" s="21"/>
+      <c r="AT155" s="21"/>
+      <c r="AU155" s="21"/>
+      <c r="AV155" s="21"/>
+      <c r="AW155" s="21"/>
+      <c r="AX155" s="21"/>
+      <c r="AY155" s="21"/>
+      <c r="AZ155" s="21"/>
+      <c r="BA155" s="21"/>
+      <c r="BB155" s="21"/>
+      <c r="BC155" s="21"/>
+      <c r="BD155" s="21"/>
+      <c r="BE155" s="21"/>
+      <c r="BF155" s="21"/>
+      <c r="BG155" s="21"/>
+      <c r="BH155" s="21"/>
+      <c r="BI155" s="21"/>
+      <c r="BJ155" s="21"/>
+      <c r="BK155" s="21"/>
+      <c r="BL155" s="21"/>
+      <c r="BM155" s="21"/>
+      <c r="BN155" s="21"/>
+    </row>
+    <row r="156" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A156" s="4">
+        <v>102</v>
       </c>
       <c r="B156" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C156" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="D156" s="92" t="s">
+      <c r="C156" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D156" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E156" s="92" t="s">
+      <c r="E156" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F156" s="92" t="s">
+      <c r="F156" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G156" s="92">
-        <v>403</v>
-      </c>
-      <c r="H156" s="92" t="s">
+      <c r="G156" s="24">
+        <v>401</v>
+      </c>
+      <c r="H156" s="65" t="s">
         <v>216</v>
       </c>
       <c r="I156" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J156" s="92" t="s">
+      <c r="J156" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K156" s="92" t="s">
+      <c r="K156" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L156" s="92">
-        <v>1016</v>
-      </c>
-      <c r="M156" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N156" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="O156" s="93" t="s">
+      <c r="L156" s="4">
+        <v>1012</v>
+      </c>
+      <c r="M156" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="N156" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="P156" s="21"/>
-      <c r="Q156" s="21"/>
-      <c r="R156" s="21"/>
-      <c r="S156" s="21"/>
-      <c r="T156" s="21"/>
-      <c r="U156" s="21"/>
-      <c r="V156" s="21"/>
-      <c r="W156" s="21"/>
-      <c r="X156" s="21"/>
-      <c r="Y156" s="21"/>
-      <c r="Z156" s="21"/>
-      <c r="AA156" s="21"/>
-      <c r="AB156" s="21"/>
-      <c r="AC156" s="21"/>
-      <c r="AD156" s="21"/>
-      <c r="AE156" s="21"/>
-      <c r="AF156" s="21"/>
-      <c r="AG156" s="21"/>
-      <c r="AH156" s="21"/>
-      <c r="AI156" s="21"/>
-      <c r="AJ156" s="21"/>
-      <c r="AK156" s="21"/>
-      <c r="AL156" s="21"/>
-      <c r="AM156" s="21"/>
-      <c r="AN156" s="21"/>
-      <c r="AO156" s="21"/>
-      <c r="AP156" s="21"/>
-      <c r="AQ156" s="21"/>
-      <c r="AR156" s="21"/>
-      <c r="AS156" s="21"/>
-      <c r="AT156" s="21"/>
-      <c r="AU156" s="21"/>
-      <c r="AV156" s="21"/>
-      <c r="AW156" s="21"/>
-      <c r="AX156" s="21"/>
-      <c r="AY156" s="21"/>
-      <c r="AZ156" s="21"/>
-      <c r="BA156" s="21"/>
-      <c r="BB156" s="21"/>
-      <c r="BC156" s="21"/>
-      <c r="BD156" s="21"/>
-      <c r="BE156" s="21"/>
-      <c r="BF156" s="21"/>
-      <c r="BG156" s="21"/>
-      <c r="BH156" s="21"/>
-      <c r="BI156" s="21"/>
-      <c r="BJ156" s="21"/>
-      <c r="BK156" s="21"/>
-      <c r="BL156" s="21"/>
-      <c r="BM156" s="21"/>
-      <c r="BN156" s="21"/>
-    </row>
-    <row r="157" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A157" s="4">
-        <v>102</v>
-      </c>
-      <c r="B157" s="32" t="s">
+      <c r="O156" s="49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:66" s="22" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A157" s="92">
+        <v>103</v>
+      </c>
+      <c r="B157" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="C157" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D157" s="4" t="s">
+      <c r="C157" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="D157" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E157" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="F157" s="4" t="s">
+      <c r="F157" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="G157" s="24">
+      <c r="G157" s="74">
         <v>401</v>
       </c>
       <c r="H157" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="I157" s="24" t="s">
+      <c r="I157" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="J157" s="4" t="s">
+      <c r="J157" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K157" s="4" t="s">
+      <c r="K157" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L157" s="4">
-        <v>1012</v>
-      </c>
-      <c r="M157" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="N157" s="32" t="s">
+      <c r="L157" s="92">
+        <v>1013</v>
+      </c>
+      <c r="M157" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="N157" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="O157" s="49" t="s">
+      <c r="O157" s="93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:66" s="22" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="92">
-        <v>103</v>
-      </c>
-      <c r="B158" s="101" t="s">
+    <row r="158" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A158" s="4">
+        <v>105</v>
+      </c>
+      <c r="B158" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C158" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="D158" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E158" s="92" t="s">
+      <c r="C158" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D158" s="24">
+        <v>201</v>
+      </c>
+      <c r="E158" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F158" s="92" t="s">
+      <c r="F158" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G158" s="74">
-        <v>401</v>
+      <c r="G158" s="44">
+        <v>400</v>
       </c>
       <c r="H158" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="I158" s="74" t="s">
+      <c r="I158" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J158" s="92" t="s">
+      <c r="J158" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K158" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L158" s="92">
-        <v>1013</v>
-      </c>
-      <c r="M158" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="N158" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="O158" s="93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="159" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="K158" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L158" s="40">
+        <v>1003</v>
+      </c>
+      <c r="M158" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="N158" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="O158" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="159" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B159" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C159" s="23" t="s">
-        <v>264</v>
+        <v>148</v>
       </c>
       <c r="D159" s="24">
         <v>201</v>
@@ -34370,7 +34366,7 @@
       <c r="F159" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G159" s="44">
+      <c r="G159" s="24">
         <v>400</v>
       </c>
       <c r="H159" s="65" t="s">
@@ -34383,13 +34379,13 @@
         <v>7</v>
       </c>
       <c r="K159" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L159" s="40">
-        <v>1003</v>
+        <v>11</v>
+      </c>
+      <c r="L159" s="25">
+        <v>1004</v>
       </c>
       <c r="M159" s="32" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N159" s="32" t="s">
         <v>55</v>
@@ -34398,26 +34394,26 @@
         <v>43</v>
       </c>
     </row>
-    <row r="160" spans="1:66" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B160" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C160" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="D160" s="24">
-        <v>201</v>
-      </c>
-      <c r="E160" s="24" t="s">
+      <c r="C160" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D160" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F160" s="24" t="s">
+      <c r="F160" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G160" s="24">
+      <c r="G160" s="54">
         <v>400</v>
       </c>
       <c r="H160" s="65" t="s">
@@ -34426,46 +34422,46 @@
       <c r="I160" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J160" s="24" t="s">
+      <c r="J160" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K160" s="24" t="s">
+      <c r="K160" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L160" s="25">
-        <v>1004</v>
-      </c>
-      <c r="M160" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="N160" s="32" t="s">
+      <c r="L160" s="53">
+        <v>1015</v>
+      </c>
+      <c r="M160" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="N160" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="O160" s="32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="O160" s="63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B161" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C161" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D161" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E161" s="53" t="s">
+      <c r="C161" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D161" s="24">
+        <v>202</v>
+      </c>
+      <c r="E161" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F161" s="53" t="s">
+      <c r="F161" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G161" s="54">
-        <v>400</v>
+      <c r="G161" s="44">
+        <v>403</v>
       </c>
       <c r="H161" s="65" t="s">
         <v>216</v>
@@ -34473,34 +34469,34 @@
       <c r="I161" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J161" s="53" t="s">
+      <c r="J161" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K161" s="54" t="s">
+      <c r="K161" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L161" s="53">
-        <v>1015</v>
-      </c>
-      <c r="M161" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="N161" s="52" t="s">
+      <c r="L161" s="25">
+        <v>1006</v>
+      </c>
+      <c r="M161" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="N161" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O161" s="63" t="s">
-        <v>12</v>
+      <c r="O161" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B162" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C162" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D162" s="24">
         <v>202</v>
@@ -34524,13 +34520,13 @@
         <v>7</v>
       </c>
       <c r="K162" s="24" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L162" s="25">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M162" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N162" s="32" t="s">
         <v>55</v>
@@ -34539,15 +34535,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B163" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C163" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D163" s="24">
         <v>202</v>
@@ -34558,7 +34554,7 @@
       <c r="F163" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G163" s="44">
+      <c r="G163" s="24">
         <v>403</v>
       </c>
       <c r="H163" s="65" t="s">
@@ -34574,10 +34570,10 @@
         <v>30</v>
       </c>
       <c r="L163" s="25">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M163" s="32" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N163" s="32" t="s">
         <v>55</v>
@@ -34586,15 +34582,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B164" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C164" s="23" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="D164" s="24">
         <v>202</v>
@@ -34620,11 +34616,11 @@
       <c r="K164" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="L164" s="25">
-        <v>1008</v>
+      <c r="L164" s="65">
+        <v>5001</v>
       </c>
       <c r="M164" s="32" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="N164" s="32" t="s">
         <v>55</v>
@@ -34633,15 +34629,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="165" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="4">
-        <v>110</v>
-      </c>
+    <row r="165" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="4"/>
       <c r="B165" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C165" s="23" t="s">
-        <v>175</v>
+        <v>295</v>
       </c>
       <c r="D165" s="24">
         <v>202</v>
@@ -34655,7 +34649,7 @@
       <c r="G165" s="24">
         <v>403</v>
       </c>
-      <c r="H165" s="65" t="s">
+      <c r="H165" s="24" t="s">
         <v>216</v>
       </c>
       <c r="I165" s="24" t="s">
@@ -34665,13 +34659,13 @@
         <v>7</v>
       </c>
       <c r="K165" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="L165" s="65">
-        <v>5001</v>
+        <v>32</v>
+      </c>
+      <c r="L165" s="24">
+        <v>1011</v>
       </c>
       <c r="M165" s="32" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="N165" s="32" t="s">
         <v>55</v>
@@ -34680,13 +34674,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="166" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="4"/>
+    <row r="166" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A166" s="4">
+        <v>111</v>
+      </c>
       <c r="B166" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C166" s="23" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
       <c r="D166" s="24">
         <v>202</v>
@@ -34697,10 +34693,10 @@
       <c r="F166" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G166" s="24">
+      <c r="G166" s="44">
         <v>403</v>
       </c>
-      <c r="H166" s="24" t="s">
+      <c r="H166" s="65" t="s">
         <v>216</v>
       </c>
       <c r="I166" s="24" t="s">
@@ -34722,30 +34718,30 @@
         <v>55</v>
       </c>
       <c r="O166" s="30" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B167" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C167" s="23" t="s">
+      <c r="C167" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D167" s="4">
         <v>203</v>
       </c>
-      <c r="D167" s="24">
-        <v>202</v>
-      </c>
-      <c r="E167" s="24" t="s">
+      <c r="E167" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F167" s="24" t="s">
+      <c r="F167" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G167" s="44">
-        <v>403</v>
+      <c r="G167" s="24">
+        <v>400</v>
       </c>
       <c r="H167" s="65" t="s">
         <v>216</v>
@@ -34753,34 +34749,34 @@
       <c r="I167" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J167" s="24" t="s">
+      <c r="J167" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K167" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L167" s="24">
-        <v>1011</v>
-      </c>
-      <c r="M167" s="32" t="s">
-        <v>202</v>
+      <c r="K167" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L167" s="20">
+        <v>5005</v>
+      </c>
+      <c r="M167" s="30" t="s">
+        <v>178</v>
       </c>
       <c r="N167" s="32" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="O167" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="4">
-        <v>112</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="A168" s="26">
+        <v>132</v>
       </c>
       <c r="B168" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C168" s="6" t="s">
-        <v>177</v>
+      <c r="C168" s="57" t="s">
+        <v>195</v>
       </c>
       <c r="D168" s="4">
         <v>203</v>
@@ -34800,19 +34796,19 @@
       <c r="I168" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J168" s="4" t="s">
+      <c r="J168" s="58" t="s">
         <v>7</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L168" s="20">
-        <v>5005</v>
-      </c>
-      <c r="M168" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="N168" s="32" t="s">
+      <c r="L168" s="26">
+        <v>3003</v>
+      </c>
+      <c r="M168" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="N168" s="33" t="s">
         <v>214</v>
       </c>
       <c r="O168" s="30" t="s">
@@ -34821,16 +34817,16 @@
     </row>
     <row r="169" spans="1:15" ht="45.75" x14ac:dyDescent="0.25">
       <c r="A169" s="26">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B169" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C169" s="57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D169" s="4">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>140</v>
@@ -34854,30 +34850,30 @@
         <v>11</v>
       </c>
       <c r="L169" s="26">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="M169" s="57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N169" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="O169" s="30" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" ht="45.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="26">
-        <v>131</v>
+      <c r="O169" s="56" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A170" s="8">
+        <v>130</v>
       </c>
       <c r="B170" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C170" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="D170" s="4">
-        <v>204</v>
+        <v>201</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>140</v>
@@ -34901,30 +34897,30 @@
         <v>11</v>
       </c>
       <c r="L170" s="26">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="M170" s="57" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="N170" s="33" t="s">
         <v>214</v>
       </c>
       <c r="O170" s="56" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" ht="60.75" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B171" s="32" t="s">
         <v>174</v>
       </c>
       <c r="C171" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>12</v>
+        <v>198</v>
+      </c>
+      <c r="D171" s="4">
+        <v>203</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>140</v>
@@ -34948,30 +34944,30 @@
         <v>11</v>
       </c>
       <c r="L171" s="26">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="M171" s="57" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N171" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="O171" s="56" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="8">
-        <v>128</v>
+      <c r="O171" s="57" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="26">
+        <v>129</v>
       </c>
       <c r="B172" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C172" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="D172" s="4">
-        <v>203</v>
+      <c r="C172" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>140</v>
@@ -34979,8 +34975,8 @@
       <c r="F172" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G172" s="24">
-        <v>400</v>
+      <c r="G172" s="65">
+        <v>404</v>
       </c>
       <c r="H172" s="65" t="s">
         <v>216</v>
@@ -34994,11 +34990,11 @@
       <c r="K172" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L172" s="26">
-        <v>3006</v>
-      </c>
-      <c r="M172" s="57" t="s">
-        <v>198</v>
+      <c r="L172" s="66">
+        <v>3007</v>
+      </c>
+      <c r="M172" s="67" t="s">
+        <v>205</v>
       </c>
       <c r="N172" s="33" t="s">
         <v>214</v>
@@ -35007,99 +35003,69 @@
         <v>179</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A173" s="26">
-        <v>129</v>
+    <row r="173" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A173" s="8">
+        <v>170</v>
       </c>
       <c r="B173" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C173" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="D173" s="4" t="s">
+      <c r="C173" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D173" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E173" s="4" t="s">
+      <c r="E173" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F173" s="4" t="s">
+      <c r="F173" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G173" s="65">
-        <v>404</v>
-      </c>
-      <c r="H173" s="65" t="s">
+      <c r="G173" s="8">
+        <v>401</v>
+      </c>
+      <c r="H173" s="54" t="s">
         <v>216</v>
       </c>
       <c r="I173" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J173" s="58" t="s">
+      <c r="J173" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="K173" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L173" s="66">
-        <v>3007</v>
-      </c>
-      <c r="M173" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="N173" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="O173" s="57" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A174" s="8">
-        <v>170</v>
-      </c>
-      <c r="B174" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="C174" s="31" t="s">
+      <c r="K173" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L173" s="8">
+        <v>1014</v>
+      </c>
+      <c r="M173" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="D174" s="58" t="s">
+      <c r="N173" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="E174" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F174" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="G174" s="8">
-        <v>401</v>
-      </c>
-      <c r="H174" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="I174" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J174" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="K174" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="L174" s="8">
-        <v>1014</v>
-      </c>
-      <c r="M174" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="N174" s="64" t="s">
+      <c r="O173" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="O174" s="64" t="s">
-        <v>12</v>
-      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="20"/>
+      <c r="B174" s="21"/>
+      <c r="C174" s="22"/>
+      <c r="D174" s="20"/>
+      <c r="E174" s="20"/>
+      <c r="F174" s="20"/>
+      <c r="G174" s="45"/>
+      <c r="H174" s="45"/>
+      <c r="I174" s="45"/>
+      <c r="J174" s="20"/>
+      <c r="K174" s="20"/>
+      <c r="L174" s="20"/>
+      <c r="M174" s="34"/>
+      <c r="N174" s="21"/>
+      <c r="O174" s="21"/>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="20"/>
@@ -35113,7 +35079,6 @@
       <c r="I175" s="45"/>
       <c r="J175" s="20"/>
       <c r="K175" s="20"/>
-      <c r="L175" s="20"/>
       <c r="M175" s="34"/>
       <c r="N175" s="21"/>
       <c r="O175" s="21"/>
@@ -35130,6 +35095,7 @@
       <c r="I176" s="45"/>
       <c r="J176" s="20"/>
       <c r="K176" s="20"/>
+      <c r="L176" s="20"/>
       <c r="M176" s="34"/>
       <c r="N176" s="21"/>
       <c r="O176" s="21"/>
@@ -35401,7 +35367,6 @@
       <c r="I192" s="45"/>
       <c r="J192" s="20"/>
       <c r="K192" s="20"/>
-      <c r="L192" s="20"/>
       <c r="M192" s="34"/>
       <c r="N192" s="21"/>
       <c r="O192" s="21"/>
@@ -35418,6 +35383,7 @@
       <c r="I193" s="45"/>
       <c r="J193" s="20"/>
       <c r="K193" s="20"/>
+      <c r="L193" s="20"/>
       <c r="M193" s="34"/>
       <c r="N193" s="21"/>
       <c r="O193" s="21"/>
@@ -40301,51 +40267,34 @@
       <c r="N480" s="21"/>
       <c r="O480" s="21"/>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A481" s="20"/>
-      <c r="B481" s="21"/>
-      <c r="C481" s="22"/>
-      <c r="D481" s="20"/>
-      <c r="E481" s="20"/>
-      <c r="F481" s="20"/>
-      <c r="G481" s="45"/>
-      <c r="H481" s="45"/>
-      <c r="I481" s="45"/>
-      <c r="J481" s="20"/>
-      <c r="K481" s="20"/>
-      <c r="L481" s="20"/>
-      <c r="M481" s="34"/>
-      <c r="N481" s="21"/>
-      <c r="O481" s="21"/>
-    </row>
   </sheetData>
-  <autoFilter ref="G1:G481" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="G1:G480" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataConsolidate/>
   <mergeCells count="15">
-    <mergeCell ref="A154:O154"/>
-    <mergeCell ref="A155:O155"/>
-    <mergeCell ref="A147:O147"/>
-    <mergeCell ref="A126:O126"/>
-    <mergeCell ref="A130:O130"/>
-    <mergeCell ref="A103:O103"/>
-    <mergeCell ref="A102:O102"/>
-    <mergeCell ref="A129:O129"/>
-    <mergeCell ref="A87:O87"/>
-    <mergeCell ref="A71:O71"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A69:O69"/>
+    <mergeCell ref="A85:O85"/>
+    <mergeCell ref="A102:O102"/>
+    <mergeCell ref="A101:O101"/>
+    <mergeCell ref="A128:O128"/>
+    <mergeCell ref="A86:O86"/>
     <mergeCell ref="A70:O70"/>
-    <mergeCell ref="A86:O86"/>
+    <mergeCell ref="A153:O153"/>
+    <mergeCell ref="A154:O154"/>
+    <mergeCell ref="A146:O146"/>
+    <mergeCell ref="A125:O125"/>
+    <mergeCell ref="A129:O129"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J17 J127:J128 J148:J153 J7:J8 J76:J77 J92:J93 J107:J109 J134:J136 J159:J160 J20:J21 J138:J146 J111:J125 J95:J100 J30 J79:J84 J33:J53 J162:J173 J55:J69" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J17 J126:J127 J147:J152 J7:J8 J75:J76 J91:J92 J106:J108 J133:J135 J158:J159 J20:J21 J137:J145 J110:J124 J94:J99 J30 J78:J83 J55:J68 J161:J172 J33:J53" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Error,Warning"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K148:K150 K10:K17 K153 K127:K128 K7:K8 K76:K77 K92:K93 K107:K109 K134:K136 K159:K160 K20:K21 K79:K84 K138:K146 K111:K125 K95:K100 K30:K53 K162:K173 K55:K69" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K147:K149 K10:K17 K152 K126:K127 K7:K8 K75:K76 K91:K92 K106:K108 K133:K135 K158:K159 K20:K21 K78:K83 K137:K145 K110:K124 K94:K99 K55:K68 K161:K172 K30:K53" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Field,Cross Field,Cross Form"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L10:L15 L20:L21 L111:L117 L95:L100 L128 L35:L41 L166:L168 L162:L164 L7:L8 L76:L77 L92:L93 L107:L109 L134:L136 L159:L160 L17 L43:L52 L79:L84 L138:L140 L142:L146 L33 L30 L150 L153 L55 L57:L60" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L10:L15 L20:L21 L110:L116 L94:L99 L127 L55:L59 L165:L167 L161:L163 L7:L8 L75:L76 L91:L92 L106:L108 L133:L135 L158:L159 L17 L43:L52 L78:L83 L137:L139 L141:L145 L33 L30 L149 L152 L35:L41" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -40357,8 +40306,8 @@
   </headerFooter>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="25" max="16383" man="1"/>
-    <brk id="69" max="16383" man="1"/>
-    <brk id="101" max="9" man="1"/>
+    <brk id="68" max="16383" man="1"/>
+    <brk id="100" max="9" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>